--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -1646,7 +1646,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1660,7 +1660,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1671,7 +1670,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
@@ -2431,7 +2429,7 @@
         <v>4</v>
       </c>
       <c r="O6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="4">
         <v>0</v>
@@ -2631,7 +2629,7 @@
         <v>12</v>
       </c>
       <c r="O8" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8" s="2">
         <f t="shared" ref="P8:P71" si="6">P7+1</f>
@@ -2733,7 +2731,7 @@
         <v>16</v>
       </c>
       <c r="O9" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P9" s="2">
         <f t="shared" si="6"/>
@@ -2835,7 +2833,7 @@
         <v>20</v>
       </c>
       <c r="O10" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P10" s="2">
         <f t="shared" si="6"/>
@@ -2936,8 +2934,8 @@
         <f t="shared" si="3"/>
         <v>24</v>
       </c>
-      <c r="O11" s="5">
-        <v>5</v>
+      <c r="O11" s="1">
+        <v>1</v>
       </c>
       <c r="P11" s="3">
         <f t="shared" si="6"/>
@@ -3039,7 +3037,8 @@
         <v>28</v>
       </c>
       <c r="O12" s="6">
-        <v>6</v>
+        <f t="shared" ref="O12:O75" si="8">O6+1</f>
+        <v>2</v>
       </c>
       <c r="P12" s="4">
         <f t="shared" si="6"/>
@@ -3086,7 +3085,7 @@
         <v>6</v>
       </c>
       <c r="AC12" s="4">
-        <f t="shared" ref="AC8:AC75" si="8">AC11+AG11</f>
+        <f t="shared" ref="AC8:AC75" si="9">AC11+AG11</f>
         <v>153</v>
       </c>
       <c r="AD12" s="6">
@@ -3110,7 +3109,7 @@
       <c r="E13" s="6">
         <v>1</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>42</v>
       </c>
       <c r="G13" s="6">
@@ -3142,7 +3141,8 @@
         <v>32</v>
       </c>
       <c r="O13" s="6">
-        <v>7</v>
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="P13" s="4">
         <f t="shared" si="6"/>
@@ -3189,7 +3189,7 @@
         <v>7</v>
       </c>
       <c r="AC13" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>170</v>
       </c>
       <c r="AD13" s="6">
@@ -3245,7 +3245,8 @@
         <v>36</v>
       </c>
       <c r="O14" s="6">
-        <v>8</v>
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="6"/>
@@ -3292,7 +3293,7 @@
         <v>8</v>
       </c>
       <c r="AC14" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>189</v>
       </c>
       <c r="AD14" s="6">
@@ -3316,7 +3317,7 @@
       <c r="E15" s="6">
         <v>1</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G15" s="6">
@@ -3348,7 +3349,8 @@
         <v>40</v>
       </c>
       <c r="O15" s="6">
-        <v>9</v>
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="P15" s="4">
         <f t="shared" si="6"/>
@@ -3395,7 +3397,7 @@
         <v>9</v>
       </c>
       <c r="AC15" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>212</v>
       </c>
       <c r="AD15" s="6">
@@ -3451,7 +3453,8 @@
         <v>44</v>
       </c>
       <c r="O16" s="6">
-        <v>10</v>
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="P16" s="4">
         <f t="shared" si="6"/>
@@ -3498,7 +3501,7 @@
         <v>10</v>
       </c>
       <c r="AC16" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>241</v>
       </c>
       <c r="AD16" s="6">
@@ -3553,8 +3556,9 @@
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
-      <c r="O17" s="5">
-        <v>11</v>
+      <c r="O17" s="6">
+        <f t="shared" si="8"/>
+        <v>2</v>
       </c>
       <c r="P17" s="3">
         <f t="shared" si="6"/>
@@ -3591,7 +3595,7 @@
         <v>12</v>
       </c>
       <c r="Z17" s="3">
-        <f t="shared" ref="Z17:Z22" si="9">Z16+100</f>
+        <f t="shared" ref="Z17:Z22" si="10">Z16+100</f>
         <v>500</v>
       </c>
       <c r="AA17" s="3">
@@ -3601,7 +3605,7 @@
         <v>11</v>
       </c>
       <c r="AC17" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>272</v>
       </c>
       <c r="AD17" s="5">
@@ -3625,7 +3629,7 @@
       <c r="E18" s="6">
         <v>1</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="9" t="s">
         <v>47</v>
       </c>
       <c r="G18" s="6">
@@ -3657,7 +3661,8 @@
         <v>52</v>
       </c>
       <c r="O18" s="6">
-        <v>12</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="6"/>
@@ -3694,7 +3699,7 @@
         <v>13</v>
       </c>
       <c r="Z18" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>600</v>
       </c>
       <c r="AA18" s="4">
@@ -3704,7 +3709,7 @@
         <v>12</v>
       </c>
       <c r="AC18" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>309</v>
       </c>
       <c r="AD18" s="6">
@@ -3760,7 +3765,8 @@
         <v>56</v>
       </c>
       <c r="O19" s="6">
-        <v>13</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="6"/>
@@ -3797,7 +3803,7 @@
         <v>14</v>
       </c>
       <c r="Z19" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>700</v>
       </c>
       <c r="AA19" s="4">
@@ -3807,7 +3813,7 @@
         <v>13</v>
       </c>
       <c r="AC19" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>350</v>
       </c>
       <c r="AD19" s="6">
@@ -3863,7 +3869,8 @@
         <v>60</v>
       </c>
       <c r="O20" s="6">
-        <v>14</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="P20" s="4">
         <f t="shared" si="6"/>
@@ -3900,7 +3907,7 @@
         <v>15</v>
       </c>
       <c r="Z20" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>800</v>
       </c>
       <c r="AA20" s="4">
@@ -3910,7 +3917,7 @@
         <v>14</v>
       </c>
       <c r="AC20" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>393</v>
       </c>
       <c r="AD20" s="6">
@@ -3966,7 +3973,8 @@
         <v>64</v>
       </c>
       <c r="O21" s="6">
-        <v>15</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="6"/>
@@ -4003,7 +4011,7 @@
         <v>16</v>
       </c>
       <c r="Z21" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>900</v>
       </c>
       <c r="AA21" s="4">
@@ -4013,7 +4021,7 @@
         <v>15</v>
       </c>
       <c r="AC21" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>440</v>
       </c>
       <c r="AD21" s="6">
@@ -4069,7 +4077,8 @@
         <v>68</v>
       </c>
       <c r="O22" s="6">
-        <v>16</v>
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="P22" s="4">
         <f t="shared" si="6"/>
@@ -4106,7 +4115,7 @@
         <v>17</v>
       </c>
       <c r="Z22" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1000</v>
       </c>
       <c r="AA22" s="4">
@@ -4116,7 +4125,7 @@
         <v>16</v>
       </c>
       <c r="AC22" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>493</v>
       </c>
       <c r="AD22" s="6">
@@ -4171,8 +4180,9 @@
         <f t="shared" si="3"/>
         <v>72</v>
       </c>
-      <c r="O23" s="5">
-        <v>17</v>
+      <c r="O23" s="6">
+        <f t="shared" si="8"/>
+        <v>3</v>
       </c>
       <c r="P23" s="3">
         <f t="shared" si="6"/>
@@ -4219,7 +4229,7 @@
         <v>17</v>
       </c>
       <c r="AC23" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>552</v>
       </c>
       <c r="AD23" s="5">
@@ -4275,7 +4285,8 @@
         <v>76</v>
       </c>
       <c r="O24" s="6">
-        <v>18</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="P24" s="4">
         <f t="shared" si="6"/>
@@ -4322,7 +4333,7 @@
         <v>18</v>
       </c>
       <c r="AC24" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>613</v>
       </c>
       <c r="AD24" s="6">
@@ -4378,7 +4389,8 @@
         <v>80</v>
       </c>
       <c r="O25" s="6">
-        <v>19</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="P25" s="4">
         <f t="shared" si="6"/>
@@ -4425,7 +4437,7 @@
         <v>19</v>
       </c>
       <c r="AC25" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>680</v>
       </c>
       <c r="AD25" s="6">
@@ -4481,7 +4493,8 @@
         <v>84</v>
       </c>
       <c r="O26" s="6">
-        <v>20</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="P26" s="4">
         <f t="shared" si="6"/>
@@ -4528,7 +4541,7 @@
         <v>20</v>
       </c>
       <c r="AC26" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>751</v>
       </c>
       <c r="AD26" s="6">
@@ -4584,7 +4597,8 @@
         <v>88</v>
       </c>
       <c r="O27" s="6">
-        <v>21</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="P27" s="4">
         <f t="shared" si="6"/>
@@ -4631,7 +4645,7 @@
         <v>21</v>
       </c>
       <c r="AC27" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>824</v>
       </c>
       <c r="AD27" s="6">
@@ -4655,7 +4669,7 @@
       <c r="E28" s="6">
         <v>1</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="9" t="s">
         <v>57</v>
       </c>
       <c r="G28" s="6">
@@ -4687,7 +4701,8 @@
         <v>92</v>
       </c>
       <c r="O28" s="6">
-        <v>22</v>
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="P28" s="4">
         <f t="shared" si="6"/>
@@ -4724,7 +4739,7 @@
         <v>23</v>
       </c>
       <c r="Z28" s="4">
-        <f t="shared" ref="Z28:Z33" si="10">Z27+500</f>
+        <f t="shared" ref="Z28:Z33" si="11">Z27+500</f>
         <v>2500</v>
       </c>
       <c r="AA28" s="4">
@@ -4734,7 +4749,7 @@
         <v>22</v>
       </c>
       <c r="AC28" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>903</v>
       </c>
       <c r="AD28" s="6">
@@ -4789,8 +4804,9 @@
         <f t="shared" si="3"/>
         <v>96</v>
       </c>
-      <c r="O29" s="5">
-        <v>23</v>
+      <c r="O29" s="6">
+        <f t="shared" si="8"/>
+        <v>4</v>
       </c>
       <c r="P29" s="3">
         <f t="shared" si="6"/>
@@ -4827,7 +4843,7 @@
         <v>24</v>
       </c>
       <c r="Z29" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3000</v>
       </c>
       <c r="AA29" s="3">
@@ -4837,7 +4853,7 @@
         <v>23</v>
       </c>
       <c r="AC29" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>986</v>
       </c>
       <c r="AD29" s="5">
@@ -4893,7 +4909,8 @@
         <v>100</v>
       </c>
       <c r="O30" s="6">
-        <v>24</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="P30" s="4">
         <f t="shared" si="6"/>
@@ -4930,7 +4947,7 @@
         <v>25</v>
       </c>
       <c r="Z30" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>3500</v>
       </c>
       <c r="AA30" s="4">
@@ -4940,7 +4957,7 @@
         <v>24</v>
       </c>
       <c r="AC30" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1075</v>
       </c>
       <c r="AD30" s="6">
@@ -4996,7 +5013,8 @@
         <v>104</v>
       </c>
       <c r="O31" s="6">
-        <v>25</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="P31" s="4">
         <f t="shared" si="6"/>
@@ -5033,7 +5051,7 @@
         <v>26</v>
       </c>
       <c r="Z31" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4000</v>
       </c>
       <c r="AA31" s="4">
@@ -5043,7 +5061,7 @@
         <v>25</v>
       </c>
       <c r="AC31" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1172</v>
       </c>
       <c r="AD31" s="6">
@@ -5067,7 +5085,7 @@
       <c r="E32" s="6">
         <v>1</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="10" t="s">
         <v>61</v>
       </c>
       <c r="G32" s="6">
@@ -5099,7 +5117,8 @@
         <v>108</v>
       </c>
       <c r="O32" s="6">
-        <v>26</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="P32" s="4">
         <f t="shared" si="6"/>
@@ -5136,7 +5155,7 @@
         <v>27</v>
       </c>
       <c r="Z32" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4500</v>
       </c>
       <c r="AA32" s="4">
@@ -5146,7 +5165,7 @@
         <v>26</v>
       </c>
       <c r="AC32" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1273</v>
       </c>
       <c r="AD32" s="6">
@@ -5202,7 +5221,8 @@
         <v>112</v>
       </c>
       <c r="O33" s="6">
-        <v>27</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="P33" s="4">
         <f t="shared" si="6"/>
@@ -5239,7 +5259,7 @@
         <v>28</v>
       </c>
       <c r="Z33" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5000</v>
       </c>
       <c r="AA33" s="4">
@@ -5249,7 +5269,7 @@
         <v>27</v>
       </c>
       <c r="AC33" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1376</v>
       </c>
       <c r="AD33" s="6">
@@ -5273,7 +5293,7 @@
       <c r="E34" s="6">
         <v>1</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="10" t="s">
         <v>63</v>
       </c>
       <c r="G34" s="6">
@@ -5305,7 +5325,8 @@
         <v>116</v>
       </c>
       <c r="O34" s="6">
-        <v>28</v>
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="P34" s="4">
         <f t="shared" si="6"/>
@@ -5352,7 +5373,7 @@
         <v>28</v>
       </c>
       <c r="AC34" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1483</v>
       </c>
       <c r="AD34" s="6">
@@ -5407,8 +5428,9 @@
         <f t="shared" si="3"/>
         <v>120</v>
       </c>
-      <c r="O35" s="5">
-        <v>29</v>
+      <c r="O35" s="6">
+        <f t="shared" si="8"/>
+        <v>5</v>
       </c>
       <c r="P35" s="3">
         <f t="shared" si="6"/>
@@ -5455,7 +5477,7 @@
         <v>29</v>
       </c>
       <c r="AC35" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1592</v>
       </c>
       <c r="AD35" s="5">
@@ -5511,7 +5533,8 @@
         <v>124</v>
       </c>
       <c r="O36" s="6">
-        <v>30</v>
+        <f t="shared" si="8"/>
+        <v>6</v>
       </c>
       <c r="P36" s="4">
         <f t="shared" si="6"/>
@@ -5558,7 +5581,7 @@
         <v>30</v>
       </c>
       <c r="AC36" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1705</v>
       </c>
       <c r="AD36" s="6">
@@ -5614,7 +5637,8 @@
         <v>128</v>
       </c>
       <c r="O37" s="6">
-        <v>31</v>
+        <f t="shared" si="8"/>
+        <v>6</v>
       </c>
       <c r="P37" s="4">
         <f t="shared" si="6"/>
@@ -5661,7 +5685,7 @@
         <v>31</v>
       </c>
       <c r="AC37" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1832</v>
       </c>
       <c r="AD37" s="6">
@@ -5717,7 +5741,8 @@
         <v>132</v>
       </c>
       <c r="O38" s="6">
-        <v>32</v>
+        <f t="shared" si="8"/>
+        <v>6</v>
       </c>
       <c r="P38" s="4">
         <f t="shared" si="6"/>
@@ -5764,7 +5789,7 @@
         <v>32</v>
       </c>
       <c r="AC38" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1963</v>
       </c>
       <c r="AD38" s="6">
@@ -5820,7 +5845,8 @@
         <v>136</v>
       </c>
       <c r="O39" s="6">
-        <v>33</v>
+        <f t="shared" si="8"/>
+        <v>6</v>
       </c>
       <c r="P39" s="4">
         <f t="shared" si="6"/>
@@ -5857,7 +5883,7 @@
         <v>34</v>
       </c>
       <c r="Z39" s="4">
-        <f t="shared" ref="Z39:Z45" si="11">Z38+2000</f>
+        <f t="shared" ref="Z39:Z45" si="12">Z38+2000</f>
         <v>12000</v>
       </c>
       <c r="AA39" s="4">
@@ -5867,7 +5893,7 @@
         <v>33</v>
       </c>
       <c r="AC39" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2100</v>
       </c>
       <c r="AD39" s="6">
@@ -5923,7 +5949,8 @@
         <v>140</v>
       </c>
       <c r="O40" s="6">
-        <v>34</v>
+        <f t="shared" si="8"/>
+        <v>6</v>
       </c>
       <c r="P40" s="4">
         <f t="shared" si="6"/>
@@ -5960,7 +5987,7 @@
         <v>35</v>
       </c>
       <c r="Z40" s="4">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>14000</v>
       </c>
       <c r="AA40" s="4">
@@ -5970,7 +5997,7 @@
         <v>34</v>
       </c>
       <c r="AC40" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2239</v>
       </c>
       <c r="AD40" s="6">
@@ -6026,8 +6053,9 @@
         <f t="shared" si="3"/>
         <v>144</v>
       </c>
-      <c r="O41" s="5">
-        <v>35</v>
+      <c r="O41" s="6">
+        <f t="shared" si="8"/>
+        <v>6</v>
       </c>
       <c r="P41" s="3">
         <f t="shared" si="6"/>
@@ -6064,7 +6092,7 @@
         <v>36</v>
       </c>
       <c r="Z41" s="3">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>16000</v>
       </c>
       <c r="AA41" s="3">
@@ -6074,7 +6102,7 @@
         <v>35</v>
       </c>
       <c r="AC41" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2388</v>
       </c>
       <c r="AD41" s="5">
@@ -6098,7 +6126,7 @@
       <c r="E42" s="1">
         <v>1</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="9" t="s">
         <v>71</v>
       </c>
       <c r="G42" s="1">
@@ -6129,8 +6157,9 @@
         <f t="shared" si="3"/>
         <v>148</v>
       </c>
-      <c r="O42" s="1">
-        <v>36</v>
+      <c r="O42" s="6">
+        <f t="shared" si="8"/>
+        <v>7</v>
       </c>
       <c r="P42" s="2">
         <f t="shared" si="6"/>
@@ -6167,7 +6196,7 @@
         <v>37</v>
       </c>
       <c r="Z42" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>18000</v>
       </c>
       <c r="AA42" s="2">
@@ -6177,7 +6206,7 @@
         <v>36</v>
       </c>
       <c r="AC42" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2539</v>
       </c>
       <c r="AD42" s="1">
@@ -6232,8 +6261,9 @@
         <f t="shared" si="3"/>
         <v>152</v>
       </c>
-      <c r="O43" s="1">
-        <v>37</v>
+      <c r="O43" s="6">
+        <f t="shared" si="8"/>
+        <v>7</v>
       </c>
       <c r="P43" s="2">
         <f t="shared" si="6"/>
@@ -6270,7 +6300,7 @@
         <v>38</v>
       </c>
       <c r="Z43" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>20000</v>
       </c>
       <c r="AA43" s="2">
@@ -6280,7 +6310,7 @@
         <v>37</v>
       </c>
       <c r="AC43" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2696</v>
       </c>
       <c r="AD43" s="1">
@@ -6304,7 +6334,7 @@
       <c r="E44" s="1">
         <v>1</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="G44" s="1">
@@ -6335,8 +6365,9 @@
         <f t="shared" si="3"/>
         <v>156</v>
       </c>
-      <c r="O44" s="1">
-        <v>38</v>
+      <c r="O44" s="6">
+        <f t="shared" si="8"/>
+        <v>7</v>
       </c>
       <c r="P44" s="2">
         <f t="shared" si="6"/>
@@ -6373,7 +6404,7 @@
         <v>39</v>
       </c>
       <c r="Z44" s="2">
-        <f t="shared" ref="Z44:Z77" si="12">Z43+5000</f>
+        <f t="shared" ref="Z44:Z77" si="13">Z43+5000</f>
         <v>25000</v>
       </c>
       <c r="AA44" s="2">
@@ -6383,7 +6414,7 @@
         <v>38</v>
       </c>
       <c r="AC44" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2859</v>
       </c>
       <c r="AD44" s="1">
@@ -6438,8 +6469,9 @@
         <f t="shared" si="3"/>
         <v>160</v>
       </c>
-      <c r="O45" s="1">
-        <v>38</v>
+      <c r="O45" s="6">
+        <f t="shared" si="8"/>
+        <v>7</v>
       </c>
       <c r="P45" s="2">
         <f t="shared" si="6"/>
@@ -6476,7 +6508,7 @@
         <v>40</v>
       </c>
       <c r="Z45" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>30000</v>
       </c>
       <c r="AA45" s="1">
@@ -6486,7 +6518,7 @@
         <v>39</v>
       </c>
       <c r="AC45" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3026</v>
       </c>
       <c r="AD45" s="1">
@@ -6510,7 +6542,7 @@
       <c r="E46" s="1">
         <v>1</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="10" t="s">
         <v>75</v>
       </c>
       <c r="G46" s="1">
@@ -6541,8 +6573,9 @@
         <f t="shared" si="3"/>
         <v>164</v>
       </c>
-      <c r="O46" s="1">
-        <v>38</v>
+      <c r="O46" s="6">
+        <f t="shared" si="8"/>
+        <v>7</v>
       </c>
       <c r="P46" s="2">
         <f t="shared" si="6"/>
@@ -6579,7 +6612,7 @@
         <v>41</v>
       </c>
       <c r="Z46" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>35000</v>
       </c>
       <c r="AA46" s="1">
@@ -6589,7 +6622,7 @@
         <v>40</v>
       </c>
       <c r="AC46" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3199</v>
       </c>
       <c r="AD46" s="1">
@@ -6612,7 +6645,7 @@
       <c r="E47" s="5">
         <v>1</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F47" s="11" t="s">
         <v>76</v>
       </c>
       <c r="G47" s="5">
@@ -6643,8 +6676,9 @@
         <f t="shared" si="3"/>
         <v>168</v>
       </c>
-      <c r="O47" s="5">
-        <v>38</v>
+      <c r="O47" s="6">
+        <f t="shared" si="8"/>
+        <v>7</v>
       </c>
       <c r="P47" s="3">
         <f t="shared" si="6"/>
@@ -6681,7 +6715,7 @@
         <v>42</v>
       </c>
       <c r="Z47" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>40000</v>
       </c>
       <c r="AA47" s="5">
@@ -6691,7 +6725,7 @@
         <v>41</v>
       </c>
       <c r="AC47" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3378</v>
       </c>
       <c r="AD47" s="5">
@@ -6746,8 +6780,9 @@
         <f t="shared" si="3"/>
         <v>172</v>
       </c>
-      <c r="O48" s="1">
-        <v>38</v>
+      <c r="O48" s="6">
+        <f t="shared" si="8"/>
+        <v>8</v>
       </c>
       <c r="P48" s="2">
         <f t="shared" si="6"/>
@@ -6784,7 +6819,7 @@
         <v>43</v>
       </c>
       <c r="Z48" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>45000</v>
       </c>
       <c r="AA48" s="1">
@@ -6794,7 +6829,7 @@
         <v>42</v>
       </c>
       <c r="AC48" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3559</v>
       </c>
       <c r="AD48" s="1">
@@ -6849,8 +6884,9 @@
         <f t="shared" si="3"/>
         <v>176</v>
       </c>
-      <c r="O49" s="1">
-        <v>38</v>
+      <c r="O49" s="6">
+        <f t="shared" si="8"/>
+        <v>8</v>
       </c>
       <c r="P49" s="2">
         <f t="shared" si="6"/>
@@ -6887,7 +6923,7 @@
         <v>44</v>
       </c>
       <c r="Z49" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>50000</v>
       </c>
       <c r="AA49" s="1">
@@ -6897,7 +6933,7 @@
         <v>43</v>
       </c>
       <c r="AC49" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3750</v>
       </c>
       <c r="AD49" s="1">
@@ -6952,8 +6988,9 @@
         <f t="shared" si="3"/>
         <v>180</v>
       </c>
-      <c r="O50" s="1">
-        <v>38</v>
+      <c r="O50" s="6">
+        <f t="shared" si="8"/>
+        <v>8</v>
       </c>
       <c r="P50" s="2">
         <f t="shared" si="6"/>
@@ -6990,7 +7027,7 @@
         <v>45</v>
       </c>
       <c r="Z50" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>55000</v>
       </c>
       <c r="AA50" s="3">
@@ -7000,7 +7037,7 @@
         <v>44</v>
       </c>
       <c r="AC50" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3943</v>
       </c>
       <c r="AD50" s="1">
@@ -7024,7 +7061,7 @@
       <c r="E51" s="1">
         <v>1</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="10" t="s">
         <v>80</v>
       </c>
       <c r="G51" s="1">
@@ -7055,8 +7092,9 @@
         <f t="shared" si="3"/>
         <v>184</v>
       </c>
-      <c r="O51" s="1">
-        <v>38</v>
+      <c r="O51" s="6">
+        <f t="shared" si="8"/>
+        <v>8</v>
       </c>
       <c r="P51" s="2">
         <f t="shared" si="6"/>
@@ -7093,7 +7131,7 @@
         <v>46</v>
       </c>
       <c r="Z51" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>60000</v>
       </c>
       <c r="AA51" s="2">
@@ -7103,7 +7141,7 @@
         <v>45</v>
       </c>
       <c r="AC51" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4140</v>
       </c>
       <c r="AD51" s="1">
@@ -7158,8 +7196,9 @@
         <f t="shared" si="3"/>
         <v>188</v>
       </c>
-      <c r="O52" s="1">
-        <v>38</v>
+      <c r="O52" s="6">
+        <f t="shared" si="8"/>
+        <v>8</v>
       </c>
       <c r="P52" s="2">
         <f t="shared" si="6"/>
@@ -7196,7 +7235,7 @@
         <v>47</v>
       </c>
       <c r="Z52" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>65000</v>
       </c>
       <c r="AA52" s="2">
@@ -7206,7 +7245,7 @@
         <v>46</v>
       </c>
       <c r="AC52" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4339</v>
       </c>
       <c r="AD52" s="1">
@@ -7261,8 +7300,9 @@
         <f t="shared" si="3"/>
         <v>192</v>
       </c>
-      <c r="O53" s="5">
-        <v>38</v>
+      <c r="O53" s="6">
+        <f t="shared" si="8"/>
+        <v>8</v>
       </c>
       <c r="P53" s="3">
         <f t="shared" si="6"/>
@@ -7299,7 +7339,7 @@
         <v>48</v>
       </c>
       <c r="Z53" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>70000</v>
       </c>
       <c r="AA53" s="3">
@@ -7309,7 +7349,7 @@
         <v>47</v>
       </c>
       <c r="AC53" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4550</v>
       </c>
       <c r="AD53" s="5">
@@ -7364,8 +7404,9 @@
         <f t="shared" si="3"/>
         <v>196</v>
       </c>
-      <c r="O54" s="1">
-        <v>38</v>
+      <c r="O54" s="6">
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="P54" s="2">
         <f t="shared" si="6"/>
@@ -7402,7 +7443,7 @@
         <v>49</v>
       </c>
       <c r="Z54" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>75000</v>
       </c>
       <c r="AA54" s="2">
@@ -7412,7 +7453,7 @@
         <v>48</v>
       </c>
       <c r="AC54" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>4773</v>
       </c>
       <c r="AD54" s="1">
@@ -7467,8 +7508,9 @@
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
-      <c r="O55" s="1">
-        <v>38</v>
+      <c r="O55" s="6">
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="P55" s="2">
         <f t="shared" si="6"/>
@@ -7505,7 +7547,7 @@
         <v>50</v>
       </c>
       <c r="Z55" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>80000</v>
       </c>
       <c r="AA55" s="2">
@@ -7515,7 +7557,7 @@
         <v>49</v>
       </c>
       <c r="AC55" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5000</v>
       </c>
       <c r="AD55" s="1">
@@ -7570,8 +7612,9 @@
         <f t="shared" si="3"/>
         <v>204</v>
       </c>
-      <c r="O56" s="1">
-        <v>38</v>
+      <c r="O56" s="6">
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="P56" s="2">
         <f t="shared" si="6"/>
@@ -7608,7 +7651,7 @@
         <v>51</v>
       </c>
       <c r="Z56" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>85000</v>
       </c>
       <c r="AA56" s="3">
@@ -7618,7 +7661,7 @@
         <v>50</v>
       </c>
       <c r="AC56" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5229</v>
       </c>
       <c r="AD56" s="1">
@@ -7673,8 +7716,9 @@
         <f t="shared" si="3"/>
         <v>208</v>
       </c>
-      <c r="O57" s="1">
-        <v>38</v>
+      <c r="O57" s="6">
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="P57" s="2">
         <f t="shared" si="6"/>
@@ -7711,7 +7755,7 @@
         <v>52</v>
       </c>
       <c r="Z57" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>90000</v>
       </c>
       <c r="AA57" s="2">
@@ -7721,7 +7765,7 @@
         <v>51</v>
       </c>
       <c r="AC57" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5462</v>
       </c>
       <c r="AD57" s="1">
@@ -7776,8 +7820,9 @@
         <f t="shared" si="3"/>
         <v>212</v>
       </c>
-      <c r="O58" s="1">
-        <v>38</v>
+      <c r="O58" s="6">
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="P58" s="2">
         <f t="shared" si="6"/>
@@ -7814,7 +7859,7 @@
         <v>53</v>
       </c>
       <c r="Z58" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>95000</v>
       </c>
       <c r="AA58" s="2">
@@ -7824,7 +7869,7 @@
         <v>52</v>
       </c>
       <c r="AC58" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5701</v>
       </c>
       <c r="AD58" s="1">
@@ -7879,8 +7924,9 @@
         <f t="shared" si="3"/>
         <v>216</v>
       </c>
-      <c r="O59" s="1">
-        <v>38</v>
+      <c r="O59" s="6">
+        <f t="shared" si="8"/>
+        <v>9</v>
       </c>
       <c r="P59" s="2">
         <f t="shared" si="6"/>
@@ -7917,7 +7963,7 @@
         <v>54</v>
       </c>
       <c r="Z59" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>100000</v>
       </c>
       <c r="AA59" s="2">
@@ -7927,7 +7973,7 @@
         <v>53</v>
       </c>
       <c r="AC59" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>5942</v>
       </c>
       <c r="AD59" s="5">
@@ -7982,8 +8028,9 @@
         <f t="shared" si="3"/>
         <v>220</v>
       </c>
-      <c r="O60" s="1">
-        <v>38</v>
+      <c r="O60" s="6">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="P60" s="2">
         <f t="shared" si="6"/>
@@ -8020,7 +8067,7 @@
         <v>55</v>
       </c>
       <c r="Z60" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>105000</v>
       </c>
       <c r="AA60" s="2">
@@ -8030,7 +8077,7 @@
         <v>54</v>
       </c>
       <c r="AC60" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6193</v>
       </c>
       <c r="AD60" s="1">
@@ -8085,8 +8132,9 @@
         <f t="shared" si="3"/>
         <v>224</v>
       </c>
-      <c r="O61" s="1">
-        <v>38</v>
+      <c r="O61" s="6">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="P61" s="2">
         <f t="shared" si="6"/>
@@ -8123,7 +8171,7 @@
         <v>56</v>
       </c>
       <c r="Z61" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>110000</v>
       </c>
       <c r="AA61" s="2">
@@ -8133,7 +8181,7 @@
         <v>55</v>
       </c>
       <c r="AC61" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6450</v>
       </c>
       <c r="AD61" s="1">
@@ -8188,8 +8236,9 @@
         <f t="shared" si="3"/>
         <v>228</v>
       </c>
-      <c r="O62" s="1">
-        <v>38</v>
+      <c r="O62" s="6">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="P62" s="2">
         <f t="shared" si="6"/>
@@ -8226,7 +8275,7 @@
         <v>57</v>
       </c>
       <c r="Z62" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>115000</v>
       </c>
       <c r="AA62" s="3">
@@ -8236,7 +8285,7 @@
         <v>56</v>
       </c>
       <c r="AC62" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6713</v>
       </c>
       <c r="AD62" s="1">
@@ -8260,7 +8309,7 @@
       <c r="E63" s="1">
         <v>1</v>
       </c>
-      <c r="F63" s="10" t="s">
+      <c r="F63" s="9" t="s">
         <v>92</v>
       </c>
       <c r="G63" s="1">
@@ -8291,8 +8340,9 @@
         <f t="shared" si="3"/>
         <v>232</v>
       </c>
-      <c r="O63" s="1">
-        <v>38</v>
+      <c r="O63" s="6">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="P63" s="2">
         <f t="shared" si="6"/>
@@ -8329,7 +8379,7 @@
         <v>58</v>
       </c>
       <c r="Z63" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>120000</v>
       </c>
       <c r="AA63" s="2">
@@ -8339,7 +8389,7 @@
         <v>57</v>
       </c>
       <c r="AC63" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6982</v>
       </c>
       <c r="AD63" s="1">
@@ -8394,8 +8444,9 @@
         <f t="shared" si="3"/>
         <v>236</v>
       </c>
-      <c r="O64" s="1">
-        <v>38</v>
+      <c r="O64" s="6">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="P64" s="2">
         <f t="shared" si="6"/>
@@ -8432,7 +8483,7 @@
         <v>59</v>
       </c>
       <c r="Z64" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>125000</v>
       </c>
       <c r="AA64" s="2">
@@ -8442,7 +8493,7 @@
         <v>58</v>
       </c>
       <c r="AC64" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7253</v>
       </c>
       <c r="AD64" s="1">
@@ -8497,8 +8548,9 @@
         <f t="shared" si="3"/>
         <v>240</v>
       </c>
-      <c r="O65" s="1">
-        <v>38</v>
+      <c r="O65" s="6">
+        <f t="shared" si="8"/>
+        <v>10</v>
       </c>
       <c r="P65" s="2">
         <f t="shared" si="6"/>
@@ -8535,7 +8587,7 @@
         <v>60</v>
       </c>
       <c r="Z65" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>130000</v>
       </c>
       <c r="AA65" s="2">
@@ -8545,7 +8597,7 @@
         <v>59</v>
       </c>
       <c r="AC65" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7530</v>
       </c>
       <c r="AD65" s="5">
@@ -8585,11 +8637,11 @@
         <v>23400000000</v>
       </c>
       <c r="K66" s="1">
-        <f t="shared" ref="K66:K77" si="13">K65+10</f>
+        <f t="shared" ref="K66:K77" si="14">K65+10</f>
         <v>310</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" ref="L66:L77" si="14">L65+5</f>
+        <f t="shared" ref="L66:L77" si="15">L65+5</f>
         <v>185</v>
       </c>
       <c r="M66" s="1">
@@ -8600,8 +8652,9 @@
         <f t="shared" si="3"/>
         <v>244</v>
       </c>
-      <c r="O66" s="1">
-        <v>38</v>
+      <c r="O66" s="6">
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="P66" s="2">
         <f t="shared" si="6"/>
@@ -8638,7 +8691,7 @@
         <v>61</v>
       </c>
       <c r="Z66" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>135000</v>
       </c>
       <c r="AA66" s="2">
@@ -8648,7 +8701,7 @@
         <v>60</v>
       </c>
       <c r="AC66" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7811</v>
       </c>
       <c r="AD66" s="1">
@@ -8672,7 +8725,7 @@
       <c r="E67" s="1">
         <v>1</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="10" t="s">
         <v>96</v>
       </c>
       <c r="G67" s="1">
@@ -8688,11 +8741,11 @@
         <v>29250000000</v>
       </c>
       <c r="K67" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>320</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>190</v>
       </c>
       <c r="M67" s="1">
@@ -8703,8 +8756,9 @@
         <f t="shared" si="3"/>
         <v>248</v>
       </c>
-      <c r="O67" s="1">
-        <v>38</v>
+      <c r="O67" s="6">
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="P67" s="2">
         <f t="shared" si="6"/>
@@ -8741,7 +8795,7 @@
         <v>62</v>
       </c>
       <c r="Z67" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>140000</v>
       </c>
       <c r="AA67" s="2">
@@ -8751,7 +8805,7 @@
         <v>61</v>
       </c>
       <c r="AC67" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8094</v>
       </c>
       <c r="AD67" s="1">
@@ -8791,11 +8845,11 @@
         <v>36550000000</v>
       </c>
       <c r="K68" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>330</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>195</v>
       </c>
       <c r="M68" s="1">
@@ -8806,8 +8860,9 @@
         <f t="shared" si="3"/>
         <v>252</v>
       </c>
-      <c r="O68" s="1">
-        <v>38</v>
+      <c r="O68" s="6">
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="P68" s="2">
         <f t="shared" si="6"/>
@@ -8844,7 +8899,7 @@
         <v>63</v>
       </c>
       <c r="Z68" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>145000</v>
       </c>
       <c r="AA68" s="3">
@@ -8854,7 +8909,7 @@
         <v>62</v>
       </c>
       <c r="AC68" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8387</v>
       </c>
       <c r="AD68" s="1">
@@ -8894,11 +8949,11 @@
         <v>45650000000</v>
       </c>
       <c r="K69" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>340</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>200</v>
       </c>
       <c r="M69" s="1">
@@ -8909,8 +8964,9 @@
         <f t="shared" si="3"/>
         <v>256</v>
       </c>
-      <c r="O69" s="1">
-        <v>38</v>
+      <c r="O69" s="6">
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="P69" s="2">
         <f t="shared" si="6"/>
@@ -8947,7 +9003,7 @@
         <v>64</v>
       </c>
       <c r="Z69" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>150000</v>
       </c>
       <c r="AA69" s="2">
@@ -8957,7 +9013,7 @@
         <v>63</v>
       </c>
       <c r="AC69" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>8694</v>
       </c>
       <c r="AD69" s="1">
@@ -8997,23 +9053,24 @@
         <v>91200000000</v>
       </c>
       <c r="K70" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>350</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>205</v>
       </c>
       <c r="M70" s="1">
-        <f t="shared" ref="M70:M77" si="15">Y70*2</f>
+        <f t="shared" ref="M70:M77" si="16">Y70*2</f>
         <v>130</v>
       </c>
       <c r="N70" s="1">
-        <f t="shared" ref="N70:N77" si="16">Y70*4</f>
+        <f t="shared" ref="N70:N77" si="17">Y70*4</f>
         <v>260</v>
       </c>
-      <c r="O70" s="1">
-        <v>38</v>
+      <c r="O70" s="6">
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="P70" s="2">
         <f t="shared" si="6"/>
@@ -9036,11 +9093,11 @@
         <v>0</v>
       </c>
       <c r="V70" s="1">
-        <f t="shared" ref="V70:V77" si="17">X70*10</f>
+        <f t="shared" ref="V70:V77" si="18">X70*10</f>
         <v>650</v>
       </c>
       <c r="W70" s="1">
-        <f t="shared" ref="W70:W77" si="18">X70*10</f>
+        <f t="shared" ref="W70:W77" si="19">X70*10</f>
         <v>650</v>
       </c>
       <c r="X70" s="1">
@@ -9050,7 +9107,7 @@
         <v>65</v>
       </c>
       <c r="Z70" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>155000</v>
       </c>
       <c r="AA70" s="2">
@@ -9060,7 +9117,7 @@
         <v>64</v>
       </c>
       <c r="AC70" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9005</v>
       </c>
       <c r="AD70" s="1">
@@ -9098,27 +9155,28 @@
       <c r="I71" s="5">
         <v>856000000</v>
       </c>
-      <c r="J71" s="13" t="s">
+      <c r="J71" s="12" t="s">
         <v>101</v>
       </c>
       <c r="K71" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>360</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>210</v>
       </c>
       <c r="M71" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>132</v>
       </c>
       <c r="N71" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>264</v>
       </c>
-      <c r="O71" s="1">
-        <v>38</v>
+      <c r="O71" s="6">
+        <f t="shared" si="8"/>
+        <v>11</v>
       </c>
       <c r="P71" s="2">
         <f t="shared" si="6"/>
@@ -9141,13 +9199,13 @@
         <v>0</v>
       </c>
       <c r="V71" s="5">
-        <f t="shared" si="17"/>
-        <v>660</v>
-      </c>
-      <c r="W71" s="5">
         <f t="shared" si="18"/>
         <v>660</v>
       </c>
+      <c r="W71" s="5">
+        <f t="shared" si="19"/>
+        <v>660</v>
+      </c>
       <c r="X71" s="5">
         <v>66</v>
       </c>
@@ -9155,7 +9213,7 @@
         <v>66</v>
       </c>
       <c r="Z71" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>160000</v>
       </c>
       <c r="AA71" s="2">
@@ -9165,7 +9223,7 @@
         <v>65</v>
       </c>
       <c r="AC71" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9318</v>
       </c>
       <c r="AD71" s="5">
@@ -9201,30 +9259,31 @@
       <c r="I72" s="6">
         <v>1000000000</v>
       </c>
-      <c r="J72" s="14" t="s">
+      <c r="J72" s="13" t="s">
         <v>103</v>
       </c>
       <c r="K72" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>370</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>215</v>
       </c>
       <c r="M72" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>134</v>
       </c>
       <c r="N72" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>268</v>
       </c>
-      <c r="O72" s="1">
-        <v>38</v>
+      <c r="O72" s="6">
+        <f t="shared" si="8"/>
+        <v>12</v>
       </c>
       <c r="P72" s="2">
-        <f t="shared" ref="P72:P77" si="19">P71+1</f>
+        <f t="shared" ref="P72:P77" si="20">P71+1</f>
         <v>66</v>
       </c>
       <c r="Q72" s="2">
@@ -9244,13 +9303,13 @@
         <v>0</v>
       </c>
       <c r="V72" s="1">
-        <f t="shared" si="17"/>
-        <v>670</v>
-      </c>
-      <c r="W72" s="1">
         <f t="shared" si="18"/>
         <v>670</v>
       </c>
+      <c r="W72" s="1">
+        <f t="shared" si="19"/>
+        <v>670</v>
+      </c>
       <c r="X72" s="1">
         <v>67</v>
       </c>
@@ -9258,7 +9317,7 @@
         <v>67</v>
       </c>
       <c r="Z72" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>165000</v>
       </c>
       <c r="AA72" s="2">
@@ -9268,7 +9327,7 @@
         <v>66</v>
       </c>
       <c r="AC72" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9635</v>
       </c>
       <c r="AD72" s="1">
@@ -9304,34 +9363,35 @@
       <c r="I73" s="6">
         <v>1200000000</v>
       </c>
-      <c r="J73" s="14" t="s">
+      <c r="J73" s="13" t="s">
         <v>105</v>
       </c>
       <c r="K73" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>380</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>220</v>
       </c>
       <c r="M73" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>136</v>
       </c>
       <c r="N73" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>272</v>
       </c>
-      <c r="O73" s="1">
-        <v>38</v>
+      <c r="O73" s="6">
+        <f t="shared" si="8"/>
+        <v>12</v>
       </c>
       <c r="P73" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>67</v>
       </c>
       <c r="Q73" s="2">
-        <f t="shared" ref="Q73:Q77" si="20">Q72+1</f>
+        <f t="shared" ref="Q73:Q77" si="21">Q72+1</f>
         <v>68</v>
       </c>
       <c r="R73" s="1">
@@ -9347,13 +9407,13 @@
         <v>0</v>
       </c>
       <c r="V73" s="1">
-        <f t="shared" si="17"/>
-        <v>680</v>
-      </c>
-      <c r="W73" s="1">
         <f t="shared" si="18"/>
         <v>680</v>
       </c>
+      <c r="W73" s="1">
+        <f t="shared" si="19"/>
+        <v>680</v>
+      </c>
       <c r="X73" s="1">
         <v>68</v>
       </c>
@@ -9361,7 +9421,7 @@
         <v>68</v>
       </c>
       <c r="Z73" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>170000</v>
       </c>
       <c r="AA73" s="2">
@@ -9371,7 +9431,7 @@
         <v>67</v>
       </c>
       <c r="AC73" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9966</v>
       </c>
       <c r="AD73" s="1">
@@ -9407,34 +9467,35 @@
       <c r="I74" s="6">
         <v>1440000000</v>
       </c>
-      <c r="J74" s="14" t="s">
+      <c r="J74" s="13" t="s">
         <v>107</v>
       </c>
       <c r="K74" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>390</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>225</v>
       </c>
       <c r="M74" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>138</v>
       </c>
       <c r="N74" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>276</v>
       </c>
-      <c r="O74" s="1">
-        <v>38</v>
+      <c r="O74" s="6">
+        <f t="shared" si="8"/>
+        <v>12</v>
       </c>
       <c r="P74" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>68</v>
       </c>
       <c r="Q74" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>69</v>
       </c>
       <c r="R74" s="1">
@@ -9450,13 +9511,13 @@
         <v>0</v>
       </c>
       <c r="V74" s="1">
-        <f t="shared" si="17"/>
-        <v>690</v>
-      </c>
-      <c r="W74" s="1">
         <f t="shared" si="18"/>
         <v>690</v>
       </c>
+      <c r="W74" s="1">
+        <f t="shared" si="19"/>
+        <v>690</v>
+      </c>
       <c r="X74" s="1">
         <v>69</v>
       </c>
@@ -9464,7 +9525,7 @@
         <v>69</v>
       </c>
       <c r="Z74" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>175000</v>
       </c>
       <c r="AA74" s="3">
@@ -9474,7 +9535,7 @@
         <v>68</v>
       </c>
       <c r="AC74" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10303</v>
       </c>
       <c r="AD74" s="1">
@@ -9510,34 +9571,35 @@
       <c r="I75" s="6">
         <v>1720000000</v>
       </c>
-      <c r="J75" s="14" t="s">
+      <c r="J75" s="13" t="s">
         <v>109</v>
       </c>
       <c r="K75" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>400</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>230</v>
       </c>
       <c r="M75" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>140</v>
       </c>
       <c r="N75" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>280</v>
       </c>
-      <c r="O75" s="1">
-        <v>38</v>
+      <c r="O75" s="6">
+        <f t="shared" si="8"/>
+        <v>12</v>
       </c>
       <c r="P75" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>69</v>
       </c>
       <c r="Q75" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>70</v>
       </c>
       <c r="R75" s="1">
@@ -9553,13 +9615,13 @@
         <v>0</v>
       </c>
       <c r="V75" s="1">
-        <f t="shared" si="17"/>
-        <v>700</v>
-      </c>
-      <c r="W75" s="1">
         <f t="shared" si="18"/>
         <v>700</v>
       </c>
+      <c r="W75" s="1">
+        <f t="shared" si="19"/>
+        <v>700</v>
+      </c>
       <c r="X75" s="1">
         <v>70</v>
       </c>
@@ -9567,7 +9629,7 @@
         <v>70</v>
       </c>
       <c r="Z75" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>180000</v>
       </c>
       <c r="AA75" s="2">
@@ -9577,7 +9639,7 @@
         <v>69</v>
       </c>
       <c r="AC75" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>10650</v>
       </c>
       <c r="AD75" s="1">
@@ -9601,7 +9663,7 @@
       <c r="E76" s="1">
         <v>1</v>
       </c>
-      <c r="F76" s="10" t="s">
+      <c r="F76" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G76" s="1">
@@ -9613,34 +9675,35 @@
       <c r="I76" s="6">
         <v>2060000000</v>
       </c>
-      <c r="J76" s="14" t="s">
+      <c r="J76" s="13" t="s">
         <v>111</v>
       </c>
       <c r="K76" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>410</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>235</v>
       </c>
       <c r="M76" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>142</v>
       </c>
       <c r="N76" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>284</v>
       </c>
-      <c r="O76" s="1">
-        <v>38</v>
+      <c r="O76" s="6">
+        <f>O70+1</f>
+        <v>12</v>
       </c>
       <c r="P76" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>70</v>
       </c>
       <c r="Q76" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>71</v>
       </c>
       <c r="R76" s="1">
@@ -9656,13 +9719,13 @@
         <v>0</v>
       </c>
       <c r="V76" s="1">
-        <f t="shared" si="17"/>
-        <v>710</v>
-      </c>
-      <c r="W76" s="1">
         <f t="shared" si="18"/>
         <v>710</v>
       </c>
+      <c r="W76" s="1">
+        <f t="shared" si="19"/>
+        <v>710</v>
+      </c>
       <c r="X76" s="1">
         <v>71</v>
       </c>
@@ -9670,7 +9733,7 @@
         <v>71</v>
       </c>
       <c r="Z76" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>185000</v>
       </c>
       <c r="AA76" s="2">
@@ -9716,34 +9779,35 @@
       <c r="I77" s="5">
         <v>2470000000</v>
       </c>
-      <c r="J77" s="13" t="s">
+      <c r="J77" s="12" t="s">
         <v>113</v>
       </c>
       <c r="K77" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>420</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>240</v>
       </c>
       <c r="M77" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>144</v>
       </c>
       <c r="N77" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>288</v>
       </c>
-      <c r="O77" s="1">
-        <v>38</v>
+      <c r="O77" s="6">
+        <f>O71+1</f>
+        <v>12</v>
       </c>
       <c r="P77" s="2">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>71</v>
       </c>
       <c r="Q77" s="2">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>72</v>
       </c>
       <c r="R77" s="1">
@@ -9759,13 +9823,13 @@
         <v>0</v>
       </c>
       <c r="V77" s="1">
-        <f t="shared" si="17"/>
-        <v>720</v>
-      </c>
-      <c r="W77" s="1">
         <f t="shared" si="18"/>
         <v>720</v>
       </c>
+      <c r="W77" s="1">
+        <f t="shared" si="19"/>
+        <v>720</v>
+      </c>
       <c r="X77" s="1">
         <v>72</v>
       </c>
@@ -9773,7 +9837,7 @@
         <v>72</v>
       </c>
       <c r="Z77" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>190000</v>
       </c>
       <c r="AA77" s="2">
@@ -9958,7 +10022,7 @@
     <col min="12" max="12" width="10.3333333333333" style="2" customWidth="1"/>
     <col min="13" max="13" width="9.91666666666667" style="2" customWidth="1"/>
     <col min="14" max="14" width="8.75" style="2" customWidth="1"/>
-    <col min="15" max="15" width="11.0833333333333" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.75" style="2" customWidth="1"/>
     <col min="16" max="16" width="10.75" style="2" customWidth="1"/>
     <col min="17" max="17" width="11.3333333333333" style="2" customWidth="1"/>
     <col min="18" max="19" width="8.75" style="2" customWidth="1"/>
@@ -10228,13 +10292,13 @@
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K6" s="1">
@@ -10250,7 +10314,7 @@
         <v>300</v>
       </c>
       <c r="O6" s="1">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="P6" s="2">
         <v>72</v>
@@ -10295,13 +10359,13 @@
       <c r="G7" s="1">
         <v>2</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="13" t="s">
         <v>118</v>
       </c>
       <c r="K7" s="2">
@@ -10321,7 +10385,7 @@
         <v>310</v>
       </c>
       <c r="O7" s="1">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="P7" s="2">
         <f t="shared" ref="P7:P70" si="6">P6+1</f>
@@ -10368,13 +10432,13 @@
       <c r="G8" s="1">
         <v>3</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="13" t="s">
         <v>121</v>
       </c>
       <c r="K8" s="2">
@@ -10394,7 +10458,7 @@
         <v>320</v>
       </c>
       <c r="O8" s="1">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="P8" s="2">
         <f t="shared" si="6"/>
@@ -10441,13 +10505,13 @@
       <c r="G9" s="1">
         <v>4</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="13" t="s">
         <v>124</v>
       </c>
       <c r="K9" s="2">
@@ -10466,9 +10530,8 @@
         <f t="shared" si="5"/>
         <v>330</v>
       </c>
-      <c r="O9" s="2">
-        <f t="shared" ref="O9:O72" si="8">O6+1</f>
-        <v>40</v>
+      <c r="O9" s="1">
+        <v>13</v>
       </c>
       <c r="P9" s="2">
         <f t="shared" si="6"/>
@@ -10515,13 +10578,13 @@
       <c r="G10" s="1">
         <v>5</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="13" t="s">
         <v>127</v>
       </c>
       <c r="K10" s="2">
@@ -10540,9 +10603,8 @@
         <f t="shared" si="5"/>
         <v>340</v>
       </c>
-      <c r="O10" s="2">
-        <f t="shared" si="8"/>
-        <v>40</v>
+      <c r="O10" s="1">
+        <v>13</v>
       </c>
       <c r="P10" s="2">
         <f t="shared" si="6"/>
@@ -10589,13 +10651,13 @@
       <c r="G11" s="5">
         <v>6</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="13" t="s">
         <v>130</v>
       </c>
       <c r="K11" s="2">
@@ -10614,9 +10676,8 @@
         <f t="shared" si="5"/>
         <v>350</v>
       </c>
-      <c r="O11" s="2">
-        <f t="shared" si="8"/>
-        <v>40</v>
+      <c r="O11" s="1">
+        <v>13</v>
       </c>
       <c r="P11" s="2">
         <f t="shared" si="6"/>
@@ -10663,13 +10724,13 @@
       <c r="G12" s="6">
         <v>7</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="J12" s="13" t="s">
         <v>133</v>
       </c>
       <c r="K12" s="2">
@@ -10688,9 +10749,9 @@
         <f t="shared" si="5"/>
         <v>360</v>
       </c>
-      <c r="O12" s="2">
-        <f t="shared" si="8"/>
-        <v>41</v>
+      <c r="O12" s="6">
+        <f t="shared" ref="O12:O75" si="8">O6+1</f>
+        <v>14</v>
       </c>
       <c r="P12" s="2">
         <f t="shared" si="6"/>
@@ -10731,19 +10792,19 @@
       <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>42</v>
       </c>
       <c r="G13" s="6">
         <v>8</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="13" t="s">
         <v>136</v>
       </c>
       <c r="K13" s="2">
@@ -10762,9 +10823,9 @@
         <f t="shared" si="5"/>
         <v>370</v>
       </c>
-      <c r="O13" s="2">
+      <c r="O13" s="6">
         <f t="shared" si="8"/>
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="P13" s="2">
         <f t="shared" si="6"/>
@@ -10811,13 +10872,13 @@
       <c r="G14" s="6">
         <v>9</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="J14" s="15" t="s">
+      <c r="J14" s="13" t="s">
         <v>139</v>
       </c>
       <c r="K14" s="2">
@@ -10836,9 +10897,9 @@
         <f t="shared" si="5"/>
         <v>380</v>
       </c>
-      <c r="O14" s="2">
+      <c r="O14" s="6">
         <f t="shared" si="8"/>
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="P14" s="2">
         <f t="shared" si="6"/>
@@ -10879,19 +10940,19 @@
       <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="9" t="s">
         <v>44</v>
       </c>
       <c r="G15" s="6">
         <v>10</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="13" t="s">
         <v>142</v>
       </c>
       <c r="K15" s="2">
@@ -10910,9 +10971,9 @@
         <f t="shared" si="5"/>
         <v>390</v>
       </c>
-      <c r="O15" s="2">
+      <c r="O15" s="6">
         <f t="shared" si="8"/>
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="P15" s="2">
         <f t="shared" si="6"/>
@@ -10959,13 +11020,13 @@
       <c r="G16" s="6">
         <v>11</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="13" t="s">
         <v>145</v>
       </c>
       <c r="K16" s="2">
@@ -10984,9 +11045,9 @@
         <f t="shared" si="5"/>
         <v>400</v>
       </c>
-      <c r="O16" s="2">
+      <c r="O16" s="6">
         <f t="shared" si="8"/>
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="P16" s="2">
         <f t="shared" si="6"/>
@@ -11033,13 +11094,13 @@
       <c r="G17" s="5">
         <v>12</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="13" t="s">
         <v>148</v>
       </c>
       <c r="K17" s="2">
@@ -11058,9 +11119,9 @@
         <f t="shared" si="5"/>
         <v>410</v>
       </c>
-      <c r="O17" s="2">
+      <c r="O17" s="6">
         <f t="shared" si="8"/>
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="P17" s="2">
         <f t="shared" si="6"/>
@@ -11101,19 +11162,19 @@
       <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="9" t="s">
         <v>47</v>
       </c>
       <c r="G18" s="6">
         <v>13</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="13" t="s">
         <v>151</v>
       </c>
       <c r="K18" s="2">
@@ -11132,9 +11193,9 @@
         <f t="shared" si="5"/>
         <v>420</v>
       </c>
-      <c r="O18" s="2">
+      <c r="O18" s="6">
         <f t="shared" si="8"/>
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="P18" s="2">
         <f t="shared" si="6"/>
@@ -11181,13 +11242,13 @@
       <c r="G19" s="6">
         <v>14</v>
       </c>
-      <c r="H19" s="16" t="s">
+      <c r="H19" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="13" t="s">
         <v>153</v>
       </c>
       <c r="K19" s="2">
@@ -11206,9 +11267,9 @@
         <f t="shared" si="5"/>
         <v>430</v>
       </c>
-      <c r="O19" s="2">
+      <c r="O19" s="6">
         <f t="shared" si="8"/>
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="P19" s="2">
         <f t="shared" si="6"/>
@@ -11255,13 +11316,13 @@
       <c r="G20" s="6">
         <v>15</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="H20" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="I20" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="13" t="s">
         <v>156</v>
       </c>
       <c r="K20" s="2">
@@ -11280,9 +11341,9 @@
         <f t="shared" si="5"/>
         <v>440</v>
       </c>
-      <c r="O20" s="2">
+      <c r="O20" s="6">
         <f t="shared" si="8"/>
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="P20" s="2">
         <f t="shared" si="6"/>
@@ -11329,13 +11390,13 @@
       <c r="G21" s="6">
         <v>16</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H21" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="I21" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="13" t="s">
         <v>159</v>
       </c>
       <c r="K21" s="2">
@@ -11354,9 +11415,9 @@
         <f t="shared" si="5"/>
         <v>450</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="6">
         <f t="shared" si="8"/>
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="P21" s="2">
         <f t="shared" si="6"/>
@@ -11403,13 +11464,13 @@
       <c r="G22" s="6">
         <v>17</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="I22" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="J22" s="13" t="s">
         <v>162</v>
       </c>
       <c r="K22" s="2">
@@ -11428,9 +11489,9 @@
         <f t="shared" si="5"/>
         <v>460</v>
       </c>
-      <c r="O22" s="2">
+      <c r="O22" s="6">
         <f t="shared" si="8"/>
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="P22" s="2">
         <f t="shared" si="6"/>
@@ -11477,13 +11538,13 @@
       <c r="G23" s="5">
         <v>18</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="I23" s="15" t="s">
+      <c r="I23" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="J23" s="15" t="s">
+      <c r="J23" s="13" t="s">
         <v>165</v>
       </c>
       <c r="K23" s="2">
@@ -11502,9 +11563,9 @@
         <f t="shared" si="5"/>
         <v>470</v>
       </c>
-      <c r="O23" s="2">
+      <c r="O23" s="6">
         <f t="shared" si="8"/>
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="P23" s="2">
         <f t="shared" si="6"/>
@@ -11551,13 +11612,13 @@
       <c r="G24" s="6">
         <v>19</v>
       </c>
-      <c r="H24" s="16" t="s">
+      <c r="H24" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="I24" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="J24" s="15" t="s">
+      <c r="J24" s="13" t="s">
         <v>168</v>
       </c>
       <c r="K24" s="2">
@@ -11576,9 +11637,9 @@
         <f t="shared" si="5"/>
         <v>480</v>
       </c>
-      <c r="O24" s="2">
+      <c r="O24" s="6">
         <f t="shared" si="8"/>
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="P24" s="2">
         <f t="shared" si="6"/>
@@ -11625,13 +11686,13 @@
       <c r="G25" s="6">
         <v>20</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="H25" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="I25" s="15" t="s">
+      <c r="I25" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="J25" s="13" t="s">
         <v>171</v>
       </c>
       <c r="K25" s="2">
@@ -11650,9 +11711,9 @@
         <f t="shared" si="5"/>
         <v>490</v>
       </c>
-      <c r="O25" s="2">
+      <c r="O25" s="6">
         <f t="shared" si="8"/>
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="P25" s="2">
         <f t="shared" si="6"/>
@@ -11699,13 +11760,13 @@
       <c r="G26" s="6">
         <v>21</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="I26" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="J26" s="15" t="s">
+      <c r="J26" s="13" t="s">
         <v>173</v>
       </c>
       <c r="K26" s="2">
@@ -11724,9 +11785,9 @@
         <f t="shared" si="5"/>
         <v>500</v>
       </c>
-      <c r="O26" s="2">
+      <c r="O26" s="6">
         <f t="shared" si="8"/>
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="P26" s="2">
         <f t="shared" si="6"/>
@@ -11773,13 +11834,13 @@
       <c r="G27" s="6">
         <v>22</v>
       </c>
-      <c r="H27" s="16" t="s">
+      <c r="H27" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="I27" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="J27" s="13" t="s">
         <v>176</v>
       </c>
       <c r="K27" s="2">
@@ -11798,9 +11859,9 @@
         <f t="shared" si="5"/>
         <v>510</v>
       </c>
-      <c r="O27" s="2">
+      <c r="O27" s="6">
         <f t="shared" si="8"/>
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="P27" s="2">
         <f t="shared" si="6"/>
@@ -11841,19 +11902,19 @@
       <c r="E28" s="1">
         <v>2</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="9" t="s">
         <v>57</v>
       </c>
       <c r="G28" s="6">
         <v>23</v>
       </c>
-      <c r="H28" s="16" t="s">
+      <c r="H28" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="J28" s="13" t="s">
         <v>179</v>
       </c>
       <c r="K28" s="2">
@@ -11872,9 +11933,9 @@
         <f t="shared" si="5"/>
         <v>520</v>
       </c>
-      <c r="O28" s="2">
+      <c r="O28" s="6">
         <f t="shared" si="8"/>
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="P28" s="2">
         <f t="shared" si="6"/>
@@ -11921,13 +11982,13 @@
       <c r="G29" s="5">
         <v>24</v>
       </c>
-      <c r="H29" s="16" t="s">
+      <c r="H29" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="I29" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="J29" s="13" t="s">
         <v>182</v>
       </c>
       <c r="K29" s="2">
@@ -11946,9 +12007,9 @@
         <f t="shared" si="5"/>
         <v>530</v>
       </c>
-      <c r="O29" s="2">
+      <c r="O29" s="6">
         <f t="shared" si="8"/>
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="P29" s="2">
         <f t="shared" si="6"/>
@@ -11995,13 +12056,13 @@
       <c r="G30" s="6">
         <v>25</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="H30" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="I30" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="J30" s="13" t="s">
         <v>185</v>
       </c>
       <c r="K30" s="2">
@@ -12020,9 +12081,9 @@
         <f t="shared" si="5"/>
         <v>540</v>
       </c>
-      <c r="O30" s="2">
+      <c r="O30" s="6">
         <f t="shared" si="8"/>
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="P30" s="2">
         <f t="shared" si="6"/>
@@ -12069,13 +12130,13 @@
       <c r="G31" s="6">
         <v>26</v>
       </c>
-      <c r="H31" s="16" t="s">
+      <c r="H31" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="I31" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="J31" s="15" t="s">
+      <c r="J31" s="13" t="s">
         <v>188</v>
       </c>
       <c r="K31" s="2">
@@ -12094,9 +12155,9 @@
         <f t="shared" si="5"/>
         <v>550</v>
       </c>
-      <c r="O31" s="2">
+      <c r="O31" s="6">
         <f t="shared" si="8"/>
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="P31" s="2">
         <f t="shared" si="6"/>
@@ -12137,19 +12198,19 @@
       <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="10" t="s">
         <v>61</v>
       </c>
       <c r="G32" s="6">
         <v>27</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="H32" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="J32" s="13" t="s">
         <v>191</v>
       </c>
       <c r="K32" s="2">
@@ -12168,9 +12229,9 @@
         <f t="shared" si="5"/>
         <v>560</v>
       </c>
-      <c r="O32" s="2">
+      <c r="O32" s="6">
         <f t="shared" si="8"/>
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="P32" s="2">
         <f t="shared" si="6"/>
@@ -12217,13 +12278,13 @@
       <c r="G33" s="6">
         <v>28</v>
       </c>
-      <c r="H33" s="16" t="s">
+      <c r="H33" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="I33" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="J33" s="13" t="s">
         <v>194</v>
       </c>
       <c r="K33" s="2">
@@ -12242,9 +12303,9 @@
         <f t="shared" si="5"/>
         <v>570</v>
       </c>
-      <c r="O33" s="2">
+      <c r="O33" s="6">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="P33" s="2">
         <f t="shared" si="6"/>
@@ -12285,19 +12346,19 @@
       <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="10" t="s">
         <v>63</v>
       </c>
       <c r="G34" s="6">
         <v>29</v>
       </c>
-      <c r="H34" s="16" t="s">
+      <c r="H34" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="I34" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="J34" s="15" t="s">
+      <c r="J34" s="13" t="s">
         <v>197</v>
       </c>
       <c r="K34" s="2">
@@ -12316,9 +12377,9 @@
         <f t="shared" si="5"/>
         <v>580</v>
       </c>
-      <c r="O34" s="2">
+      <c r="O34" s="6">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="P34" s="2">
         <f t="shared" si="6"/>
@@ -12365,13 +12426,13 @@
       <c r="G35" s="5">
         <v>30</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="H35" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="I35" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="J35" s="13" t="s">
         <v>200</v>
       </c>
       <c r="K35" s="2">
@@ -12390,9 +12451,9 @@
         <f t="shared" si="5"/>
         <v>590</v>
       </c>
-      <c r="O35" s="2">
+      <c r="O35" s="6">
         <f t="shared" si="8"/>
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="P35" s="2">
         <f t="shared" si="6"/>
@@ -12439,13 +12500,13 @@
       <c r="G36" s="6">
         <v>31</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="H36" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="I36" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="J36" s="15" t="s">
+      <c r="J36" s="13" t="s">
         <v>203</v>
       </c>
       <c r="K36" s="2">
@@ -12464,9 +12525,9 @@
         <f t="shared" si="5"/>
         <v>600</v>
       </c>
-      <c r="O36" s="2">
+      <c r="O36" s="6">
         <f t="shared" si="8"/>
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="P36" s="2">
         <f t="shared" si="6"/>
@@ -12513,13 +12574,13 @@
       <c r="G37" s="6">
         <v>32</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="H37" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="I37" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="J37" s="15" t="s">
+      <c r="J37" s="13" t="s">
         <v>206</v>
       </c>
       <c r="K37" s="2">
@@ -12538,9 +12599,9 @@
         <f t="shared" si="5"/>
         <v>610</v>
       </c>
-      <c r="O37" s="2">
+      <c r="O37" s="6">
         <f t="shared" si="8"/>
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="P37" s="2">
         <f t="shared" si="6"/>
@@ -12587,13 +12648,13 @@
       <c r="G38" s="6">
         <v>33</v>
       </c>
-      <c r="H38" s="16" t="s">
+      <c r="H38" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="I38" s="15" t="s">
+      <c r="I38" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="J38" s="15" t="s">
+      <c r="J38" s="13" t="s">
         <v>209</v>
       </c>
       <c r="K38" s="2">
@@ -12612,9 +12673,9 @@
         <f t="shared" si="5"/>
         <v>620</v>
       </c>
-      <c r="O38" s="2">
+      <c r="O38" s="6">
         <f t="shared" si="8"/>
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="P38" s="2">
         <f t="shared" si="6"/>
@@ -12661,13 +12722,13 @@
       <c r="G39" s="6">
         <v>34</v>
       </c>
-      <c r="H39" s="16" t="s">
+      <c r="H39" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="I39" s="13" t="s">
         <v>211</v>
       </c>
-      <c r="J39" s="15" t="s">
+      <c r="J39" s="13" t="s">
         <v>212</v>
       </c>
       <c r="K39" s="2">
@@ -12686,9 +12747,9 @@
         <f t="shared" si="5"/>
         <v>630</v>
       </c>
-      <c r="O39" s="2">
+      <c r="O39" s="6">
         <f t="shared" si="8"/>
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="P39" s="2">
         <f t="shared" si="6"/>
@@ -12735,13 +12796,13 @@
       <c r="G40" s="6">
         <v>35</v>
       </c>
-      <c r="H40" s="16" t="s">
+      <c r="H40" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="I40" s="15" t="s">
+      <c r="I40" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="J40" s="15" t="s">
+      <c r="J40" s="13" t="s">
         <v>215</v>
       </c>
       <c r="K40" s="2">
@@ -12760,9 +12821,9 @@
         <f t="shared" si="5"/>
         <v>640</v>
       </c>
-      <c r="O40" s="2">
+      <c r="O40" s="6">
         <f t="shared" si="8"/>
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="P40" s="2">
         <f t="shared" si="6"/>
@@ -12810,13 +12871,13 @@
       <c r="G41" s="5">
         <v>36</v>
       </c>
-      <c r="H41" s="16" t="s">
+      <c r="H41" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="I41" s="15" t="s">
+      <c r="I41" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="J41" s="15" t="s">
+      <c r="J41" s="13" t="s">
         <v>218</v>
       </c>
       <c r="K41" s="2">
@@ -12835,9 +12896,9 @@
         <f t="shared" si="5"/>
         <v>650</v>
       </c>
-      <c r="O41" s="2">
+      <c r="O41" s="6">
         <f t="shared" si="8"/>
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="P41" s="2">
         <f t="shared" si="6"/>
@@ -12879,19 +12940,19 @@
       <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="9" t="s">
         <v>71</v>
       </c>
       <c r="G42" s="1">
         <v>37</v>
       </c>
-      <c r="H42" s="16" t="s">
+      <c r="H42" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="I42" s="15" t="s">
+      <c r="I42" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="J42" s="15" t="s">
+      <c r="J42" s="13" t="s">
         <v>221</v>
       </c>
       <c r="K42" s="2">
@@ -12910,9 +12971,9 @@
         <f t="shared" si="5"/>
         <v>660</v>
       </c>
-      <c r="O42" s="2">
+      <c r="O42" s="6">
         <f t="shared" si="8"/>
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="P42" s="2">
         <f t="shared" si="6"/>
@@ -12960,13 +13021,13 @@
       <c r="G43" s="1">
         <v>38</v>
       </c>
-      <c r="H43" s="16" t="s">
+      <c r="H43" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="I43" s="15" t="s">
+      <c r="I43" s="13" t="s">
         <v>223</v>
       </c>
-      <c r="J43" s="15" t="s">
+      <c r="J43" s="13" t="s">
         <v>224</v>
       </c>
       <c r="K43" s="2">
@@ -12985,9 +13046,9 @@
         <f t="shared" si="5"/>
         <v>670</v>
       </c>
-      <c r="O43" s="2">
+      <c r="O43" s="6">
         <f t="shared" si="8"/>
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="P43" s="2">
         <f t="shared" si="6"/>
@@ -13029,19 +13090,19 @@
       <c r="E44" s="1">
         <v>2</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="G44" s="1">
         <v>39</v>
       </c>
-      <c r="H44" s="16" t="s">
+      <c r="H44" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="I44" s="15" t="s">
+      <c r="I44" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="J44" s="15" t="s">
+      <c r="J44" s="13" t="s">
         <v>227</v>
       </c>
       <c r="K44" s="2">
@@ -13060,9 +13121,9 @@
         <f t="shared" si="5"/>
         <v>680</v>
       </c>
-      <c r="O44" s="2">
+      <c r="O44" s="6">
         <f t="shared" si="8"/>
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="P44" s="2">
         <f t="shared" si="6"/>
@@ -13110,13 +13171,13 @@
       <c r="G45" s="1">
         <v>40</v>
       </c>
-      <c r="H45" s="16" t="s">
+      <c r="H45" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="I45" s="15" t="s">
+      <c r="I45" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="J45" s="15" t="s">
+      <c r="J45" s="13" t="s">
         <v>230</v>
       </c>
       <c r="K45" s="2">
@@ -13135,9 +13196,9 @@
         <f t="shared" si="5"/>
         <v>690</v>
       </c>
-      <c r="O45" s="2">
+      <c r="O45" s="6">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="P45" s="2">
         <f t="shared" si="6"/>
@@ -13179,19 +13240,19 @@
       <c r="E46" s="1">
         <v>2</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="10" t="s">
         <v>75</v>
       </c>
       <c r="G46" s="1">
         <v>41</v>
       </c>
-      <c r="H46" s="16" t="s">
+      <c r="H46" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="I46" s="15" t="s">
+      <c r="I46" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="J46" s="15" t="s">
+      <c r="J46" s="13" t="s">
         <v>233</v>
       </c>
       <c r="K46" s="2">
@@ -13210,9 +13271,9 @@
         <f t="shared" si="5"/>
         <v>700</v>
       </c>
-      <c r="O46" s="2">
+      <c r="O46" s="6">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="P46" s="2">
         <f t="shared" si="6"/>
@@ -13253,19 +13314,19 @@
       <c r="E47" s="1">
         <v>2</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F47" s="11" t="s">
         <v>76</v>
       </c>
       <c r="G47" s="5">
         <v>42</v>
       </c>
-      <c r="H47" s="16" t="s">
+      <c r="H47" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="I47" s="15" t="s">
+      <c r="I47" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="J47" s="15" t="s">
+      <c r="J47" s="13" t="s">
         <v>236</v>
       </c>
       <c r="K47" s="2">
@@ -13284,9 +13345,9 @@
         <f t="shared" si="5"/>
         <v>710</v>
       </c>
-      <c r="O47" s="2">
+      <c r="O47" s="6">
         <f t="shared" si="8"/>
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="P47" s="2">
         <f t="shared" si="6"/>
@@ -13333,13 +13394,13 @@
       <c r="G48" s="1">
         <v>43</v>
       </c>
-      <c r="H48" s="16" t="s">
+      <c r="H48" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="I48" s="15" t="s">
+      <c r="I48" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="J48" s="15" t="s">
+      <c r="J48" s="13" t="s">
         <v>239</v>
       </c>
       <c r="K48" s="2">
@@ -13358,9 +13419,9 @@
         <f t="shared" si="5"/>
         <v>720</v>
       </c>
-      <c r="O48" s="2">
+      <c r="O48" s="6">
         <f t="shared" si="8"/>
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="P48" s="2">
         <f t="shared" si="6"/>
@@ -13407,13 +13468,13 @@
       <c r="G49" s="1">
         <v>44</v>
       </c>
-      <c r="H49" s="16" t="s">
+      <c r="H49" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="I49" s="15" t="s">
+      <c r="I49" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="J49" s="15" t="s">
+      <c r="J49" s="13" t="s">
         <v>242</v>
       </c>
       <c r="K49" s="2">
@@ -13432,9 +13493,9 @@
         <f t="shared" si="5"/>
         <v>730</v>
       </c>
-      <c r="O49" s="2">
+      <c r="O49" s="6">
         <f t="shared" si="8"/>
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="P49" s="2">
         <f t="shared" si="6"/>
@@ -13481,13 +13542,13 @@
       <c r="G50" s="1">
         <v>45</v>
       </c>
-      <c r="H50" s="16" t="s">
+      <c r="H50" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="I50" s="15" t="s">
+      <c r="I50" s="13" t="s">
         <v>244</v>
       </c>
-      <c r="J50" s="15" t="s">
+      <c r="J50" s="13" t="s">
         <v>245</v>
       </c>
       <c r="K50" s="2">
@@ -13506,9 +13567,9 @@
         <f t="shared" si="5"/>
         <v>740</v>
       </c>
-      <c r="O50" s="2">
+      <c r="O50" s="6">
         <f t="shared" si="8"/>
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="P50" s="2">
         <f t="shared" si="6"/>
@@ -13549,19 +13610,19 @@
       <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="10" t="s">
         <v>80</v>
       </c>
       <c r="G51" s="1">
         <v>46</v>
       </c>
-      <c r="H51" s="16" t="s">
+      <c r="H51" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="I51" s="15" t="s">
+      <c r="I51" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="J51" s="15" t="s">
+      <c r="J51" s="13" t="s">
         <v>248</v>
       </c>
       <c r="K51" s="2">
@@ -13580,9 +13641,9 @@
         <f t="shared" si="5"/>
         <v>750</v>
       </c>
-      <c r="O51" s="2">
+      <c r="O51" s="6">
         <f t="shared" si="8"/>
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="P51" s="2">
         <f t="shared" si="6"/>
@@ -13629,13 +13690,13 @@
       <c r="G52" s="1">
         <v>47</v>
       </c>
-      <c r="H52" s="16" t="s">
+      <c r="H52" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="I52" s="15" t="s">
+      <c r="I52" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="J52" s="15" t="s">
+      <c r="J52" s="13" t="s">
         <v>250</v>
       </c>
       <c r="K52" s="2">
@@ -13654,9 +13715,9 @@
         <f t="shared" si="5"/>
         <v>760</v>
       </c>
-      <c r="O52" s="2">
+      <c r="O52" s="6">
         <f t="shared" si="8"/>
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="P52" s="2">
         <f t="shared" si="6"/>
@@ -13703,13 +13764,13 @@
       <c r="G53" s="5">
         <v>48</v>
       </c>
-      <c r="H53" s="16" t="s">
+      <c r="H53" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="I53" s="15" t="s">
+      <c r="I53" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="J53" s="15" t="s">
+      <c r="J53" s="13" t="s">
         <v>253</v>
       </c>
       <c r="K53" s="2">
@@ -13728,9 +13789,9 @@
         <f t="shared" si="5"/>
         <v>770</v>
       </c>
-      <c r="O53" s="2">
+      <c r="O53" s="6">
         <f t="shared" si="8"/>
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="P53" s="2">
         <f t="shared" si="6"/>
@@ -13777,13 +13838,13 @@
       <c r="G54" s="1">
         <v>49</v>
       </c>
-      <c r="H54" s="16" t="s">
+      <c r="H54" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="I54" s="15" t="s">
+      <c r="I54" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="J54" s="15" t="s">
+      <c r="J54" s="13" t="s">
         <v>256</v>
       </c>
       <c r="K54" s="2">
@@ -13802,9 +13863,9 @@
         <f t="shared" si="5"/>
         <v>780</v>
       </c>
-      <c r="O54" s="2">
+      <c r="O54" s="6">
         <f t="shared" si="8"/>
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="P54" s="2">
         <f t="shared" si="6"/>
@@ -13851,13 +13912,13 @@
       <c r="G55" s="1">
         <v>50</v>
       </c>
-      <c r="H55" s="16" t="s">
+      <c r="H55" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="I55" s="15" t="s">
+      <c r="I55" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="J55" s="15" t="s">
+      <c r="J55" s="13" t="s">
         <v>259</v>
       </c>
       <c r="K55" s="2">
@@ -13876,9 +13937,9 @@
         <f t="shared" si="5"/>
         <v>790</v>
       </c>
-      <c r="O55" s="2">
+      <c r="O55" s="6">
         <f t="shared" si="8"/>
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="P55" s="2">
         <f t="shared" si="6"/>
@@ -13925,13 +13986,13 @@
       <c r="G56" s="1">
         <v>51</v>
       </c>
-      <c r="H56" s="16" t="s">
+      <c r="H56" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="I56" s="15" t="s">
+      <c r="I56" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="J56" s="15" t="s">
+      <c r="J56" s="13" t="s">
         <v>262</v>
       </c>
       <c r="K56" s="2">
@@ -13950,9 +14011,9 @@
         <f t="shared" si="5"/>
         <v>800</v>
       </c>
-      <c r="O56" s="2">
+      <c r="O56" s="6">
         <f t="shared" si="8"/>
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="P56" s="2">
         <f t="shared" si="6"/>
@@ -13999,13 +14060,13 @@
       <c r="G57" s="1">
         <v>52</v>
       </c>
-      <c r="H57" s="16" t="s">
+      <c r="H57" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="I57" s="15" t="s">
+      <c r="I57" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="J57" s="15" t="s">
+      <c r="J57" s="13" t="s">
         <v>265</v>
       </c>
       <c r="K57" s="2">
@@ -14024,9 +14085,9 @@
         <f t="shared" si="5"/>
         <v>810</v>
       </c>
-      <c r="O57" s="2">
+      <c r="O57" s="6">
         <f t="shared" si="8"/>
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="P57" s="2">
         <f t="shared" si="6"/>
@@ -14073,13 +14134,13 @@
       <c r="G58" s="1">
         <v>53</v>
       </c>
-      <c r="H58" s="16" t="s">
+      <c r="H58" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="I58" s="15" t="s">
+      <c r="I58" s="13" t="s">
         <v>267</v>
       </c>
-      <c r="J58" s="15" t="s">
+      <c r="J58" s="13" t="s">
         <v>268</v>
       </c>
       <c r="K58" s="2">
@@ -14098,9 +14159,9 @@
         <f t="shared" si="5"/>
         <v>820</v>
       </c>
-      <c r="O58" s="2">
+      <c r="O58" s="6">
         <f t="shared" si="8"/>
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="P58" s="2">
         <f t="shared" si="6"/>
@@ -14147,13 +14208,13 @@
       <c r="G59" s="5">
         <v>54</v>
       </c>
-      <c r="H59" s="16" t="s">
+      <c r="H59" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="I59" s="15" t="s">
+      <c r="I59" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="J59" s="15" t="s">
+      <c r="J59" s="13" t="s">
         <v>271</v>
       </c>
       <c r="K59" s="2">
@@ -14172,9 +14233,9 @@
         <f t="shared" si="5"/>
         <v>830</v>
       </c>
-      <c r="O59" s="2">
+      <c r="O59" s="6">
         <f t="shared" si="8"/>
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="P59" s="2">
         <f t="shared" si="6"/>
@@ -14221,13 +14282,13 @@
       <c r="G60" s="1">
         <v>55</v>
       </c>
-      <c r="H60" s="16" t="s">
+      <c r="H60" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="I60" s="15" t="s">
+      <c r="I60" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="J60" s="15" t="s">
+      <c r="J60" s="13" t="s">
         <v>274</v>
       </c>
       <c r="K60" s="2">
@@ -14246,9 +14307,9 @@
         <f t="shared" si="5"/>
         <v>840</v>
       </c>
-      <c r="O60" s="2">
+      <c r="O60" s="6">
         <f t="shared" si="8"/>
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="P60" s="2">
         <f t="shared" si="6"/>
@@ -14295,13 +14356,13 @@
       <c r="G61" s="1">
         <v>56</v>
       </c>
-      <c r="H61" s="16" t="s">
+      <c r="H61" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="I61" s="15" t="s">
+      <c r="I61" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="J61" s="15" t="s">
+      <c r="J61" s="13" t="s">
         <v>277</v>
       </c>
       <c r="K61" s="2">
@@ -14320,9 +14381,9 @@
         <f t="shared" si="5"/>
         <v>850</v>
       </c>
-      <c r="O61" s="2">
+      <c r="O61" s="6">
         <f t="shared" si="8"/>
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="P61" s="2">
         <f t="shared" si="6"/>
@@ -14369,13 +14430,13 @@
       <c r="G62" s="1">
         <v>57</v>
       </c>
-      <c r="H62" s="16" t="s">
+      <c r="H62" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="I62" s="15" t="s">
+      <c r="I62" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="J62" s="15" t="s">
+      <c r="J62" s="13" t="s">
         <v>280</v>
       </c>
       <c r="K62" s="2">
@@ -14394,9 +14455,9 @@
         <f t="shared" si="5"/>
         <v>860</v>
       </c>
-      <c r="O62" s="2">
+      <c r="O62" s="6">
         <f t="shared" si="8"/>
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="P62" s="2">
         <f t="shared" si="6"/>
@@ -14437,19 +14498,19 @@
       <c r="E63" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="10" t="s">
+      <c r="F63" s="9" t="s">
         <v>92</v>
       </c>
       <c r="G63" s="1">
         <v>58</v>
       </c>
-      <c r="H63" s="16" t="s">
+      <c r="H63" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="I63" s="15" t="s">
+      <c r="I63" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="J63" s="15" t="s">
+      <c r="J63" s="13" t="s">
         <v>283</v>
       </c>
       <c r="K63" s="2">
@@ -14468,9 +14529,9 @@
         <f t="shared" si="5"/>
         <v>870</v>
       </c>
-      <c r="O63" s="2">
+      <c r="O63" s="6">
         <f t="shared" si="8"/>
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="P63" s="2">
         <f t="shared" si="6"/>
@@ -14517,13 +14578,13 @@
       <c r="G64" s="1">
         <v>59</v>
       </c>
-      <c r="H64" s="16" t="s">
+      <c r="H64" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="I64" s="15" t="s">
+      <c r="I64" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="J64" s="15" t="s">
+      <c r="J64" s="13" t="s">
         <v>286</v>
       </c>
       <c r="K64" s="2">
@@ -14542,9 +14603,9 @@
         <f t="shared" si="5"/>
         <v>880</v>
       </c>
-      <c r="O64" s="2">
+      <c r="O64" s="6">
         <f t="shared" si="8"/>
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="P64" s="2">
         <f t="shared" si="6"/>
@@ -14591,13 +14652,13 @@
       <c r="G65" s="5">
         <v>60</v>
       </c>
-      <c r="H65" s="16" t="s">
+      <c r="H65" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="I65" s="15" t="s">
+      <c r="I65" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="J65" s="15" t="s">
+      <c r="J65" s="13" t="s">
         <v>289</v>
       </c>
       <c r="K65" s="2">
@@ -14616,9 +14677,9 @@
         <f t="shared" si="5"/>
         <v>890</v>
       </c>
-      <c r="O65" s="2">
+      <c r="O65" s="6">
         <f t="shared" si="8"/>
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="P65" s="2">
         <f t="shared" si="6"/>
@@ -14665,13 +14726,13 @@
       <c r="G66" s="1">
         <v>61</v>
       </c>
-      <c r="H66" s="16" t="s">
+      <c r="H66" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="I66" s="15" t="s">
+      <c r="I66" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="J66" s="15" t="s">
+      <c r="J66" s="13" t="s">
         <v>292</v>
       </c>
       <c r="K66" s="2">
@@ -14690,9 +14751,9 @@
         <f t="shared" si="5"/>
         <v>900</v>
       </c>
-      <c r="O66" s="2">
+      <c r="O66" s="6">
         <f t="shared" si="8"/>
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="P66" s="2">
         <f t="shared" si="6"/>
@@ -14733,19 +14794,19 @@
       <c r="E67" s="1">
         <v>2</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="10" t="s">
         <v>96</v>
       </c>
       <c r="G67" s="1">
         <v>62</v>
       </c>
-      <c r="H67" s="16" t="s">
+      <c r="H67" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="I67" s="15" t="s">
+      <c r="I67" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="J67" s="15" t="s">
+      <c r="J67" s="13" t="s">
         <v>295</v>
       </c>
       <c r="K67" s="2">
@@ -14764,9 +14825,9 @@
         <f t="shared" si="5"/>
         <v>910</v>
       </c>
-      <c r="O67" s="2">
+      <c r="O67" s="6">
         <f t="shared" si="8"/>
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="P67" s="2">
         <f t="shared" si="6"/>
@@ -14813,13 +14874,13 @@
       <c r="G68" s="1">
         <v>63</v>
       </c>
-      <c r="H68" s="16" t="s">
+      <c r="H68" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="I68" s="15" t="s">
+      <c r="I68" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="J68" s="15" t="s">
+      <c r="J68" s="13" t="s">
         <v>298</v>
       </c>
       <c r="K68" s="2">
@@ -14838,9 +14899,9 @@
         <f t="shared" si="5"/>
         <v>920</v>
       </c>
-      <c r="O68" s="2">
+      <c r="O68" s="6">
         <f t="shared" si="8"/>
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="P68" s="2">
         <f t="shared" si="6"/>
@@ -14887,13 +14948,13 @@
       <c r="G69" s="1">
         <v>64</v>
       </c>
-      <c r="H69" s="16" t="s">
+      <c r="H69" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="I69" s="15" t="s">
+      <c r="I69" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="J69" s="15" t="s">
+      <c r="J69" s="13" t="s">
         <v>301</v>
       </c>
       <c r="K69" s="2">
@@ -14912,9 +14973,9 @@
         <f t="shared" si="5"/>
         <v>930</v>
       </c>
-      <c r="O69" s="2">
+      <c r="O69" s="6">
         <f t="shared" si="8"/>
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="P69" s="2">
         <f t="shared" si="6"/>
@@ -14961,13 +15022,13 @@
       <c r="G70" s="1">
         <v>65</v>
       </c>
-      <c r="H70" s="16" t="s">
+      <c r="H70" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="I70" s="15" t="s">
+      <c r="I70" s="13" t="s">
         <v>303</v>
       </c>
-      <c r="J70" s="15" t="s">
+      <c r="J70" s="13" t="s">
         <v>304</v>
       </c>
       <c r="K70" s="2">
@@ -14986,9 +15047,9 @@
         <f t="shared" si="5"/>
         <v>940</v>
       </c>
-      <c r="O70" s="2">
+      <c r="O70" s="6">
         <f t="shared" si="8"/>
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="P70" s="2">
         <f t="shared" si="6"/>
@@ -15037,13 +15098,13 @@
       <c r="G71" s="5">
         <v>66</v>
       </c>
-      <c r="H71" s="16" t="s">
+      <c r="H71" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="I71" s="15" t="s">
+      <c r="I71" s="13" t="s">
         <v>306</v>
       </c>
-      <c r="J71" s="15" t="s">
+      <c r="J71" s="13" t="s">
         <v>307</v>
       </c>
       <c r="K71" s="2">
@@ -15062,9 +15123,9 @@
         <f t="shared" ref="N71:N77" si="14">N70+10</f>
         <v>950</v>
       </c>
-      <c r="O71" s="2">
+      <c r="O71" s="6">
         <f t="shared" si="8"/>
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="P71" s="2">
         <f t="shared" ref="P71:P77" si="15">P70+1</f>
@@ -15111,13 +15172,13 @@
       <c r="G72" s="1">
         <v>67</v>
       </c>
-      <c r="H72" s="16" t="s">
+      <c r="H72" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="I72" s="15" t="s">
+      <c r="I72" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="J72" s="15" t="s">
+      <c r="J72" s="13" t="s">
         <v>309</v>
       </c>
       <c r="K72" s="2">
@@ -15136,9 +15197,9 @@
         <f t="shared" si="14"/>
         <v>960</v>
       </c>
-      <c r="O72" s="2">
+      <c r="O72" s="6">
         <f t="shared" si="8"/>
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="P72" s="2">
         <f t="shared" si="15"/>
@@ -15185,13 +15246,13 @@
       <c r="G73" s="1">
         <v>68</v>
       </c>
-      <c r="H73" s="16" t="s">
+      <c r="H73" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="I73" s="15" t="s">
+      <c r="I73" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="J73" s="15" t="s">
+      <c r="J73" s="13" t="s">
         <v>312</v>
       </c>
       <c r="K73" s="2">
@@ -15210,9 +15271,9 @@
         <f t="shared" si="14"/>
         <v>970</v>
       </c>
-      <c r="O73" s="2">
-        <f t="shared" ref="O73:O77" si="17">O70+1</f>
-        <v>61</v>
+      <c r="O73" s="6">
+        <f t="shared" si="8"/>
+        <v>24</v>
       </c>
       <c r="P73" s="2">
         <f t="shared" si="15"/>
@@ -15259,13 +15320,13 @@
       <c r="G74" s="1">
         <v>69</v>
       </c>
-      <c r="H74" s="16" t="s">
+      <c r="H74" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="I74" s="15" t="s">
+      <c r="I74" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="J74" s="15" t="s">
+      <c r="J74" s="13" t="s">
         <v>315</v>
       </c>
       <c r="K74" s="2">
@@ -15284,9 +15345,9 @@
         <f t="shared" si="14"/>
         <v>980</v>
       </c>
-      <c r="O74" s="2">
-        <f t="shared" si="17"/>
-        <v>61</v>
+      <c r="O74" s="6">
+        <f t="shared" si="8"/>
+        <v>24</v>
       </c>
       <c r="P74" s="2">
         <f t="shared" si="15"/>
@@ -15333,13 +15394,13 @@
       <c r="G75" s="1">
         <v>70</v>
       </c>
-      <c r="H75" s="16" t="s">
+      <c r="H75" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="I75" s="15" t="s">
+      <c r="I75" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="J75" s="15" t="s">
+      <c r="J75" s="13" t="s">
         <v>318</v>
       </c>
       <c r="K75" s="2">
@@ -15358,9 +15419,9 @@
         <f t="shared" si="14"/>
         <v>990</v>
       </c>
-      <c r="O75" s="2">
-        <f t="shared" si="17"/>
-        <v>62</v>
+      <c r="O75" s="6">
+        <f t="shared" si="8"/>
+        <v>24</v>
       </c>
       <c r="P75" s="2">
         <f t="shared" si="15"/>
@@ -15401,19 +15462,19 @@
       <c r="E76" s="1">
         <v>2</v>
       </c>
-      <c r="F76" s="10" t="s">
+      <c r="F76" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G76" s="1">
         <v>71</v>
       </c>
-      <c r="H76" s="16" t="s">
+      <c r="H76" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="I76" s="15" t="s">
+      <c r="I76" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="J76" s="15" t="s">
+      <c r="J76" s="13" t="s">
         <v>321</v>
       </c>
       <c r="K76" s="2">
@@ -15432,9 +15493,9 @@
         <f t="shared" si="14"/>
         <v>1000</v>
       </c>
-      <c r="O76" s="2">
-        <f t="shared" si="17"/>
-        <v>62</v>
+      <c r="O76" s="6">
+        <f>O70+1</f>
+        <v>24</v>
       </c>
       <c r="P76" s="2">
         <f t="shared" si="15"/>
@@ -15481,13 +15542,13 @@
       <c r="G77" s="1">
         <v>72</v>
       </c>
-      <c r="H77" s="16" t="s">
+      <c r="H77" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="I77" s="15" t="s">
+      <c r="I77" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="15" t="s">
+      <c r="J77" s="13" t="s">
         <v>324</v>
       </c>
       <c r="K77" s="2">
@@ -15506,9 +15567,9 @@
         <f t="shared" si="14"/>
         <v>1010</v>
       </c>
-      <c r="O77" s="2">
-        <f t="shared" si="17"/>
-        <v>62</v>
+      <c r="O77" s="6">
+        <f>O71+1</f>
+        <v>24</v>
       </c>
       <c r="P77" s="2">
         <f t="shared" si="15"/>
@@ -15723,7 +15784,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5 K3:U5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3:O5 C3:N5 P3:U5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="324">
   <si>
     <t>#</t>
   </si>
@@ -527,7 +527,7 @@
     <t>213E+7</t>
   </si>
   <si>
-    <t>540E+7</t>
+    <t>594E+7</t>
   </si>
   <si>
     <t>207E+11</t>
@@ -536,7 +536,7 @@
     <t>242E+7</t>
   </si>
   <si>
-    <t>648E+7</t>
+    <t>777E+7</t>
   </si>
   <si>
     <t>256E+11</t>
@@ -545,13 +545,13 @@
     <t>275E+7</t>
   </si>
   <si>
-    <t>777E+7</t>
+    <t>101E+8</t>
   </si>
   <si>
     <t>317E+11</t>
   </si>
   <si>
-    <t>932E+7</t>
+    <t>130E+8</t>
   </si>
   <si>
     <t>393E+11</t>
@@ -560,7 +560,7 @@
     <t>356E+7</t>
   </si>
   <si>
-    <t>111E+8</t>
+    <t>166E+8</t>
   </si>
   <si>
     <t>487E+11</t>
@@ -569,7 +569,7 @@
     <t>406E+7</t>
   </si>
   <si>
-    <t>133E+8</t>
+    <t>213E+8</t>
   </si>
   <si>
     <t>604E+11</t>
@@ -578,7 +578,7 @@
     <t>462E+7</t>
   </si>
   <si>
-    <t>159E+8</t>
+    <t>270E+8</t>
   </si>
   <si>
     <t>749E+11</t>
@@ -587,7 +587,7 @@
     <t>526E+7</t>
   </si>
   <si>
-    <t>191E+8</t>
+    <t>343E+8</t>
   </si>
   <si>
     <t>928E+11</t>
@@ -596,7 +596,7 @@
     <t>600E+7</t>
   </si>
   <si>
-    <t>229E+8</t>
+    <t>435E+8</t>
   </si>
   <si>
     <t>115E+12</t>
@@ -605,7 +605,7 @@
     <t>684E+7</t>
   </si>
   <si>
-    <t>274E+8</t>
+    <t>548E+8</t>
   </si>
   <si>
     <t>142E+12</t>
@@ -614,7 +614,7 @@
     <t>780E+7</t>
   </si>
   <si>
-    <t>329E+8</t>
+    <t>691E+8</t>
   </si>
   <si>
     <t>176E+12</t>
@@ -623,16 +623,13 @@
     <t>889E+7</t>
   </si>
   <si>
-    <t>395E+8</t>
+    <t>870E+8</t>
   </si>
   <si>
     <t>218E+12</t>
   </si>
   <si>
-    <t>101E+8</t>
-  </si>
-  <si>
-    <t>474E+8</t>
+    <t>109E+9</t>
   </si>
   <si>
     <t>270E+12</t>
@@ -641,7 +638,7 @@
     <t>115E+8</t>
   </si>
   <si>
-    <t>569E+8</t>
+    <t>136E+9</t>
   </si>
   <si>
     <t>335E+12</t>
@@ -650,7 +647,7 @@
     <t>131E+8</t>
   </si>
   <si>
-    <t>683E+8</t>
+    <t>170E+9</t>
   </si>
   <si>
     <t>415E+12</t>
@@ -659,7 +656,7 @@
     <t>149E+8</t>
   </si>
   <si>
-    <t>819E+8</t>
+    <t>213E+9</t>
   </si>
   <si>
     <t>514E+12</t>
@@ -668,7 +665,7 @@
     <t>169E+8</t>
   </si>
   <si>
-    <t>983E+8</t>
+    <t>265E+9</t>
   </si>
   <si>
     <t>637E+12</t>
@@ -677,7 +674,7 @@
     <t>192E+8</t>
   </si>
   <si>
-    <t>117E+9</t>
+    <t>327E+9</t>
   </si>
   <si>
     <t>790E+12</t>
@@ -686,7 +683,7 @@
     <t>219E+8</t>
   </si>
   <si>
-    <t>140E+9</t>
+    <t>406E+9</t>
   </si>
   <si>
     <t>980E+12</t>
@@ -695,7 +692,7 @@
     <t>250E+8</t>
   </si>
   <si>
-    <t>168E+9</t>
+    <t>504E+9</t>
   </si>
   <si>
     <t>121E+13</t>
@@ -704,7 +701,7 @@
     <t>285E+8</t>
   </si>
   <si>
-    <t>201E+9</t>
+    <t>623E+9</t>
   </si>
   <si>
     <t>150E+13</t>
@@ -713,7 +710,7 @@
     <t>325E+8</t>
   </si>
   <si>
-    <t>241E+9</t>
+    <t>771E+9</t>
   </si>
   <si>
     <t>186E+13</t>
@@ -722,7 +719,7 @@
     <t>370E+8</t>
   </si>
   <si>
-    <t>289E+9</t>
+    <t>954E+9</t>
   </si>
   <si>
     <t>230E+13</t>
@@ -731,7 +728,7 @@
     <t>422E+8</t>
   </si>
   <si>
-    <t>347E+9</t>
+    <t>118E+10</t>
   </si>
   <si>
     <t>285E+13</t>
@@ -740,16 +737,13 @@
     <t>481E+8</t>
   </si>
   <si>
-    <t>416E+9</t>
+    <t>146E+10</t>
   </si>
   <si>
     <t>353E+13</t>
   </si>
   <si>
-    <t>548E+8</t>
-  </si>
-  <si>
-    <t>499E+9</t>
+    <t>180E+10</t>
   </si>
   <si>
     <t>437E+13</t>
@@ -758,7 +752,7 @@
     <t>624E+8</t>
   </si>
   <si>
-    <t>599E+9</t>
+    <t>222E+10</t>
   </si>
   <si>
     <t>542E+13</t>
@@ -767,7 +761,7 @@
     <t>711E+8</t>
   </si>
   <si>
-    <t>719E+9</t>
+    <t>273E+10</t>
   </si>
   <si>
     <t>672E+13</t>
@@ -776,7 +770,7 @@
     <t>810E+8</t>
   </si>
   <si>
-    <t>863E+9</t>
+    <t>336E+10</t>
   </si>
   <si>
     <t>833E+13</t>
@@ -785,181 +779,184 @@
     <t>923E+8</t>
   </si>
   <si>
+    <t>412E+10</t>
+  </si>
+  <si>
     <t>103E+14</t>
   </si>
   <si>
     <t>105E+9</t>
   </si>
   <si>
+    <t>504E+10</t>
+  </si>
+  <si>
+    <t>127E+14</t>
+  </si>
+  <si>
+    <t>119E+9</t>
+  </si>
+  <si>
+    <t>617E+10</t>
+  </si>
+  <si>
+    <t>157E+14</t>
+  </si>
+  <si>
+    <t>135E+9</t>
+  </si>
+  <si>
+    <t>757E+10</t>
+  </si>
+  <si>
+    <t>194E+14</t>
+  </si>
+  <si>
+    <t>153E+9</t>
+  </si>
+  <si>
+    <t>928E+10</t>
+  </si>
+  <si>
+    <t>240E+14</t>
+  </si>
+  <si>
+    <t>174E+9</t>
+  </si>
+  <si>
+    <t>114E+11</t>
+  </si>
+  <si>
+    <t>297E+14</t>
+  </si>
+  <si>
+    <t>198E+9</t>
+  </si>
+  <si>
+    <t>139E+11</t>
+  </si>
+  <si>
+    <t>368E+14</t>
+  </si>
+  <si>
+    <t>225E+9</t>
+  </si>
+  <si>
+    <t>170E+11</t>
+  </si>
+  <si>
+    <t>456E+14</t>
+  </si>
+  <si>
+    <t>256E+9</t>
+  </si>
+  <si>
+    <t>208E+11</t>
+  </si>
+  <si>
+    <t>565E+14</t>
+  </si>
+  <si>
+    <t>292E+9</t>
+  </si>
+  <si>
+    <t>700E+14</t>
+  </si>
+  <si>
+    <t>333E+9</t>
+  </si>
+  <si>
+    <t>313E+11</t>
+  </si>
+  <si>
+    <t>868E+14</t>
+  </si>
+  <si>
+    <t>380E+9</t>
+  </si>
+  <si>
+    <t>383E+11</t>
+  </si>
+  <si>
+    <t>107E+15</t>
+  </si>
+  <si>
+    <t>433E+9</t>
+  </si>
+  <si>
+    <t>468E+11</t>
+  </si>
+  <si>
+    <t>132E+15</t>
+  </si>
+  <si>
+    <t>493E+9</t>
+  </si>
+  <si>
+    <t>572E+11</t>
+  </si>
+  <si>
+    <t>163E+15</t>
+  </si>
+  <si>
+    <t>562E+9</t>
+  </si>
+  <si>
+    <t>697E+11</t>
+  </si>
+  <si>
+    <t>202E+15</t>
+  </si>
+  <si>
+    <t>640E+9</t>
+  </si>
+  <si>
+    <t>852E+11</t>
+  </si>
+  <si>
+    <t>250E+15</t>
+  </si>
+  <si>
+    <t>730E+9</t>
+  </si>
+  <si>
+    <t>104E+12</t>
+  </si>
+  <si>
+    <t>310E+15</t>
+  </si>
+  <si>
+    <t>832E+9</t>
+  </si>
+  <si>
+    <t>127E+12</t>
+  </si>
+  <si>
+    <t>384E+15</t>
+  </si>
+  <si>
+    <t>948E+9</t>
+  </si>
+  <si>
+    <t>155E+12</t>
+  </si>
+  <si>
+    <t>476E+15</t>
+  </si>
+  <si>
+    <t>108E+10</t>
+  </si>
+  <si>
+    <t>189E+12</t>
+  </si>
+  <si>
+    <t>590E+15</t>
+  </si>
+  <si>
     <t>123E+10</t>
   </si>
   <si>
-    <t>127E+14</t>
-  </si>
-  <si>
-    <t>119E+9</t>
-  </si>
-  <si>
-    <t>147E+10</t>
-  </si>
-  <si>
-    <t>157E+14</t>
-  </si>
-  <si>
-    <t>135E+9</t>
-  </si>
-  <si>
-    <t>176E+10</t>
-  </si>
-  <si>
-    <t>194E+14</t>
-  </si>
-  <si>
-    <t>153E+9</t>
-  </si>
-  <si>
-    <t>211E+10</t>
-  </si>
-  <si>
-    <t>240E+14</t>
-  </si>
-  <si>
-    <t>174E+9</t>
-  </si>
-  <si>
-    <t>253E+10</t>
-  </si>
-  <si>
-    <t>297E+14</t>
-  </si>
-  <si>
-    <t>198E+9</t>
-  </si>
-  <si>
-    <t>303E+10</t>
-  </si>
-  <si>
-    <t>368E+14</t>
-  </si>
-  <si>
-    <t>225E+9</t>
-  </si>
-  <si>
-    <t>363E+10</t>
-  </si>
-  <si>
-    <t>456E+14</t>
-  </si>
-  <si>
-    <t>256E+9</t>
-  </si>
-  <si>
-    <t>435E+10</t>
-  </si>
-  <si>
-    <t>565E+14</t>
-  </si>
-  <si>
-    <t>292E+9</t>
-  </si>
-  <si>
-    <t>522E+10</t>
-  </si>
-  <si>
-    <t>700E+14</t>
-  </si>
-  <si>
-    <t>333E+9</t>
-  </si>
-  <si>
-    <t>626E+10</t>
-  </si>
-  <si>
-    <t>868E+14</t>
-  </si>
-  <si>
-    <t>380E+9</t>
-  </si>
-  <si>
-    <t>751E+10</t>
-  </si>
-  <si>
-    <t>107E+15</t>
-  </si>
-  <si>
-    <t>433E+9</t>
-  </si>
-  <si>
-    <t>901E+10</t>
-  </si>
-  <si>
-    <t>132E+15</t>
-  </si>
-  <si>
-    <t>493E+9</t>
-  </si>
-  <si>
-    <t>108E+11</t>
-  </si>
-  <si>
-    <t>163E+15</t>
-  </si>
-  <si>
-    <t>562E+9</t>
-  </si>
-  <si>
-    <t>129E+11</t>
-  </si>
-  <si>
-    <t>202E+15</t>
-  </si>
-  <si>
-    <t>640E+9</t>
-  </si>
-  <si>
-    <t>155E+11</t>
-  </si>
-  <si>
-    <t>250E+15</t>
-  </si>
-  <si>
-    <t>730E+9</t>
-  </si>
-  <si>
-    <t>186E+11</t>
-  </si>
-  <si>
-    <t>310E+15</t>
-  </si>
-  <si>
-    <t>832E+9</t>
-  </si>
-  <si>
-    <t>223E+11</t>
-  </si>
-  <si>
-    <t>384E+15</t>
-  </si>
-  <si>
-    <t>948E+9</t>
-  </si>
-  <si>
-    <t>267E+11</t>
-  </si>
-  <si>
-    <t>476E+15</t>
-  </si>
-  <si>
-    <t>108E+10</t>
-  </si>
-  <si>
-    <t>320E+11</t>
-  </si>
-  <si>
-    <t>590E+15</t>
-  </si>
-  <si>
-    <t>384E+11</t>
+    <t>230E+12</t>
   </si>
   <si>
     <t>731E+15</t>
@@ -968,7 +965,7 @@
     <t>140E+10</t>
   </si>
   <si>
-    <t>461E+11</t>
+    <t>281E+12</t>
   </si>
   <si>
     <t>906E+15</t>
@@ -977,7 +974,7 @@
     <t>160E+10</t>
   </si>
   <si>
-    <t>553E+11</t>
+    <t>343E+12</t>
   </si>
   <si>
     <t>112E+16</t>
@@ -986,7 +983,7 @@
     <t>182E+10</t>
   </si>
   <si>
-    <t>663E+11</t>
+    <t>418E+12</t>
   </si>
   <si>
     <t>139E+16</t>
@@ -995,7 +992,7 @@
     <t>207E+10</t>
   </si>
   <si>
-    <t>795E+11</t>
+    <t>509E+12</t>
   </si>
   <si>
     <t>172E+16</t>
@@ -1004,7 +1001,7 @@
     <t>236E+10</t>
   </si>
   <si>
-    <t>954E+11</t>
+    <t>620E+12</t>
   </si>
   <si>
     <t>213E+16</t>
@@ -10005,7 +10002,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:W103"/>
+  <dimension ref="A1:X103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -10016,24 +10013,24 @@
     <col min="6" max="6" width="12.125" style="6" customWidth="1"/>
     <col min="7" max="7" width="9.58333333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.0833333333333" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.0833333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.4166666666667" style="2" customWidth="1"/>
-    <col min="12" max="12" width="10.3333333333333" style="2" customWidth="1"/>
-    <col min="13" max="13" width="9.91666666666667" style="2" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="2" customWidth="1"/>
-    <col min="15" max="15" width="12.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="10.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.3333333333333" style="2" customWidth="1"/>
-    <col min="18" max="19" width="8.75" style="2" customWidth="1"/>
-    <col min="20" max="20" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="21" max="21" width="8.33333333333333" style="2" customWidth="1"/>
-    <col min="22" max="22" width="9.91666666666667" style="2" customWidth="1"/>
-    <col min="23" max="23" width="10.3333333333333" style="2" customWidth="1"/>
-    <col min="24" max="16384" width="9" style="2"/>
+    <col min="9" max="10" width="15.0833333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="18.5" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.4166666666667" style="2" customWidth="1"/>
+    <col min="13" max="13" width="10.3333333333333" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9.91666666666667" style="2" customWidth="1"/>
+    <col min="15" max="15" width="8.75" style="2" customWidth="1"/>
+    <col min="16" max="16" width="12.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="10.75" style="2" customWidth="1"/>
+    <col min="18" max="18" width="11.3333333333333" style="2" customWidth="1"/>
+    <col min="19" max="20" width="8.75" style="2" customWidth="1"/>
+    <col min="21" max="21" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.33333333333333" style="2" customWidth="1"/>
+    <col min="23" max="23" width="9.91666666666667" style="2" customWidth="1"/>
+    <col min="24" max="24" width="10.3333333333333" style="2" customWidth="1"/>
+    <col min="25" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="F1" s="6"/>
@@ -10053,8 +10050,9 @@
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="F2" s="6"/>
@@ -10074,8 +10072,9 @@
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="7" t="s">
@@ -10099,50 +10098,51 @@
       <c r="I3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="7"/>
+      <c r="K3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="L3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="M3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="N3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="O3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="P3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="Q3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="R3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="7" t="s">
@@ -10166,50 +10166,51 @@
       <c r="I4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="7"/>
+      <c r="K4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="M4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="N4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="O4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="P4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="Q4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="R4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="S4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="T4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="U4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="U4" s="7" t="s">
+      <c r="V4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="W4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="W4" s="7" t="s">
+      <c r="X4" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="7" t="s">
@@ -10233,11 +10234,9 @@
       <c r="I5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="7"/>
+      <c r="K5" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>32</v>
       </c>
       <c r="L5" s="7" t="s">
         <v>32</v>
@@ -10270,13 +10269,16 @@
         <v>32</v>
       </c>
       <c r="V5" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="W5" s="7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="11.5" spans="1:23">
+      <c r="X5" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="11.5" spans="1:24">
       <c r="C6" s="1">
         <v>73</v>
       </c>
@@ -10298,52 +10300,53 @@
       <c r="I6" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="6"/>
+      <c r="K6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>440</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>250</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>147</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>300</v>
       </c>
-      <c r="O6" s="1">
+      <c r="P6" s="1">
         <v>13</v>
       </c>
-      <c r="P6" s="2">
+      <c r="Q6" s="2">
         <v>72</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="R6" s="2">
         <v>73</v>
       </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
       <c r="S6" s="1">
         <v>0</v>
       </c>
-      <c r="T6" s="4">
+      <c r="T6" s="1">
         <v>0</v>
       </c>
       <c r="U6" s="4">
         <v>0</v>
       </c>
-      <c r="V6" s="1">
-        <f t="shared" ref="V6:V69" si="0">C6*10</f>
+      <c r="V6" s="4">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" ref="W6:W69" si="0">C6*10</f>
         <v>730</v>
       </c>
-      <c r="W6" s="1">
-        <f t="shared" ref="W6:W69" si="1">D6*10</f>
+      <c r="X6" s="1">
+        <f t="shared" ref="X6:X69" si="1">D6*10</f>
         <v>730</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:23">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C7" s="1">
         <v>74</v>
       </c>
@@ -10365,58 +10368,62 @@
       <c r="I7" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="6">
+        <f t="shared" ref="J7:J70" si="2">I7/I6</f>
+        <v>1.19838056680162</v>
+      </c>
+      <c r="K7" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="K7" s="2">
-        <f t="shared" ref="K7:K70" si="2">K6+20</f>
+      <c r="L7" s="2">
+        <f t="shared" ref="L7:L70" si="3">L6+20</f>
         <v>460</v>
       </c>
-      <c r="L7" s="2">
-        <f t="shared" ref="L7:L70" si="3">L6+10</f>
+      <c r="M7" s="2">
+        <f t="shared" ref="M7:M70" si="4">M6+10</f>
         <v>260</v>
       </c>
-      <c r="M7" s="2">
-        <f t="shared" ref="M7:M70" si="4">M6+3</f>
+      <c r="N7" s="2">
+        <f t="shared" ref="N7:N70" si="5">N6+3</f>
         <v>150</v>
       </c>
-      <c r="N7" s="2">
-        <f t="shared" ref="N7:N70" si="5">N6+10</f>
+      <c r="O7" s="2">
+        <f t="shared" ref="O7:O70" si="6">O6+10</f>
         <v>310</v>
       </c>
-      <c r="O7" s="1">
+      <c r="P7" s="1">
         <v>13</v>
-      </c>
-      <c r="P7" s="2">
-        <f t="shared" ref="P7:P70" si="6">P6+1</f>
-        <v>73</v>
       </c>
       <c r="Q7" s="2">
         <f t="shared" ref="Q7:Q70" si="7">Q6+1</f>
+        <v>73</v>
+      </c>
+      <c r="R7" s="2">
+        <f t="shared" ref="R7:R70" si="8">R6+1</f>
         <v>74</v>
       </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
       <c r="S7" s="1">
         <v>0</v>
       </c>
-      <c r="T7" s="4">
+      <c r="T7" s="1">
         <v>0</v>
       </c>
       <c r="U7" s="4">
         <v>0</v>
       </c>
-      <c r="V7" s="1">
+      <c r="V7" s="4">
+        <v>0</v>
+      </c>
+      <c r="W7" s="1">
         <f t="shared" si="0"/>
         <v>740</v>
       </c>
-      <c r="W7" s="1">
+      <c r="X7" s="1">
         <f t="shared" si="1"/>
         <v>740</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:23">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C8" s="1">
         <v>75</v>
       </c>
@@ -10438,58 +10445,62 @@
       <c r="I8" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="6">
+        <f t="shared" si="2"/>
+        <v>1.19932432432432</v>
+      </c>
+      <c r="K8" s="13" t="s">
         <v>121</v>
-      </c>
-      <c r="K8" s="2">
-        <f t="shared" si="2"/>
-        <v>480</v>
       </c>
       <c r="L8" s="2">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>480</v>
       </c>
       <c r="M8" s="2">
         <f t="shared" si="4"/>
-        <v>153</v>
+        <v>270</v>
       </c>
       <c r="N8" s="2">
         <f t="shared" si="5"/>
+        <v>153</v>
+      </c>
+      <c r="O8" s="2">
+        <f t="shared" si="6"/>
         <v>320</v>
       </c>
-      <c r="O8" s="1">
+      <c r="P8" s="1">
         <v>13</v>
-      </c>
-      <c r="P8" s="2">
-        <f t="shared" si="6"/>
-        <v>74</v>
       </c>
       <c r="Q8" s="2">
         <f t="shared" si="7"/>
+        <v>74</v>
+      </c>
+      <c r="R8" s="2">
+        <f t="shared" si="8"/>
         <v>75</v>
       </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
       <c r="S8" s="1">
         <v>0</v>
       </c>
-      <c r="T8" s="4">
+      <c r="T8" s="1">
         <v>0</v>
       </c>
       <c r="U8" s="4">
         <v>0</v>
       </c>
-      <c r="V8" s="1">
+      <c r="V8" s="4">
+        <v>0</v>
+      </c>
+      <c r="W8" s="1">
         <f t="shared" si="0"/>
         <v>750</v>
       </c>
-      <c r="W8" s="1">
+      <c r="X8" s="1">
         <f t="shared" si="1"/>
         <v>750</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:23">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C9" s="1">
         <v>76</v>
       </c>
@@ -10511,58 +10522,62 @@
       <c r="I9" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="6">
+        <f t="shared" si="2"/>
+        <v>1.2</v>
+      </c>
+      <c r="K9" s="13" t="s">
         <v>124</v>
-      </c>
-      <c r="K9" s="2">
-        <f t="shared" si="2"/>
-        <v>500</v>
       </c>
       <c r="L9" s="2">
         <f t="shared" si="3"/>
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="M9" s="2">
         <f t="shared" si="4"/>
-        <v>156</v>
+        <v>280</v>
       </c>
       <c r="N9" s="2">
         <f t="shared" si="5"/>
+        <v>156</v>
+      </c>
+      <c r="O9" s="2">
+        <f t="shared" si="6"/>
         <v>330</v>
       </c>
-      <c r="O9" s="1">
+      <c r="P9" s="1">
         <v>13</v>
-      </c>
-      <c r="P9" s="2">
-        <f t="shared" si="6"/>
-        <v>75</v>
       </c>
       <c r="Q9" s="2">
         <f t="shared" si="7"/>
+        <v>75</v>
+      </c>
+      <c r="R9" s="2">
+        <f t="shared" si="8"/>
         <v>76</v>
       </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
       <c r="S9" s="1">
         <v>0</v>
       </c>
-      <c r="T9" s="4">
+      <c r="T9" s="1">
         <v>0</v>
       </c>
       <c r="U9" s="4">
         <v>0</v>
       </c>
-      <c r="V9" s="1">
+      <c r="V9" s="4">
+        <v>0</v>
+      </c>
+      <c r="W9" s="1">
         <f t="shared" si="0"/>
         <v>760</v>
       </c>
-      <c r="W9" s="1">
+      <c r="X9" s="1">
         <f t="shared" si="1"/>
         <v>760</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:23">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C10" s="1">
         <v>77</v>
       </c>
@@ -10584,58 +10599,62 @@
       <c r="I10" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="6">
+        <f t="shared" si="2"/>
+        <v>1.19953051643192</v>
+      </c>
+      <c r="K10" s="13" t="s">
         <v>127</v>
-      </c>
-      <c r="K10" s="2">
-        <f t="shared" si="2"/>
-        <v>520</v>
       </c>
       <c r="L10" s="2">
         <f t="shared" si="3"/>
-        <v>290</v>
+        <v>520</v>
       </c>
       <c r="M10" s="2">
         <f t="shared" si="4"/>
-        <v>159</v>
+        <v>290</v>
       </c>
       <c r="N10" s="2">
         <f t="shared" si="5"/>
+        <v>159</v>
+      </c>
+      <c r="O10" s="2">
+        <f t="shared" si="6"/>
         <v>340</v>
       </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
         <v>13</v>
-      </c>
-      <c r="P10" s="2">
-        <f t="shared" si="6"/>
-        <v>76</v>
       </c>
       <c r="Q10" s="2">
         <f t="shared" si="7"/>
+        <v>76</v>
+      </c>
+      <c r="R10" s="2">
+        <f t="shared" si="8"/>
         <v>77</v>
       </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
       <c r="S10" s="1">
         <v>0</v>
       </c>
-      <c r="T10" s="4">
+      <c r="T10" s="1">
         <v>0</v>
       </c>
       <c r="U10" s="4">
         <v>0</v>
       </c>
-      <c r="V10" s="1">
+      <c r="V10" s="4">
+        <v>0</v>
+      </c>
+      <c r="W10" s="1">
         <f t="shared" si="0"/>
         <v>770</v>
       </c>
-      <c r="W10" s="1">
+      <c r="X10" s="1">
         <f t="shared" si="1"/>
         <v>770</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="1:23">
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="1:24">
       <c r="C11" s="1">
         <v>78</v>
       </c>
@@ -10657,2204 +10676,2324 @@
       <c r="I11" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="6">
+        <f t="shared" si="2"/>
+        <v>1.19960861056751</v>
+      </c>
+      <c r="K11" s="13" t="s">
         <v>130</v>
-      </c>
-      <c r="K11" s="2">
-        <f t="shared" si="2"/>
-        <v>540</v>
       </c>
       <c r="L11" s="2">
         <f t="shared" si="3"/>
-        <v>300</v>
+        <v>540</v>
       </c>
       <c r="M11" s="2">
         <f t="shared" si="4"/>
-        <v>162</v>
+        <v>300</v>
       </c>
       <c r="N11" s="2">
         <f t="shared" si="5"/>
+        <v>162</v>
+      </c>
+      <c r="O11" s="2">
+        <f t="shared" si="6"/>
         <v>350</v>
       </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="P11" s="2">
+      <c r="Q11" s="2">
+        <f t="shared" si="7"/>
+        <v>77</v>
+      </c>
+      <c r="R11" s="3">
+        <f t="shared" si="8"/>
+        <v>78</v>
+      </c>
+      <c r="S11" s="5">
+        <v>0</v>
+      </c>
+      <c r="T11" s="5">
+        <v>0</v>
+      </c>
+      <c r="U11" s="3">
+        <v>0</v>
+      </c>
+      <c r="V11" s="3">
+        <v>0</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" si="1"/>
+        <v>780</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C12" s="1">
+        <v>79</v>
+      </c>
+      <c r="D12" s="1">
+        <v>79</v>
+      </c>
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" s="6">
+        <v>7</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="J12" s="6">
+        <f t="shared" si="2"/>
+        <v>1.20065252854812</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="L12" s="2">
+        <f t="shared" si="3"/>
+        <v>560</v>
+      </c>
+      <c r="M12" s="2">
+        <f t="shared" si="4"/>
+        <v>310</v>
+      </c>
+      <c r="N12" s="2">
+        <f t="shared" si="5"/>
+        <v>165</v>
+      </c>
+      <c r="O12" s="2">
         <f t="shared" si="6"/>
-        <v>77</v>
-      </c>
-      <c r="Q11" s="3">
+        <v>360</v>
+      </c>
+      <c r="P12" s="6">
+        <f t="shared" ref="P12:P75" si="9">P6+1</f>
+        <v>14</v>
+      </c>
+      <c r="Q12" s="2">
         <f t="shared" si="7"/>
         <v>78</v>
       </c>
-      <c r="R11" s="5">
-        <v>0</v>
-      </c>
-      <c r="S11" s="5">
-        <v>0</v>
-      </c>
-      <c r="T11" s="3">
-        <v>0</v>
-      </c>
-      <c r="U11" s="3">
-        <v>0</v>
-      </c>
-      <c r="V11" s="1">
+      <c r="R12" s="4">
+        <f t="shared" si="8"/>
+        <v>79</v>
+      </c>
+      <c r="S12" s="6">
+        <v>0</v>
+      </c>
+      <c r="T12" s="6">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4">
+        <v>0</v>
+      </c>
+      <c r="V12" s="4">
+        <v>0</v>
+      </c>
+      <c r="W12" s="1">
         <f t="shared" si="0"/>
-        <v>780</v>
-      </c>
-      <c r="W11" s="1">
+        <v>790</v>
+      </c>
+      <c r="X12" s="1">
         <f t="shared" si="1"/>
-        <v>780</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C12" s="1">
-        <v>79</v>
-      </c>
-      <c r="D12" s="1">
-        <v>79</v>
-      </c>
-      <c r="E12" s="1">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C13" s="1">
+        <v>80</v>
+      </c>
+      <c r="D13" s="1">
+        <v>80</v>
+      </c>
+      <c r="E13" s="1">
         <v>2</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="6">
-        <v>7</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="J12" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="K12" s="2">
+      <c r="F13" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="6">
+        <v>8</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J13" s="6">
         <f t="shared" si="2"/>
-        <v>560</v>
-      </c>
-      <c r="L12" s="2">
+        <v>1.19972826086957</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="L13" s="2">
         <f t="shared" si="3"/>
-        <v>310</v>
-      </c>
-      <c r="M12" s="2">
+        <v>580</v>
+      </c>
+      <c r="M13" s="2">
         <f t="shared" si="4"/>
-        <v>165</v>
-      </c>
-      <c r="N12" s="2">
+        <v>320</v>
+      </c>
+      <c r="N13" s="2">
         <f t="shared" si="5"/>
-        <v>360</v>
-      </c>
-      <c r="O12" s="6">
-        <f t="shared" ref="O12:O75" si="8">O6+1</f>
+        <v>168</v>
+      </c>
+      <c r="O13" s="2">
+        <f t="shared" si="6"/>
+        <v>370</v>
+      </c>
+      <c r="P13" s="6">
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="P12" s="2">
-        <f t="shared" si="6"/>
-        <v>78</v>
-      </c>
-      <c r="Q12" s="4">
+      <c r="Q13" s="2">
         <f t="shared" si="7"/>
         <v>79</v>
       </c>
-      <c r="R12" s="6">
-        <v>0</v>
-      </c>
-      <c r="S12" s="6">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4">
-        <v>0</v>
-      </c>
-      <c r="U12" s="4">
-        <v>0</v>
-      </c>
-      <c r="V12" s="1">
+      <c r="R13" s="4">
+        <f t="shared" si="8"/>
+        <v>80</v>
+      </c>
+      <c r="S13" s="6">
+        <v>0</v>
+      </c>
+      <c r="T13" s="6">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4">
+        <v>0</v>
+      </c>
+      <c r="V13" s="4">
+        <v>0</v>
+      </c>
+      <c r="W13" s="1">
         <f t="shared" si="0"/>
-        <v>790</v>
-      </c>
-      <c r="W12" s="1">
+        <v>800</v>
+      </c>
+      <c r="X13" s="1">
         <f t="shared" si="1"/>
-        <v>790</v>
-      </c>
-    </row>
-    <row r="13" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C13" s="1">
-        <v>80</v>
-      </c>
-      <c r="D13" s="1">
-        <v>80</v>
-      </c>
-      <c r="E13" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C14" s="1">
+        <v>81</v>
+      </c>
+      <c r="D14" s="1">
+        <v>81</v>
+      </c>
+      <c r="E14" s="1">
         <v>2</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="6">
-        <v>8</v>
-      </c>
-      <c r="H13" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="I13" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="K13" s="2">
+      <c r="F14" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G14" s="6">
+        <v>9</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="J14" s="6">
         <f t="shared" si="2"/>
-        <v>580</v>
-      </c>
-      <c r="L13" s="2">
+        <v>1.2004530011325</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="L14" s="2">
         <f t="shared" si="3"/>
-        <v>320</v>
-      </c>
-      <c r="M13" s="2">
+        <v>600</v>
+      </c>
+      <c r="M14" s="2">
         <f t="shared" si="4"/>
-        <v>168</v>
-      </c>
-      <c r="N13" s="2">
+        <v>330</v>
+      </c>
+      <c r="N14" s="2">
         <f t="shared" si="5"/>
-        <v>370</v>
-      </c>
-      <c r="O13" s="6">
-        <f t="shared" si="8"/>
+        <v>171</v>
+      </c>
+      <c r="O14" s="2">
+        <f t="shared" si="6"/>
+        <v>380</v>
+      </c>
+      <c r="P14" s="6">
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="P13" s="2">
-        <f t="shared" si="6"/>
-        <v>79</v>
-      </c>
-      <c r="Q13" s="4">
+      <c r="Q14" s="2">
         <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="R13" s="6">
-        <v>0</v>
-      </c>
-      <c r="S13" s="6">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4">
-        <v>0</v>
-      </c>
-      <c r="U13" s="4">
-        <v>0</v>
-      </c>
-      <c r="V13" s="1">
+      <c r="R14" s="4">
+        <f t="shared" si="8"/>
+        <v>81</v>
+      </c>
+      <c r="S14" s="6">
+        <v>0</v>
+      </c>
+      <c r="T14" s="6">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4">
+        <v>0</v>
+      </c>
+      <c r="V14" s="4">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1">
         <f t="shared" si="0"/>
-        <v>800</v>
-      </c>
-      <c r="W13" s="1">
+        <v>810</v>
+      </c>
+      <c r="X14" s="1">
         <f t="shared" si="1"/>
-        <v>800</v>
-      </c>
-    </row>
-    <row r="14" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C14" s="1">
-        <v>81</v>
-      </c>
-      <c r="D14" s="1">
-        <v>81</v>
-      </c>
-      <c r="E14" s="1">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="15" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C15" s="1">
+        <v>82</v>
+      </c>
+      <c r="D15" s="1">
+        <v>82</v>
+      </c>
+      <c r="E15" s="1">
         <v>2</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="6">
-        <v>9</v>
-      </c>
-      <c r="H14" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="K14" s="2">
+      <c r="F15" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="6">
+        <v>10</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J15" s="6">
         <f t="shared" si="2"/>
-        <v>600</v>
-      </c>
-      <c r="L14" s="2">
+        <v>1.19811320754717</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="L15" s="2">
         <f t="shared" si="3"/>
-        <v>330</v>
-      </c>
-      <c r="M14" s="2">
+        <v>620</v>
+      </c>
+      <c r="M15" s="2">
         <f t="shared" si="4"/>
-        <v>171</v>
-      </c>
-      <c r="N14" s="2">
+        <v>340</v>
+      </c>
+      <c r="N15" s="2">
         <f t="shared" si="5"/>
-        <v>380</v>
-      </c>
-      <c r="O14" s="6">
-        <f t="shared" si="8"/>
+        <v>174</v>
+      </c>
+      <c r="O15" s="2">
+        <f t="shared" si="6"/>
+        <v>390</v>
+      </c>
+      <c r="P15" s="6">
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="P14" s="2">
-        <f t="shared" si="6"/>
-        <v>80</v>
-      </c>
-      <c r="Q14" s="4">
+      <c r="Q15" s="2">
         <f t="shared" si="7"/>
         <v>81</v>
       </c>
-      <c r="R14" s="6">
-        <v>0</v>
-      </c>
-      <c r="S14" s="6">
-        <v>0</v>
-      </c>
-      <c r="T14" s="4">
-        <v>0</v>
-      </c>
-      <c r="U14" s="4">
-        <v>0</v>
-      </c>
-      <c r="V14" s="1">
+      <c r="R15" s="4">
+        <f t="shared" si="8"/>
+        <v>82</v>
+      </c>
+      <c r="S15" s="6">
+        <v>0</v>
+      </c>
+      <c r="T15" s="6">
+        <v>0</v>
+      </c>
+      <c r="U15" s="4">
+        <v>0</v>
+      </c>
+      <c r="V15" s="4">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
         <f t="shared" si="0"/>
-        <v>810</v>
-      </c>
-      <c r="W14" s="1">
+        <v>820</v>
+      </c>
+      <c r="X15" s="1">
         <f t="shared" si="1"/>
-        <v>810</v>
-      </c>
-    </row>
-    <row r="15" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C15" s="1">
-        <v>82</v>
-      </c>
-      <c r="D15" s="1">
-        <v>82</v>
-      </c>
-      <c r="E15" s="1">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C16" s="1">
+        <v>83</v>
+      </c>
+      <c r="D16" s="1">
+        <v>83</v>
+      </c>
+      <c r="E16" s="1">
         <v>2</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" s="6">
-        <v>10</v>
-      </c>
-      <c r="H15" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="K15" s="2">
+      <c r="F16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="6">
+        <v>11</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="J16" s="6">
         <f t="shared" si="2"/>
-        <v>620</v>
-      </c>
-      <c r="L15" s="2">
+        <v>1.19685039370079</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="L16" s="2">
         <f t="shared" si="3"/>
-        <v>340</v>
-      </c>
-      <c r="M15" s="2">
+        <v>640</v>
+      </c>
+      <c r="M16" s="2">
         <f t="shared" si="4"/>
-        <v>174</v>
-      </c>
-      <c r="N15" s="2">
+        <v>350</v>
+      </c>
+      <c r="N16" s="2">
         <f t="shared" si="5"/>
-        <v>390</v>
-      </c>
-      <c r="O15" s="6">
-        <f t="shared" si="8"/>
+        <v>177</v>
+      </c>
+      <c r="O16" s="2">
+        <f t="shared" si="6"/>
+        <v>400</v>
+      </c>
+      <c r="P16" s="6">
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="P15" s="2">
-        <f t="shared" si="6"/>
-        <v>81</v>
-      </c>
-      <c r="Q15" s="4">
+      <c r="Q16" s="2">
         <f t="shared" si="7"/>
         <v>82</v>
       </c>
-      <c r="R15" s="6">
-        <v>0</v>
-      </c>
-      <c r="S15" s="6">
-        <v>0</v>
-      </c>
-      <c r="T15" s="4">
-        <v>0</v>
-      </c>
-      <c r="U15" s="4">
-        <v>0</v>
-      </c>
-      <c r="V15" s="1">
+      <c r="R16" s="4">
+        <f t="shared" si="8"/>
+        <v>83</v>
+      </c>
+      <c r="S16" s="6">
+        <v>0</v>
+      </c>
+      <c r="T16" s="6">
+        <v>0</v>
+      </c>
+      <c r="U16" s="4">
+        <v>0</v>
+      </c>
+      <c r="V16" s="4">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1">
         <f t="shared" si="0"/>
-        <v>820</v>
-      </c>
-      <c r="W15" s="1">
+        <v>830</v>
+      </c>
+      <c r="X16" s="1">
         <f t="shared" si="1"/>
-        <v>820</v>
-      </c>
-    </row>
-    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C16" s="1">
-        <v>83</v>
-      </c>
-      <c r="D16" s="1">
-        <v>83</v>
-      </c>
-      <c r="E16" s="1">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C17" s="1">
+        <v>84</v>
+      </c>
+      <c r="D17" s="1">
+        <v>84</v>
+      </c>
+      <c r="E17" s="1">
         <v>2</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="6">
-        <v>11</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="K16" s="2">
+      <c r="F17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17" s="5">
+        <v>12</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="J17" s="6">
         <f t="shared" si="2"/>
-        <v>640</v>
-      </c>
-      <c r="L16" s="2">
+        <v>1.19736842105263</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="L17" s="2">
         <f t="shared" si="3"/>
-        <v>350</v>
-      </c>
-      <c r="M16" s="2">
+        <v>660</v>
+      </c>
+      <c r="M17" s="2">
         <f t="shared" si="4"/>
-        <v>177</v>
-      </c>
-      <c r="N16" s="2">
+        <v>360</v>
+      </c>
+      <c r="N17" s="2">
         <f t="shared" si="5"/>
-        <v>400</v>
-      </c>
-      <c r="O16" s="6">
-        <f t="shared" si="8"/>
+        <v>180</v>
+      </c>
+      <c r="O17" s="2">
+        <f t="shared" si="6"/>
+        <v>410</v>
+      </c>
+      <c r="P17" s="6">
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="P16" s="2">
-        <f t="shared" si="6"/>
-        <v>82</v>
-      </c>
-      <c r="Q16" s="4">
+      <c r="Q17" s="2">
         <f t="shared" si="7"/>
         <v>83</v>
       </c>
-      <c r="R16" s="6">
-        <v>0</v>
-      </c>
-      <c r="S16" s="6">
-        <v>0</v>
-      </c>
-      <c r="T16" s="4">
-        <v>0</v>
-      </c>
-      <c r="U16" s="4">
-        <v>0</v>
-      </c>
-      <c r="V16" s="1">
+      <c r="R17" s="3">
+        <f t="shared" si="8"/>
+        <v>84</v>
+      </c>
+      <c r="S17" s="5">
+        <v>0</v>
+      </c>
+      <c r="T17" s="5">
+        <v>0</v>
+      </c>
+      <c r="U17" s="3">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3">
+        <v>0</v>
+      </c>
+      <c r="W17" s="1">
         <f t="shared" si="0"/>
-        <v>830</v>
-      </c>
-      <c r="W16" s="1">
+        <v>840</v>
+      </c>
+      <c r="X17" s="1">
         <f t="shared" si="1"/>
-        <v>830</v>
-      </c>
-    </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C17" s="1">
-        <v>84</v>
-      </c>
-      <c r="D17" s="1">
-        <v>84</v>
-      </c>
-      <c r="E17" s="1">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="18" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C18" s="1">
+        <v>85</v>
+      </c>
+      <c r="D18" s="1">
+        <v>85</v>
+      </c>
+      <c r="E18" s="1">
         <v>2</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" s="5">
-        <v>12</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="K17" s="2">
+      <c r="F18" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" s="6">
+        <v>13</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="J18" s="6">
         <f t="shared" si="2"/>
-        <v>660</v>
-      </c>
-      <c r="L17" s="2">
+        <v>1.1978021978022</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="L18" s="2">
         <f t="shared" si="3"/>
-        <v>360</v>
-      </c>
-      <c r="M17" s="2">
+        <v>680</v>
+      </c>
+      <c r="M18" s="2">
         <f t="shared" si="4"/>
-        <v>180</v>
-      </c>
-      <c r="N17" s="2">
+        <v>370</v>
+      </c>
+      <c r="N18" s="2">
         <f t="shared" si="5"/>
-        <v>410</v>
-      </c>
-      <c r="O17" s="6">
-        <f t="shared" si="8"/>
-        <v>14</v>
-      </c>
-      <c r="P17" s="2">
+        <v>183</v>
+      </c>
+      <c r="O18" s="2">
         <f t="shared" si="6"/>
-        <v>83</v>
-      </c>
-      <c r="Q17" s="3">
+        <v>420</v>
+      </c>
+      <c r="P18" s="6">
+        <f t="shared" si="9"/>
+        <v>15</v>
+      </c>
+      <c r="Q18" s="2">
         <f t="shared" si="7"/>
         <v>84</v>
       </c>
-      <c r="R17" s="5">
-        <v>0</v>
-      </c>
-      <c r="S17" s="5">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="1">
+      <c r="R18" s="4">
+        <f t="shared" si="8"/>
+        <v>85</v>
+      </c>
+      <c r="S18" s="6">
+        <v>0</v>
+      </c>
+      <c r="T18" s="6">
+        <v>0</v>
+      </c>
+      <c r="U18" s="4">
+        <v>0</v>
+      </c>
+      <c r="V18" s="4">
+        <v>0</v>
+      </c>
+      <c r="W18" s="1">
         <f t="shared" si="0"/>
-        <v>840</v>
-      </c>
-      <c r="W17" s="1">
+        <v>850</v>
+      </c>
+      <c r="X18" s="1">
         <f t="shared" si="1"/>
-        <v>840</v>
-      </c>
-    </row>
-    <row r="18" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C18" s="1">
-        <v>85</v>
-      </c>
-      <c r="D18" s="1">
-        <v>85</v>
-      </c>
-      <c r="E18" s="1">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="19" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C19" s="1">
+        <v>86</v>
+      </c>
+      <c r="D19" s="1">
+        <v>86</v>
+      </c>
+      <c r="E19" s="1">
         <v>2</v>
       </c>
-      <c r="F18" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18" s="6">
-        <v>13</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="K18" s="2">
+      <c r="F19" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="6">
+        <v>14</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="J19" s="6">
         <f t="shared" si="2"/>
-        <v>680</v>
-      </c>
-      <c r="L18" s="2">
+        <v>1.19724770642202</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="L19" s="2">
         <f t="shared" si="3"/>
-        <v>370</v>
-      </c>
-      <c r="M18" s="2">
+        <v>700</v>
+      </c>
+      <c r="M19" s="2">
         <f t="shared" si="4"/>
-        <v>183</v>
-      </c>
-      <c r="N18" s="2">
+        <v>380</v>
+      </c>
+      <c r="N19" s="2">
         <f t="shared" si="5"/>
-        <v>420</v>
-      </c>
-      <c r="O18" s="6">
-        <f t="shared" si="8"/>
+        <v>186</v>
+      </c>
+      <c r="O19" s="2">
+        <f t="shared" si="6"/>
+        <v>430</v>
+      </c>
+      <c r="P19" s="6">
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="P18" s="2">
-        <f t="shared" si="6"/>
-        <v>84</v>
-      </c>
-      <c r="Q18" s="4">
+      <c r="Q19" s="2">
         <f t="shared" si="7"/>
         <v>85</v>
       </c>
-      <c r="R18" s="6">
-        <v>0</v>
-      </c>
-      <c r="S18" s="6">
-        <v>0</v>
-      </c>
-      <c r="T18" s="4">
-        <v>0</v>
-      </c>
-      <c r="U18" s="4">
-        <v>0</v>
-      </c>
-      <c r="V18" s="1">
+      <c r="R19" s="4">
+        <f t="shared" si="8"/>
+        <v>86</v>
+      </c>
+      <c r="S19" s="6">
+        <v>0</v>
+      </c>
+      <c r="T19" s="6">
+        <v>0</v>
+      </c>
+      <c r="U19" s="4">
+        <v>0</v>
+      </c>
+      <c r="V19" s="4">
+        <v>0</v>
+      </c>
+      <c r="W19" s="1">
         <f t="shared" si="0"/>
-        <v>850</v>
-      </c>
-      <c r="W18" s="1">
+        <v>860</v>
+      </c>
+      <c r="X19" s="1">
         <f t="shared" si="1"/>
-        <v>850</v>
-      </c>
-    </row>
-    <row r="19" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C19" s="1">
-        <v>86</v>
-      </c>
-      <c r="D19" s="1">
-        <v>86</v>
-      </c>
-      <c r="E19" s="1">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="20" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C20" s="1">
+        <v>87</v>
+      </c>
+      <c r="D20" s="1">
+        <v>87</v>
+      </c>
+      <c r="E20" s="1">
         <v>2</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G19" s="6">
-        <v>14</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="K19" s="2">
+      <c r="F20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="6">
+        <v>15</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="J20" s="6">
         <f t="shared" si="2"/>
-        <v>700</v>
-      </c>
-      <c r="L19" s="2">
+        <v>1.1992337164751</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="L20" s="2">
         <f t="shared" si="3"/>
-        <v>380</v>
-      </c>
-      <c r="M19" s="2">
+        <v>720</v>
+      </c>
+      <c r="M20" s="2">
         <f t="shared" si="4"/>
-        <v>186</v>
-      </c>
-      <c r="N19" s="2">
+        <v>390</v>
+      </c>
+      <c r="N20" s="2">
         <f t="shared" si="5"/>
-        <v>430</v>
-      </c>
-      <c r="O19" s="6">
-        <f t="shared" si="8"/>
+        <v>189</v>
+      </c>
+      <c r="O20" s="2">
+        <f t="shared" si="6"/>
+        <v>440</v>
+      </c>
+      <c r="P20" s="6">
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="P19" s="2">
-        <f t="shared" si="6"/>
-        <v>85</v>
-      </c>
-      <c r="Q19" s="4">
+      <c r="Q20" s="2">
         <f t="shared" si="7"/>
         <v>86</v>
       </c>
-      <c r="R19" s="6">
-        <v>0</v>
-      </c>
-      <c r="S19" s="6">
-        <v>0</v>
-      </c>
-      <c r="T19" s="4">
-        <v>0</v>
-      </c>
-      <c r="U19" s="4">
-        <v>0</v>
-      </c>
-      <c r="V19" s="1">
+      <c r="R20" s="4">
+        <f t="shared" si="8"/>
+        <v>87</v>
+      </c>
+      <c r="S20" s="6">
+        <v>0</v>
+      </c>
+      <c r="T20" s="6">
+        <v>0</v>
+      </c>
+      <c r="U20" s="4">
+        <v>0</v>
+      </c>
+      <c r="V20" s="4">
+        <v>0</v>
+      </c>
+      <c r="W20" s="1">
         <f t="shared" si="0"/>
-        <v>860</v>
-      </c>
-      <c r="W19" s="1">
+        <v>870</v>
+      </c>
+      <c r="X20" s="1">
         <f t="shared" si="1"/>
-        <v>860</v>
-      </c>
-    </row>
-    <row r="20" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C20" s="1">
-        <v>87</v>
-      </c>
-      <c r="D20" s="1">
-        <v>87</v>
-      </c>
-      <c r="E20" s="1">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="21" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C21" s="1">
+        <v>88</v>
+      </c>
+      <c r="D21" s="1">
+        <v>88</v>
+      </c>
+      <c r="E21" s="1">
         <v>2</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="F21" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="6">
+        <v>16</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="J21" s="6">
+        <f t="shared" si="2"/>
+        <v>1.19808306709265</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="L21" s="2">
+        <f t="shared" si="3"/>
+        <v>740</v>
+      </c>
+      <c r="M21" s="2">
+        <f t="shared" si="4"/>
+        <v>400</v>
+      </c>
+      <c r="N21" s="2">
+        <f t="shared" si="5"/>
+        <v>192</v>
+      </c>
+      <c r="O21" s="2">
+        <f t="shared" si="6"/>
+        <v>450</v>
+      </c>
+      <c r="P21" s="6">
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="H20" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="K20" s="2">
-        <f t="shared" si="2"/>
-        <v>720</v>
-      </c>
-      <c r="L20" s="2">
-        <f t="shared" si="3"/>
-        <v>390</v>
-      </c>
-      <c r="M20" s="2">
-        <f t="shared" si="4"/>
-        <v>189</v>
-      </c>
-      <c r="N20" s="2">
-        <f t="shared" si="5"/>
-        <v>440</v>
-      </c>
-      <c r="O20" s="6">
-        <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="P20" s="2">
-        <f t="shared" si="6"/>
-        <v>86</v>
-      </c>
-      <c r="Q20" s="4">
+      <c r="Q21" s="2">
         <f t="shared" si="7"/>
         <v>87</v>
       </c>
-      <c r="R20" s="6">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6">
-        <v>0</v>
-      </c>
-      <c r="T20" s="4">
-        <v>0</v>
-      </c>
-      <c r="U20" s="4">
-        <v>0</v>
-      </c>
-      <c r="V20" s="1">
+      <c r="R21" s="4">
+        <f t="shared" si="8"/>
+        <v>88</v>
+      </c>
+      <c r="S21" s="6">
+        <v>0</v>
+      </c>
+      <c r="T21" s="6">
+        <v>0</v>
+      </c>
+      <c r="U21" s="4">
+        <v>0</v>
+      </c>
+      <c r="V21" s="4">
+        <v>0</v>
+      </c>
+      <c r="W21" s="1">
         <f t="shared" si="0"/>
-        <v>870</v>
-      </c>
-      <c r="W20" s="1">
+        <v>880</v>
+      </c>
+      <c r="X21" s="1">
         <f t="shared" si="1"/>
-        <v>870</v>
-      </c>
-    </row>
-    <row r="21" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C21" s="1">
-        <v>88</v>
-      </c>
-      <c r="D21" s="1">
-        <v>88</v>
-      </c>
-      <c r="E21" s="1">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="22" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C22" s="1">
+        <v>89</v>
+      </c>
+      <c r="D22" s="1">
+        <v>89</v>
+      </c>
+      <c r="E22" s="1">
         <v>2</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G21" s="6">
-        <v>16</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="K21" s="2">
+      <c r="F22" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="6">
+        <v>17</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="J22" s="6">
         <f t="shared" si="2"/>
-        <v>740</v>
-      </c>
-      <c r="L21" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="L22" s="2">
         <f t="shared" si="3"/>
-        <v>400</v>
-      </c>
-      <c r="M21" s="2">
+        <v>760</v>
+      </c>
+      <c r="M22" s="2">
         <f t="shared" si="4"/>
-        <v>192</v>
-      </c>
-      <c r="N21" s="2">
+        <v>410</v>
+      </c>
+      <c r="N22" s="2">
         <f t="shared" si="5"/>
-        <v>450</v>
-      </c>
-      <c r="O21" s="6">
-        <f t="shared" si="8"/>
+        <v>195</v>
+      </c>
+      <c r="O22" s="2">
+        <f t="shared" si="6"/>
+        <v>460</v>
+      </c>
+      <c r="P22" s="6">
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="P21" s="2">
-        <f t="shared" si="6"/>
-        <v>87</v>
-      </c>
-      <c r="Q21" s="4">
+      <c r="Q22" s="2">
         <f t="shared" si="7"/>
         <v>88</v>
       </c>
-      <c r="R21" s="6">
-        <v>0</v>
-      </c>
-      <c r="S21" s="6">
-        <v>0</v>
-      </c>
-      <c r="T21" s="4">
-        <v>0</v>
-      </c>
-      <c r="U21" s="4">
-        <v>0</v>
-      </c>
-      <c r="V21" s="1">
+      <c r="R22" s="4">
+        <f t="shared" si="8"/>
+        <v>89</v>
+      </c>
+      <c r="S22" s="6">
+        <v>0</v>
+      </c>
+      <c r="T22" s="6">
+        <v>0</v>
+      </c>
+      <c r="U22" s="4">
+        <v>0</v>
+      </c>
+      <c r="V22" s="4">
+        <v>0</v>
+      </c>
+      <c r="W22" s="1">
         <f t="shared" si="0"/>
-        <v>880</v>
-      </c>
-      <c r="W21" s="1">
+        <v>890</v>
+      </c>
+      <c r="X22" s="1">
         <f t="shared" si="1"/>
-        <v>880</v>
-      </c>
-    </row>
-    <row r="22" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C22" s="1">
-        <v>89</v>
-      </c>
-      <c r="D22" s="1">
-        <v>89</v>
-      </c>
-      <c r="E22" s="1">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="23" s="3" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C23" s="1">
+        <v>90</v>
+      </c>
+      <c r="D23" s="1">
+        <v>90</v>
+      </c>
+      <c r="E23" s="1">
         <v>2</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22" s="6">
-        <v>17</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="J22" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="K22" s="2">
+      <c r="F23" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="5">
+        <v>18</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>164</v>
+      </c>
+      <c r="J23" s="6">
         <f t="shared" si="2"/>
-        <v>760</v>
-      </c>
-      <c r="L22" s="2">
+        <v>1.32</v>
+      </c>
+      <c r="K23" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="L23" s="2">
         <f t="shared" si="3"/>
-        <v>410</v>
-      </c>
-      <c r="M22" s="2">
+        <v>780</v>
+      </c>
+      <c r="M23" s="2">
         <f t="shared" si="4"/>
-        <v>195</v>
-      </c>
-      <c r="N22" s="2">
+        <v>420</v>
+      </c>
+      <c r="N23" s="2">
         <f t="shared" si="5"/>
-        <v>460</v>
-      </c>
-      <c r="O22" s="6">
-        <f t="shared" si="8"/>
+        <v>198</v>
+      </c>
+      <c r="O23" s="2">
+        <f t="shared" si="6"/>
+        <v>470</v>
+      </c>
+      <c r="P23" s="6">
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="P22" s="2">
-        <f t="shared" si="6"/>
-        <v>88</v>
-      </c>
-      <c r="Q22" s="4">
+      <c r="Q23" s="2">
         <f t="shared" si="7"/>
         <v>89</v>
       </c>
-      <c r="R22" s="6">
-        <v>0</v>
-      </c>
-      <c r="S22" s="6">
-        <v>0</v>
-      </c>
-      <c r="T22" s="4">
-        <v>0</v>
-      </c>
-      <c r="U22" s="4">
-        <v>0</v>
-      </c>
-      <c r="V22" s="1">
+      <c r="R23" s="3">
+        <f t="shared" si="8"/>
+        <v>90</v>
+      </c>
+      <c r="S23" s="5">
+        <v>0</v>
+      </c>
+      <c r="T23" s="5">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="1">
         <f t="shared" si="0"/>
-        <v>890</v>
-      </c>
-      <c r="W22" s="1">
+        <v>900</v>
+      </c>
+      <c r="X23" s="1">
         <f t="shared" si="1"/>
-        <v>890</v>
-      </c>
-    </row>
-    <row r="23" s="3" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C23" s="1">
-        <v>90</v>
-      </c>
-      <c r="D23" s="1">
-        <v>90</v>
-      </c>
-      <c r="E23" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="24" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C24" s="1">
+        <v>91</v>
+      </c>
+      <c r="D24" s="1">
+        <v>91</v>
+      </c>
+      <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23" s="5">
-        <v>18</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="J23" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="K23" s="2">
+      <c r="F24" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="6">
+        <v>19</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="J24" s="6">
         <f t="shared" si="2"/>
-        <v>780</v>
-      </c>
-      <c r="L23" s="2">
+        <v>1.30808080808081</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="L24" s="2">
         <f t="shared" si="3"/>
-        <v>420</v>
-      </c>
-      <c r="M23" s="2">
+        <v>800</v>
+      </c>
+      <c r="M24" s="2">
         <f t="shared" si="4"/>
-        <v>198</v>
-      </c>
-      <c r="N23" s="2">
+        <v>430</v>
+      </c>
+      <c r="N24" s="2">
         <f t="shared" si="5"/>
-        <v>470</v>
-      </c>
-      <c r="O23" s="6">
-        <f t="shared" si="8"/>
-        <v>15</v>
-      </c>
-      <c r="P23" s="2">
+        <v>201</v>
+      </c>
+      <c r="O24" s="2">
         <f t="shared" si="6"/>
-        <v>89</v>
-      </c>
-      <c r="Q23" s="3">
+        <v>480</v>
+      </c>
+      <c r="P24" s="6">
+        <f t="shared" si="9"/>
+        <v>16</v>
+      </c>
+      <c r="Q24" s="2">
         <f t="shared" si="7"/>
         <v>90</v>
       </c>
-      <c r="R23" s="5">
-        <v>0</v>
-      </c>
-      <c r="S23" s="5">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="1">
+      <c r="R24" s="4">
+        <f t="shared" si="8"/>
+        <v>91</v>
+      </c>
+      <c r="S24" s="6">
+        <v>0</v>
+      </c>
+      <c r="T24" s="6">
+        <v>0</v>
+      </c>
+      <c r="U24" s="4">
+        <v>0</v>
+      </c>
+      <c r="V24" s="4">
+        <v>0</v>
+      </c>
+      <c r="W24" s="1">
         <f t="shared" si="0"/>
-        <v>900</v>
-      </c>
-      <c r="W23" s="1">
+        <v>910</v>
+      </c>
+      <c r="X24" s="1">
         <f t="shared" si="1"/>
-        <v>900</v>
-      </c>
-    </row>
-    <row r="24" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C24" s="1">
-        <v>91</v>
-      </c>
-      <c r="D24" s="1">
-        <v>91</v>
-      </c>
-      <c r="E24" s="1">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="25" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C25" s="1">
+        <v>92</v>
+      </c>
+      <c r="D25" s="1">
+        <v>92</v>
+      </c>
+      <c r="E25" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24" s="6">
-        <v>19</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="K24" s="2">
+      <c r="F25" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G25" s="6">
+        <v>20</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="J25" s="6">
         <f t="shared" si="2"/>
-        <v>800</v>
-      </c>
-      <c r="L24" s="2">
+        <v>1.2998712998713</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="L25" s="2">
         <f t="shared" si="3"/>
-        <v>430</v>
-      </c>
-      <c r="M24" s="2">
+        <v>820</v>
+      </c>
+      <c r="M25" s="2">
         <f t="shared" si="4"/>
-        <v>201</v>
-      </c>
-      <c r="N24" s="2">
+        <v>440</v>
+      </c>
+      <c r="N25" s="2">
         <f t="shared" si="5"/>
-        <v>480</v>
-      </c>
-      <c r="O24" s="6">
-        <f t="shared" si="8"/>
+        <v>204</v>
+      </c>
+      <c r="O25" s="2">
+        <f t="shared" si="6"/>
+        <v>490</v>
+      </c>
+      <c r="P25" s="6">
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="P24" s="2">
-        <f t="shared" si="6"/>
-        <v>90</v>
-      </c>
-      <c r="Q24" s="4">
+      <c r="Q25" s="2">
         <f t="shared" si="7"/>
         <v>91</v>
       </c>
-      <c r="R24" s="6">
-        <v>0</v>
-      </c>
-      <c r="S24" s="6">
-        <v>0</v>
-      </c>
-      <c r="T24" s="4">
-        <v>0</v>
-      </c>
-      <c r="U24" s="4">
-        <v>0</v>
-      </c>
-      <c r="V24" s="1">
+      <c r="R25" s="4">
+        <f t="shared" si="8"/>
+        <v>92</v>
+      </c>
+      <c r="S25" s="6">
+        <v>0</v>
+      </c>
+      <c r="T25" s="6">
+        <v>0</v>
+      </c>
+      <c r="U25" s="4">
+        <v>0</v>
+      </c>
+      <c r="V25" s="4">
+        <v>0</v>
+      </c>
+      <c r="W25" s="1">
         <f t="shared" si="0"/>
-        <v>910</v>
-      </c>
-      <c r="W24" s="1">
+        <v>920</v>
+      </c>
+      <c r="X25" s="1">
         <f t="shared" si="1"/>
-        <v>910</v>
-      </c>
-    </row>
-    <row r="25" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C25" s="1">
-        <v>92</v>
-      </c>
-      <c r="D25" s="1">
-        <v>92</v>
-      </c>
-      <c r="E25" s="1">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="26" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C26" s="1">
+        <v>93</v>
+      </c>
+      <c r="D26" s="1">
+        <v>93</v>
+      </c>
+      <c r="E26" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G25" s="6">
-        <v>20</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="J25" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="K25" s="2">
+      <c r="F26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26" s="6">
+        <v>21</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="J26" s="6">
         <f t="shared" si="2"/>
-        <v>820</v>
-      </c>
-      <c r="L25" s="2">
+        <v>1.28712871287129</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="L26" s="2">
         <f t="shared" si="3"/>
-        <v>440</v>
-      </c>
-      <c r="M25" s="2">
+        <v>840</v>
+      </c>
+      <c r="M26" s="2">
         <f t="shared" si="4"/>
-        <v>204</v>
-      </c>
-      <c r="N25" s="2">
+        <v>450</v>
+      </c>
+      <c r="N26" s="2">
         <f t="shared" si="5"/>
-        <v>490</v>
-      </c>
-      <c r="O25" s="6">
-        <f t="shared" si="8"/>
+        <v>207</v>
+      </c>
+      <c r="O26" s="2">
+        <f t="shared" si="6"/>
+        <v>500</v>
+      </c>
+      <c r="P26" s="6">
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="P25" s="2">
-        <f t="shared" si="6"/>
-        <v>91</v>
-      </c>
-      <c r="Q25" s="4">
+      <c r="Q26" s="2">
         <f t="shared" si="7"/>
         <v>92</v>
       </c>
-      <c r="R25" s="6">
-        <v>0</v>
-      </c>
-      <c r="S25" s="6">
-        <v>0</v>
-      </c>
-      <c r="T25" s="4">
-        <v>0</v>
-      </c>
-      <c r="U25" s="4">
-        <v>0</v>
-      </c>
-      <c r="V25" s="1">
+      <c r="R26" s="4">
+        <f t="shared" si="8"/>
+        <v>93</v>
+      </c>
+      <c r="S26" s="6">
+        <v>0</v>
+      </c>
+      <c r="T26" s="6">
+        <v>0</v>
+      </c>
+      <c r="U26" s="4">
+        <v>0</v>
+      </c>
+      <c r="V26" s="4">
+        <v>0</v>
+      </c>
+      <c r="W26" s="1">
         <f t="shared" si="0"/>
-        <v>920</v>
-      </c>
-      <c r="W25" s="1">
+        <v>930</v>
+      </c>
+      <c r="X26" s="1">
         <f t="shared" si="1"/>
-        <v>920</v>
-      </c>
-    </row>
-    <row r="26" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C26" s="1">
-        <v>93</v>
-      </c>
-      <c r="D26" s="1">
-        <v>93</v>
-      </c>
-      <c r="E26" s="1">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="27" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C27" s="1">
+        <v>94</v>
+      </c>
+      <c r="D27" s="1">
+        <v>94</v>
+      </c>
+      <c r="E27" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G26" s="6">
-        <v>21</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="J26" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="K26" s="2">
+      <c r="F27" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27" s="6">
+        <v>22</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="J27" s="6">
         <f t="shared" si="2"/>
-        <v>840</v>
-      </c>
-      <c r="L26" s="2">
+        <v>1.27692307692308</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="L27" s="2">
         <f t="shared" si="3"/>
-        <v>450</v>
-      </c>
-      <c r="M26" s="2">
+        <v>860</v>
+      </c>
+      <c r="M27" s="2">
         <f t="shared" si="4"/>
-        <v>207</v>
-      </c>
-      <c r="N26" s="2">
+        <v>460</v>
+      </c>
+      <c r="N27" s="2">
         <f t="shared" si="5"/>
-        <v>500</v>
-      </c>
-      <c r="O26" s="6">
-        <f t="shared" si="8"/>
+        <v>210</v>
+      </c>
+      <c r="O27" s="2">
+        <f t="shared" si="6"/>
+        <v>510</v>
+      </c>
+      <c r="P27" s="6">
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="P26" s="2">
-        <f t="shared" si="6"/>
-        <v>92</v>
-      </c>
-      <c r="Q26" s="4">
+      <c r="Q27" s="2">
         <f t="shared" si="7"/>
         <v>93</v>
       </c>
-      <c r="R26" s="6">
-        <v>0</v>
-      </c>
-      <c r="S26" s="6">
-        <v>0</v>
-      </c>
-      <c r="T26" s="4">
-        <v>0</v>
-      </c>
-      <c r="U26" s="4">
-        <v>0</v>
-      </c>
-      <c r="V26" s="1">
+      <c r="R27" s="4">
+        <f t="shared" si="8"/>
+        <v>94</v>
+      </c>
+      <c r="S27" s="6">
+        <v>0</v>
+      </c>
+      <c r="T27" s="6">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4">
+        <v>0</v>
+      </c>
+      <c r="V27" s="4">
+        <v>0</v>
+      </c>
+      <c r="W27" s="1">
         <f t="shared" si="0"/>
-        <v>930</v>
-      </c>
-      <c r="W26" s="1">
+        <v>940</v>
+      </c>
+      <c r="X27" s="1">
         <f t="shared" si="1"/>
-        <v>930</v>
-      </c>
-    </row>
-    <row r="27" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C27" s="1">
-        <v>94</v>
-      </c>
-      <c r="D27" s="1">
-        <v>94</v>
-      </c>
-      <c r="E27" s="1">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="28" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C28" s="1">
+        <v>95</v>
+      </c>
+      <c r="D28" s="1">
+        <v>95</v>
+      </c>
+      <c r="E28" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27" s="6">
-        <v>22</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="K27" s="2">
+      <c r="F28" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" s="6">
+        <v>23</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="J28" s="6">
         <f t="shared" si="2"/>
-        <v>860</v>
-      </c>
-      <c r="L27" s="2">
+        <v>1.28313253012048</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="L28" s="2">
         <f t="shared" si="3"/>
-        <v>460</v>
-      </c>
-      <c r="M27" s="2">
+        <v>880</v>
+      </c>
+      <c r="M28" s="2">
         <f t="shared" si="4"/>
-        <v>210</v>
-      </c>
-      <c r="N27" s="2">
+        <v>470</v>
+      </c>
+      <c r="N28" s="2">
         <f t="shared" si="5"/>
-        <v>510</v>
-      </c>
-      <c r="O27" s="6">
-        <f t="shared" si="8"/>
+        <v>213</v>
+      </c>
+      <c r="O28" s="2">
+        <f t="shared" si="6"/>
+        <v>520</v>
+      </c>
+      <c r="P28" s="6">
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="P27" s="2">
-        <f t="shared" si="6"/>
-        <v>93</v>
-      </c>
-      <c r="Q27" s="4">
+      <c r="Q28" s="2">
         <f t="shared" si="7"/>
         <v>94</v>
       </c>
-      <c r="R27" s="6">
-        <v>0</v>
-      </c>
-      <c r="S27" s="6">
-        <v>0</v>
-      </c>
-      <c r="T27" s="4">
-        <v>0</v>
-      </c>
-      <c r="U27" s="4">
-        <v>0</v>
-      </c>
-      <c r="V27" s="1">
+      <c r="R28" s="4">
+        <f t="shared" si="8"/>
+        <v>95</v>
+      </c>
+      <c r="S28" s="6">
+        <v>0</v>
+      </c>
+      <c r="T28" s="6">
+        <v>0</v>
+      </c>
+      <c r="U28" s="4">
+        <v>0</v>
+      </c>
+      <c r="V28" s="4">
+        <v>0</v>
+      </c>
+      <c r="W28" s="1">
         <f t="shared" si="0"/>
-        <v>940</v>
-      </c>
-      <c r="W27" s="1">
+        <v>950</v>
+      </c>
+      <c r="X28" s="1">
         <f t="shared" si="1"/>
-        <v>940</v>
-      </c>
-    </row>
-    <row r="28" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C28" s="1">
-        <v>95</v>
-      </c>
-      <c r="D28" s="1">
-        <v>95</v>
-      </c>
-      <c r="E28" s="1">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C29" s="1">
+        <v>96</v>
+      </c>
+      <c r="D29" s="1">
+        <v>96</v>
+      </c>
+      <c r="E29" s="1">
         <v>2</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G28" s="6">
-        <v>23</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="J28" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="K28" s="2">
+      <c r="F29" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G29" s="5">
+        <v>24</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="J29" s="6">
         <f t="shared" si="2"/>
-        <v>880</v>
-      </c>
-      <c r="L28" s="2">
+        <v>1.26760563380282</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="L29" s="2">
         <f t="shared" si="3"/>
-        <v>470</v>
-      </c>
-      <c r="M28" s="2">
+        <v>900</v>
+      </c>
+      <c r="M29" s="2">
         <f t="shared" si="4"/>
-        <v>213</v>
-      </c>
-      <c r="N28" s="2">
+        <v>480</v>
+      </c>
+      <c r="N29" s="2">
         <f t="shared" si="5"/>
-        <v>520</v>
-      </c>
-      <c r="O28" s="6">
-        <f t="shared" si="8"/>
+        <v>216</v>
+      </c>
+      <c r="O29" s="2">
+        <f t="shared" si="6"/>
+        <v>530</v>
+      </c>
+      <c r="P29" s="6">
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="P28" s="2">
-        <f t="shared" si="6"/>
-        <v>94</v>
-      </c>
-      <c r="Q28" s="4">
+      <c r="Q29" s="2">
         <f t="shared" si="7"/>
         <v>95</v>
       </c>
-      <c r="R28" s="6">
-        <v>0</v>
-      </c>
-      <c r="S28" s="6">
-        <v>0</v>
-      </c>
-      <c r="T28" s="4">
-        <v>0</v>
-      </c>
-      <c r="U28" s="4">
-        <v>0</v>
-      </c>
-      <c r="V28" s="1">
+      <c r="R29" s="3">
+        <f t="shared" si="8"/>
+        <v>96</v>
+      </c>
+      <c r="S29" s="5">
+        <v>0</v>
+      </c>
+      <c r="T29" s="5">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="1">
         <f t="shared" si="0"/>
-        <v>950</v>
-      </c>
-      <c r="W28" s="1">
+        <v>960</v>
+      </c>
+      <c r="X29" s="1">
         <f t="shared" si="1"/>
-        <v>950</v>
-      </c>
-    </row>
-    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C29" s="1">
-        <v>96</v>
-      </c>
-      <c r="D29" s="1">
-        <v>96</v>
-      </c>
-      <c r="E29" s="1">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="30" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C30" s="1">
+        <v>97</v>
+      </c>
+      <c r="D30" s="1">
+        <v>97</v>
+      </c>
+      <c r="E30" s="1">
         <v>2</v>
       </c>
-      <c r="F29" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G29" s="5">
-        <v>24</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="K29" s="2">
+      <c r="F30" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="6">
+        <v>25</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="J30" s="6">
         <f t="shared" si="2"/>
-        <v>900</v>
-      </c>
-      <c r="L29" s="2">
+        <v>1.27037037037037</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="L30" s="2">
         <f t="shared" si="3"/>
-        <v>480</v>
-      </c>
-      <c r="M29" s="2">
+        <v>920</v>
+      </c>
+      <c r="M30" s="2">
         <f t="shared" si="4"/>
-        <v>216</v>
-      </c>
-      <c r="N29" s="2">
+        <v>490</v>
+      </c>
+      <c r="N30" s="2">
         <f t="shared" si="5"/>
-        <v>530</v>
-      </c>
-      <c r="O29" s="6">
-        <f t="shared" si="8"/>
-        <v>16</v>
-      </c>
-      <c r="P29" s="2">
+        <v>219</v>
+      </c>
+      <c r="O30" s="2">
         <f t="shared" si="6"/>
-        <v>95</v>
-      </c>
-      <c r="Q29" s="3">
+        <v>540</v>
+      </c>
+      <c r="P30" s="6">
+        <f t="shared" si="9"/>
+        <v>17</v>
+      </c>
+      <c r="Q30" s="2">
         <f t="shared" si="7"/>
         <v>96</v>
       </c>
-      <c r="R29" s="5">
-        <v>0</v>
-      </c>
-      <c r="S29" s="5">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="1">
+      <c r="R30" s="4">
+        <f t="shared" si="8"/>
+        <v>97</v>
+      </c>
+      <c r="S30" s="6">
+        <v>0</v>
+      </c>
+      <c r="T30" s="6">
+        <v>0</v>
+      </c>
+      <c r="U30" s="4">
+        <v>0</v>
+      </c>
+      <c r="V30" s="4">
+        <v>0</v>
+      </c>
+      <c r="W30" s="1">
         <f t="shared" si="0"/>
-        <v>960</v>
-      </c>
-      <c r="W29" s="1">
+        <v>970</v>
+      </c>
+      <c r="X30" s="1">
         <f t="shared" si="1"/>
-        <v>960</v>
-      </c>
-    </row>
-    <row r="30" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C30" s="1">
-        <v>97</v>
-      </c>
-      <c r="D30" s="1">
-        <v>97</v>
-      </c>
-      <c r="E30" s="1">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="31" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C31" s="1">
+        <v>98</v>
+      </c>
+      <c r="D31" s="1">
+        <v>98</v>
+      </c>
+      <c r="E31" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30" s="6">
-        <v>25</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="I30" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="K30" s="2">
+      <c r="F31" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G31" s="6">
+        <v>26</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="J31" s="6">
         <f t="shared" si="2"/>
-        <v>920</v>
-      </c>
-      <c r="L30" s="2">
+        <v>1.26822157434402</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="L31" s="2">
         <f t="shared" si="3"/>
-        <v>490</v>
-      </c>
-      <c r="M30" s="2">
+        <v>940</v>
+      </c>
+      <c r="M31" s="2">
         <f t="shared" si="4"/>
-        <v>219</v>
-      </c>
-      <c r="N30" s="2">
+        <v>500</v>
+      </c>
+      <c r="N31" s="2">
         <f t="shared" si="5"/>
-        <v>540</v>
-      </c>
-      <c r="O30" s="6">
-        <f t="shared" si="8"/>
+        <v>222</v>
+      </c>
+      <c r="O31" s="2">
+        <f t="shared" si="6"/>
+        <v>550</v>
+      </c>
+      <c r="P31" s="6">
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="P30" s="2">
-        <f t="shared" si="6"/>
-        <v>96</v>
-      </c>
-      <c r="Q30" s="4">
+      <c r="Q31" s="2">
         <f t="shared" si="7"/>
         <v>97</v>
       </c>
-      <c r="R30" s="6">
-        <v>0</v>
-      </c>
-      <c r="S30" s="6">
-        <v>0</v>
-      </c>
-      <c r="T30" s="4">
-        <v>0</v>
-      </c>
-      <c r="U30" s="4">
-        <v>0</v>
-      </c>
-      <c r="V30" s="1">
+      <c r="R31" s="4">
+        <f t="shared" si="8"/>
+        <v>98</v>
+      </c>
+      <c r="S31" s="6">
+        <v>0</v>
+      </c>
+      <c r="T31" s="6">
+        <v>0</v>
+      </c>
+      <c r="U31" s="4">
+        <v>0</v>
+      </c>
+      <c r="V31" s="4">
+        <v>0</v>
+      </c>
+      <c r="W31" s="1">
         <f t="shared" si="0"/>
-        <v>970</v>
-      </c>
-      <c r="W30" s="1">
+        <v>980</v>
+      </c>
+      <c r="X31" s="1">
         <f t="shared" si="1"/>
-        <v>970</v>
-      </c>
-    </row>
-    <row r="31" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C31" s="1">
-        <v>98</v>
-      </c>
-      <c r="D31" s="1">
-        <v>98</v>
-      </c>
-      <c r="E31" s="1">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="32" s="4" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C32" s="1">
+        <v>99</v>
+      </c>
+      <c r="D32" s="1">
+        <v>99</v>
+      </c>
+      <c r="E32" s="1">
         <v>2</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31" s="6">
-        <v>26</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="J31" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="K31" s="2">
+      <c r="F32" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="G32" s="6">
+        <v>27</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="J32" s="6">
         <f t="shared" si="2"/>
-        <v>940</v>
-      </c>
-      <c r="L31" s="2">
+        <v>1.25977011494253</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="L32" s="2">
         <f t="shared" si="3"/>
-        <v>500</v>
-      </c>
-      <c r="M31" s="2">
+        <v>960</v>
+      </c>
+      <c r="M32" s="2">
         <f t="shared" si="4"/>
-        <v>222</v>
-      </c>
-      <c r="N31" s="2">
+        <v>510</v>
+      </c>
+      <c r="N32" s="2">
         <f t="shared" si="5"/>
-        <v>550</v>
-      </c>
-      <c r="O31" s="6">
-        <f t="shared" si="8"/>
+        <v>225</v>
+      </c>
+      <c r="O32" s="2">
+        <f t="shared" si="6"/>
+        <v>560</v>
+      </c>
+      <c r="P32" s="6">
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="P31" s="2">
-        <f t="shared" si="6"/>
-        <v>97</v>
-      </c>
-      <c r="Q31" s="4">
+      <c r="Q32" s="2">
         <f t="shared" si="7"/>
         <v>98</v>
       </c>
-      <c r="R31" s="6">
-        <v>0</v>
-      </c>
-      <c r="S31" s="6">
-        <v>0</v>
-      </c>
-      <c r="T31" s="4">
-        <v>0</v>
-      </c>
-      <c r="U31" s="4">
-        <v>0</v>
-      </c>
-      <c r="V31" s="1">
+      <c r="R32" s="4">
+        <f t="shared" si="8"/>
+        <v>99</v>
+      </c>
+      <c r="S32" s="6">
+        <v>0</v>
+      </c>
+      <c r="T32" s="6">
+        <v>0</v>
+      </c>
+      <c r="U32" s="4">
+        <v>0</v>
+      </c>
+      <c r="V32" s="4">
+        <v>0</v>
+      </c>
+      <c r="W32" s="1">
         <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="X32" s="1">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="33" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C33" s="1">
+        <v>100</v>
+      </c>
+      <c r="D33" s="1">
+        <v>100</v>
+      </c>
+      <c r="E33" s="1">
+        <v>2</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G33" s="6">
+        <v>28</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="I33" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="J33" s="6">
+        <f t="shared" si="2"/>
+        <v>1.26094890510949</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="L33" s="2">
+        <f t="shared" si="3"/>
         <v>980</v>
       </c>
-      <c r="W31" s="1">
-        <f t="shared" si="1"/>
-        <v>980</v>
-      </c>
-    </row>
-    <row r="32" s="4" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C32" s="1">
-        <v>99</v>
-      </c>
-      <c r="D32" s="1">
-        <v>99</v>
-      </c>
-      <c r="E32" s="1">
-        <v>2</v>
-      </c>
-      <c r="F32" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G32" s="6">
-        <v>27</v>
-      </c>
-      <c r="H32" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="I32" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="J32" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="K32" s="2">
-        <f t="shared" si="2"/>
-        <v>960</v>
-      </c>
-      <c r="L32" s="2">
-        <f t="shared" si="3"/>
-        <v>510</v>
-      </c>
-      <c r="M32" s="2">
+      <c r="M33" s="2">
         <f t="shared" si="4"/>
-        <v>225</v>
-      </c>
-      <c r="N32" s="2">
+        <v>520</v>
+      </c>
+      <c r="N33" s="2">
         <f t="shared" si="5"/>
-        <v>560</v>
-      </c>
-      <c r="O32" s="6">
-        <f t="shared" si="8"/>
+        <v>228</v>
+      </c>
+      <c r="O33" s="2">
+        <f t="shared" si="6"/>
+        <v>570</v>
+      </c>
+      <c r="P33" s="6">
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="P32" s="2">
-        <f t="shared" si="6"/>
-        <v>98</v>
-      </c>
-      <c r="Q32" s="4">
+      <c r="Q33" s="2">
         <f t="shared" si="7"/>
         <v>99</v>
       </c>
-      <c r="R32" s="6">
-        <v>0</v>
-      </c>
-      <c r="S32" s="6">
-        <v>0</v>
-      </c>
-      <c r="T32" s="4">
-        <v>0</v>
-      </c>
-      <c r="U32" s="4">
-        <v>0</v>
-      </c>
-      <c r="V32" s="1">
+      <c r="R33" s="4">
+        <f t="shared" si="8"/>
+        <v>100</v>
+      </c>
+      <c r="S33" s="6">
+        <v>0</v>
+      </c>
+      <c r="T33" s="6">
+        <v>0</v>
+      </c>
+      <c r="U33" s="4">
+        <v>0</v>
+      </c>
+      <c r="V33" s="4">
+        <v>0</v>
+      </c>
+      <c r="W33" s="1">
         <f t="shared" si="0"/>
-        <v>990</v>
-      </c>
-      <c r="W32" s="1">
+        <v>1000</v>
+      </c>
+      <c r="X33" s="1">
         <f t="shared" si="1"/>
-        <v>990</v>
-      </c>
-    </row>
-    <row r="33" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C33" s="1">
-        <v>100</v>
-      </c>
-      <c r="D33" s="1">
-        <v>100</v>
-      </c>
-      <c r="E33" s="1">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="34" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C34" s="1">
+        <v>101</v>
+      </c>
+      <c r="D34" s="1">
+        <v>101</v>
+      </c>
+      <c r="E34" s="1">
         <v>2</v>
       </c>
-      <c r="F33" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G33" s="6">
-        <v>28</v>
-      </c>
-      <c r="H33" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="I33" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="J33" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="K33" s="2">
+      <c r="F34" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G34" s="6">
+        <v>29</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="I34" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="J34" s="6">
         <f t="shared" si="2"/>
-        <v>980</v>
-      </c>
-      <c r="L33" s="2">
+        <v>1.25904486251809</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="L34" s="2">
         <f t="shared" si="3"/>
-        <v>520</v>
-      </c>
-      <c r="M33" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M34" s="2">
         <f t="shared" si="4"/>
-        <v>228</v>
-      </c>
-      <c r="N33" s="2">
+        <v>530</v>
+      </c>
+      <c r="N34" s="2">
         <f t="shared" si="5"/>
-        <v>570</v>
-      </c>
-      <c r="O33" s="6">
-        <f t="shared" si="8"/>
+        <v>231</v>
+      </c>
+      <c r="O34" s="2">
+        <f t="shared" si="6"/>
+        <v>580</v>
+      </c>
+      <c r="P34" s="6">
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="P33" s="2">
-        <f t="shared" si="6"/>
-        <v>99</v>
-      </c>
-      <c r="Q33" s="4">
+      <c r="Q34" s="2">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="R33" s="6">
-        <v>0</v>
-      </c>
-      <c r="S33" s="6">
-        <v>0</v>
-      </c>
-      <c r="T33" s="4">
-        <v>0</v>
-      </c>
-      <c r="U33" s="4">
-        <v>0</v>
-      </c>
-      <c r="V33" s="1">
+      <c r="R34" s="4">
+        <f t="shared" si="8"/>
+        <v>101</v>
+      </c>
+      <c r="S34" s="6">
+        <v>0</v>
+      </c>
+      <c r="T34" s="6">
+        <v>0</v>
+      </c>
+      <c r="U34" s="4">
+        <v>0</v>
+      </c>
+      <c r="V34" s="4">
+        <v>0</v>
+      </c>
+      <c r="W34" s="1">
         <f t="shared" si="0"/>
-        <v>1000</v>
-      </c>
-      <c r="W33" s="1">
+        <v>1010</v>
+      </c>
+      <c r="X34" s="1">
         <f t="shared" si="1"/>
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="34" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C34" s="1">
-        <v>101</v>
-      </c>
-      <c r="D34" s="1">
-        <v>101</v>
-      </c>
-      <c r="E34" s="1">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="35" s="3" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C35" s="1">
+        <v>102</v>
+      </c>
+      <c r="D35" s="1">
+        <v>102</v>
+      </c>
+      <c r="E35" s="1">
         <v>2</v>
       </c>
-      <c r="F34" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="G34" s="6">
-        <v>29</v>
-      </c>
-      <c r="H34" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="I34" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="J34" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="K34" s="2">
+      <c r="F35" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" s="5">
+        <v>30</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="I35" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="J35" s="6">
         <f t="shared" si="2"/>
-        <v>1000</v>
-      </c>
-      <c r="L34" s="2">
+        <v>1.25287356321839</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="L35" s="2">
         <f t="shared" si="3"/>
-        <v>530</v>
-      </c>
-      <c r="M34" s="2">
+        <v>1020</v>
+      </c>
+      <c r="M35" s="2">
         <f t="shared" si="4"/>
-        <v>231</v>
-      </c>
-      <c r="N34" s="2">
+        <v>540</v>
+      </c>
+      <c r="N35" s="2">
         <f t="shared" si="5"/>
-        <v>580</v>
-      </c>
-      <c r="O34" s="6">
-        <f t="shared" si="8"/>
+        <v>234</v>
+      </c>
+      <c r="O35" s="2">
+        <f t="shared" si="6"/>
+        <v>590</v>
+      </c>
+      <c r="P35" s="6">
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="P34" s="2">
-        <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="Q34" s="4">
+      <c r="Q35" s="2">
         <f t="shared" si="7"/>
         <v>101</v>
       </c>
-      <c r="R34" s="6">
-        <v>0</v>
-      </c>
-      <c r="S34" s="6">
-        <v>0</v>
-      </c>
-      <c r="T34" s="4">
-        <v>0</v>
-      </c>
-      <c r="U34" s="4">
-        <v>0</v>
-      </c>
-      <c r="V34" s="1">
+      <c r="R35" s="3">
+        <f t="shared" si="8"/>
+        <v>102</v>
+      </c>
+      <c r="S35" s="5">
+        <v>0</v>
+      </c>
+      <c r="T35" s="5">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="1">
         <f t="shared" si="0"/>
-        <v>1010</v>
-      </c>
-      <c r="W34" s="1">
+        <v>1020</v>
+      </c>
+      <c r="X35" s="1">
         <f t="shared" si="1"/>
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="35" s="3" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C35" s="1">
-        <v>102</v>
-      </c>
-      <c r="D35" s="1">
-        <v>102</v>
-      </c>
-      <c r="E35" s="1">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="36" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C36" s="1">
+        <v>103</v>
+      </c>
+      <c r="D36" s="1">
+        <v>103</v>
+      </c>
+      <c r="E36" s="1">
         <v>2</v>
       </c>
-      <c r="F35" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G35" s="5">
-        <v>30</v>
-      </c>
-      <c r="H35" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="I35" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="J35" s="13" t="s">
+      <c r="F36" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G36" s="6">
+        <v>31</v>
+      </c>
+      <c r="H36" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="K35" s="2">
+      <c r="I36" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="J36" s="6">
         <f t="shared" si="2"/>
-        <v>1020</v>
-      </c>
-      <c r="L35" s="2">
+        <v>1.24770642201835</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="L36" s="2">
         <f t="shared" si="3"/>
-        <v>540</v>
-      </c>
-      <c r="M35" s="2">
+        <v>1040</v>
+      </c>
+      <c r="M36" s="2">
         <f t="shared" si="4"/>
-        <v>234</v>
-      </c>
-      <c r="N35" s="2">
+        <v>550</v>
+      </c>
+      <c r="N36" s="2">
         <f t="shared" si="5"/>
-        <v>590</v>
-      </c>
-      <c r="O35" s="6">
-        <f t="shared" si="8"/>
-        <v>17</v>
-      </c>
-      <c r="P35" s="2">
+        <v>237</v>
+      </c>
+      <c r="O36" s="2">
         <f t="shared" si="6"/>
-        <v>101</v>
-      </c>
-      <c r="Q35" s="3">
+        <v>600</v>
+      </c>
+      <c r="P36" s="6">
+        <f t="shared" si="9"/>
+        <v>18</v>
+      </c>
+      <c r="Q36" s="2">
         <f t="shared" si="7"/>
         <v>102</v>
       </c>
-      <c r="R35" s="5">
-        <v>0</v>
-      </c>
-      <c r="S35" s="5">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="1">
+      <c r="R36" s="4">
+        <f t="shared" si="8"/>
+        <v>103</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0</v>
+      </c>
+      <c r="U36" s="4">
+        <v>0</v>
+      </c>
+      <c r="V36" s="4">
+        <v>0</v>
+      </c>
+      <c r="W36" s="1">
         <f t="shared" si="0"/>
-        <v>1020</v>
-      </c>
-      <c r="W35" s="1">
+        <v>1030</v>
+      </c>
+      <c r="X36" s="1">
         <f t="shared" si="1"/>
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="36" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C36" s="1">
-        <v>103</v>
-      </c>
-      <c r="D36" s="1">
-        <v>103</v>
-      </c>
-      <c r="E36" s="1">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="37" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C37" s="1">
+        <v>104</v>
+      </c>
+      <c r="D37" s="1">
+        <v>104</v>
+      </c>
+      <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F36" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G36" s="6">
-        <v>31</v>
-      </c>
-      <c r="H36" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="J36" s="13" t="s">
+      <c r="F37" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G37" s="6">
+        <v>32</v>
+      </c>
+      <c r="H37" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="K36" s="2">
+      <c r="I37" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="J37" s="6">
         <f t="shared" si="2"/>
-        <v>1040</v>
-      </c>
-      <c r="L36" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="K37" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="L37" s="2">
         <f t="shared" si="3"/>
-        <v>550</v>
-      </c>
-      <c r="M36" s="2">
+        <v>1060</v>
+      </c>
+      <c r="M37" s="2">
         <f t="shared" si="4"/>
-        <v>237</v>
-      </c>
-      <c r="N36" s="2">
+        <v>560</v>
+      </c>
+      <c r="N37" s="2">
         <f t="shared" si="5"/>
-        <v>600</v>
-      </c>
-      <c r="O36" s="6">
-        <f t="shared" si="8"/>
+        <v>240</v>
+      </c>
+      <c r="O37" s="2">
+        <f t="shared" si="6"/>
+        <v>610</v>
+      </c>
+      <c r="P37" s="6">
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="P36" s="2">
-        <f t="shared" si="6"/>
-        <v>102</v>
-      </c>
-      <c r="Q36" s="4">
+      <c r="Q37" s="2">
         <f t="shared" si="7"/>
         <v>103</v>
       </c>
-      <c r="R36" s="6">
-        <v>0</v>
-      </c>
-      <c r="S36" s="6">
-        <v>0</v>
-      </c>
-      <c r="T36" s="4">
-        <v>0</v>
-      </c>
-      <c r="U36" s="4">
-        <v>0</v>
-      </c>
-      <c r="V36" s="1">
+      <c r="R37" s="4">
+        <f t="shared" si="8"/>
+        <v>104</v>
+      </c>
+      <c r="S37" s="6">
+        <v>0</v>
+      </c>
+      <c r="T37" s="6">
+        <v>0</v>
+      </c>
+      <c r="U37" s="4">
+        <v>0</v>
+      </c>
+      <c r="V37" s="4">
+        <v>0</v>
+      </c>
+      <c r="W37" s="1">
         <f t="shared" si="0"/>
-        <v>1030</v>
-      </c>
-      <c r="W36" s="1">
+        <v>1040</v>
+      </c>
+      <c r="X37" s="1">
         <f t="shared" si="1"/>
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="37" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C37" s="1">
-        <v>104</v>
-      </c>
-      <c r="D37" s="1">
-        <v>104</v>
-      </c>
-      <c r="E37" s="1">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="38" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C38" s="1">
+        <v>105</v>
+      </c>
+      <c r="D38" s="1">
+        <v>105</v>
+      </c>
+      <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F37" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37" s="6">
-        <v>32</v>
-      </c>
-      <c r="H37" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="I37" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="J37" s="13" t="s">
+      <c r="F38" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" s="6">
+        <v>33</v>
+      </c>
+      <c r="H38" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="K37" s="2">
+      <c r="I38" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="J38" s="6">
         <f t="shared" si="2"/>
-        <v>1060</v>
-      </c>
-      <c r="L37" s="2">
+        <v>1.25294117647059</v>
+      </c>
+      <c r="K38" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="L38" s="2">
         <f t="shared" si="3"/>
-        <v>560</v>
-      </c>
-      <c r="M37" s="2">
+        <v>1080</v>
+      </c>
+      <c r="M38" s="2">
         <f t="shared" si="4"/>
-        <v>240</v>
-      </c>
-      <c r="N37" s="2">
+        <v>570</v>
+      </c>
+      <c r="N38" s="2">
         <f t="shared" si="5"/>
-        <v>610</v>
-      </c>
-      <c r="O37" s="6">
-        <f t="shared" si="8"/>
+        <v>243</v>
+      </c>
+      <c r="O38" s="2">
+        <f t="shared" si="6"/>
+        <v>620</v>
+      </c>
+      <c r="P38" s="6">
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="P37" s="2">
-        <f t="shared" si="6"/>
-        <v>103</v>
-      </c>
-      <c r="Q37" s="4">
+      <c r="Q38" s="2">
         <f t="shared" si="7"/>
         <v>104</v>
       </c>
-      <c r="R37" s="6">
-        <v>0</v>
-      </c>
-      <c r="S37" s="6">
-        <v>0</v>
-      </c>
-      <c r="T37" s="4">
-        <v>0</v>
-      </c>
-      <c r="U37" s="4">
-        <v>0</v>
-      </c>
-      <c r="V37" s="1">
+      <c r="R38" s="4">
+        <f t="shared" si="8"/>
+        <v>105</v>
+      </c>
+      <c r="S38" s="6">
+        <v>0</v>
+      </c>
+      <c r="T38" s="6">
+        <v>0</v>
+      </c>
+      <c r="U38" s="4">
+        <v>0</v>
+      </c>
+      <c r="V38" s="4">
+        <v>0</v>
+      </c>
+      <c r="W38" s="1">
         <f t="shared" si="0"/>
-        <v>1040</v>
-      </c>
-      <c r="W37" s="1">
+        <v>1050</v>
+      </c>
+      <c r="X38" s="1">
         <f t="shared" si="1"/>
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="38" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C38" s="1">
-        <v>105</v>
-      </c>
-      <c r="D38" s="1">
-        <v>105</v>
-      </c>
-      <c r="E38" s="1">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="39" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C39" s="1">
+        <v>106</v>
+      </c>
+      <c r="D39" s="1">
+        <v>106</v>
+      </c>
+      <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F38" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G38" s="6">
-        <v>33</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="I38" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="J38" s="13" t="s">
+      <c r="F39" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G39" s="6">
+        <v>34</v>
+      </c>
+      <c r="H39" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="K38" s="2">
+      <c r="I39" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="J39" s="6">
         <f t="shared" si="2"/>
-        <v>1080</v>
-      </c>
-      <c r="L38" s="2">
+        <v>1.24413145539906</v>
+      </c>
+      <c r="K39" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="L39" s="2">
         <f t="shared" si="3"/>
-        <v>570</v>
-      </c>
-      <c r="M38" s="2">
+        <v>1100</v>
+      </c>
+      <c r="M39" s="2">
         <f t="shared" si="4"/>
-        <v>243</v>
-      </c>
-      <c r="N38" s="2">
+        <v>580</v>
+      </c>
+      <c r="N39" s="2">
         <f t="shared" si="5"/>
-        <v>620</v>
-      </c>
-      <c r="O38" s="6">
-        <f t="shared" si="8"/>
+        <v>246</v>
+      </c>
+      <c r="O39" s="2">
+        <f t="shared" si="6"/>
+        <v>630</v>
+      </c>
+      <c r="P39" s="6">
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="P38" s="2">
-        <f t="shared" si="6"/>
-        <v>104</v>
-      </c>
-      <c r="Q38" s="4">
+      <c r="Q39" s="2">
         <f t="shared" si="7"/>
         <v>105</v>
       </c>
-      <c r="R38" s="6">
-        <v>0</v>
-      </c>
-      <c r="S38" s="6">
-        <v>0</v>
-      </c>
-      <c r="T38" s="4">
-        <v>0</v>
-      </c>
-      <c r="U38" s="4">
-        <v>0</v>
-      </c>
-      <c r="V38" s="1">
+      <c r="R39" s="4">
+        <f t="shared" si="8"/>
+        <v>106</v>
+      </c>
+      <c r="S39" s="6">
+        <v>0</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0</v>
+      </c>
+      <c r="U39" s="4">
+        <v>0</v>
+      </c>
+      <c r="V39" s="4">
+        <v>0</v>
+      </c>
+      <c r="W39" s="1">
         <f t="shared" si="0"/>
-        <v>1050</v>
-      </c>
-      <c r="W38" s="1">
+        <v>1060</v>
+      </c>
+      <c r="X39" s="1">
         <f t="shared" si="1"/>
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="39" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C39" s="1">
-        <v>106</v>
-      </c>
-      <c r="D39" s="1">
-        <v>106</v>
-      </c>
-      <c r="E39" s="1">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="40" s="4" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C40" s="1">
+        <v>107</v>
+      </c>
+      <c r="D40" s="1">
+        <v>107</v>
+      </c>
+      <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F39" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G39" s="6">
-        <v>34</v>
-      </c>
-      <c r="H39" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="I39" s="13" t="s">
-        <v>211</v>
-      </c>
-      <c r="J39" s="13" t="s">
+      <c r="F40" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G40" s="6">
+        <v>35</v>
+      </c>
+      <c r="H40" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="K39" s="2">
+      <c r="I40" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="J40" s="6">
         <f t="shared" si="2"/>
-        <v>1100</v>
-      </c>
-      <c r="L39" s="2">
+        <v>1.23396226415094</v>
+      </c>
+      <c r="K40" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="L40" s="2">
         <f t="shared" si="3"/>
-        <v>580</v>
-      </c>
-      <c r="M39" s="2">
+        <v>1120</v>
+      </c>
+      <c r="M40" s="2">
         <f t="shared" si="4"/>
-        <v>246</v>
-      </c>
-      <c r="N39" s="2">
+        <v>590</v>
+      </c>
+      <c r="N40" s="2">
         <f t="shared" si="5"/>
-        <v>630</v>
-      </c>
-      <c r="O39" s="6">
-        <f t="shared" si="8"/>
+        <v>249</v>
+      </c>
+      <c r="O40" s="2">
+        <f t="shared" si="6"/>
+        <v>640</v>
+      </c>
+      <c r="P40" s="6">
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="P39" s="2">
-        <f t="shared" si="6"/>
-        <v>105</v>
-      </c>
-      <c r="Q39" s="4">
+      <c r="Q40" s="2">
         <f t="shared" si="7"/>
         <v>106</v>
       </c>
-      <c r="R39" s="6">
-        <v>0</v>
-      </c>
-      <c r="S39" s="6">
-        <v>0</v>
-      </c>
-      <c r="T39" s="4">
-        <v>0</v>
-      </c>
-      <c r="U39" s="4">
-        <v>0</v>
-      </c>
-      <c r="V39" s="1">
-        <f t="shared" si="0"/>
-        <v>1060</v>
-      </c>
-      <c r="W39" s="1">
-        <f t="shared" si="1"/>
-        <v>1060</v>
-      </c>
-    </row>
-    <row r="40" s="4" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C40" s="1">
+      <c r="R40" s="4">
+        <f t="shared" si="8"/>
         <v>107</v>
       </c>
-      <c r="D40" s="1">
-        <v>107</v>
-      </c>
-      <c r="E40" s="1">
-        <v>2</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G40" s="6">
-        <v>35</v>
-      </c>
-      <c r="H40" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="I40" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="J40" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="K40" s="2">
-        <f t="shared" si="2"/>
-        <v>1120</v>
-      </c>
-      <c r="L40" s="2">
-        <f t="shared" si="3"/>
-        <v>590</v>
-      </c>
-      <c r="M40" s="2">
-        <f t="shared" si="4"/>
-        <v>249</v>
-      </c>
-      <c r="N40" s="2">
-        <f t="shared" si="5"/>
-        <v>640</v>
-      </c>
-      <c r="O40" s="6">
-        <f t="shared" si="8"/>
-        <v>18</v>
-      </c>
-      <c r="P40" s="2">
-        <f t="shared" si="6"/>
-        <v>106</v>
-      </c>
-      <c r="Q40" s="4">
-        <f t="shared" si="7"/>
-        <v>107</v>
-      </c>
-      <c r="R40" s="6">
-        <v>0</v>
-      </c>
       <c r="S40" s="6">
         <v>0</v>
       </c>
-      <c r="T40" s="4">
+      <c r="T40" s="6">
         <v>0</v>
       </c>
       <c r="U40" s="4">
         <v>0</v>
       </c>
-      <c r="V40" s="1">
+      <c r="V40" s="4">
+        <v>0</v>
+      </c>
+      <c r="W40" s="1">
         <f t="shared" si="0"/>
         <v>1070</v>
       </c>
-      <c r="W40" s="1">
+      <c r="X40" s="1">
         <f t="shared" si="1"/>
         <v>1070</v>
       </c>
     </row>
-    <row r="41" s="5" customFormat="1" customHeight="1" spans="1:23">
+    <row r="41" s="5" customFormat="1" customHeight="1" spans="1:24">
       <c r="A41" s="3"/>
       <c r="C41" s="1">
         <v>108</v>
@@ -12872,64 +13011,68 @@
         <v>36</v>
       </c>
       <c r="H41" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="I41" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="I41" s="13" t="s">
+      <c r="J41" s="6">
+        <f t="shared" si="2"/>
+        <v>1.24159021406728</v>
+      </c>
+      <c r="K41" s="13" t="s">
         <v>217</v>
-      </c>
-      <c r="J41" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="K41" s="2">
-        <f t="shared" si="2"/>
-        <v>1140</v>
       </c>
       <c r="L41" s="2">
         <f t="shared" si="3"/>
-        <v>600</v>
+        <v>1140</v>
       </c>
       <c r="M41" s="2">
         <f t="shared" si="4"/>
-        <v>252</v>
+        <v>600</v>
       </c>
       <c r="N41" s="2">
         <f t="shared" si="5"/>
+        <v>252</v>
+      </c>
+      <c r="O41" s="2">
+        <f t="shared" si="6"/>
         <v>650</v>
       </c>
-      <c r="O41" s="6">
+      <c r="P41" s="6">
+        <f t="shared" si="9"/>
+        <v>18</v>
+      </c>
+      <c r="Q41" s="2">
+        <f t="shared" si="7"/>
+        <v>107</v>
+      </c>
+      <c r="R41" s="3">
         <f t="shared" si="8"/>
-        <v>18</v>
-      </c>
-      <c r="P41" s="2">
-        <f t="shared" si="6"/>
-        <v>107</v>
-      </c>
-      <c r="Q41" s="3">
-        <f t="shared" si="7"/>
         <v>108</v>
       </c>
-      <c r="R41" s="5">
-        <v>0</v>
-      </c>
       <c r="S41" s="5">
         <v>0</v>
       </c>
-      <c r="T41" s="3">
+      <c r="T41" s="5">
         <v>0</v>
       </c>
       <c r="U41" s="3">
         <v>0</v>
       </c>
-      <c r="V41" s="1">
+      <c r="V41" s="3">
+        <v>0</v>
+      </c>
+      <c r="W41" s="1">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="W41" s="1">
+      <c r="X41" s="1">
         <f t="shared" si="1"/>
         <v>1080</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A42" s="2"/>
       <c r="C42" s="1">
         <v>109</v>
@@ -12947,64 +13090,68 @@
         <v>37</v>
       </c>
       <c r="H42" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="I42" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="I42" s="13" t="s">
+      <c r="J42" s="6">
+        <f t="shared" si="2"/>
+        <v>1.24137931034483</v>
+      </c>
+      <c r="K42" s="13" t="s">
         <v>220</v>
-      </c>
-      <c r="J42" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="K42" s="2">
-        <f t="shared" si="2"/>
-        <v>1160</v>
       </c>
       <c r="L42" s="2">
         <f t="shared" si="3"/>
-        <v>610</v>
+        <v>1160</v>
       </c>
       <c r="M42" s="2">
         <f t="shared" si="4"/>
-        <v>255</v>
+        <v>610</v>
       </c>
       <c r="N42" s="2">
         <f t="shared" si="5"/>
+        <v>255</v>
+      </c>
+      <c r="O42" s="2">
+        <f t="shared" si="6"/>
         <v>660</v>
       </c>
-      <c r="O42" s="6">
-        <f t="shared" si="8"/>
+      <c r="P42" s="6">
+        <f t="shared" si="9"/>
         <v>19</v>
-      </c>
-      <c r="P42" s="2">
-        <f t="shared" si="6"/>
-        <v>108</v>
       </c>
       <c r="Q42" s="2">
         <f t="shared" si="7"/>
+        <v>108</v>
+      </c>
+      <c r="R42" s="2">
+        <f t="shared" si="8"/>
         <v>109</v>
       </c>
-      <c r="R42" s="1">
-        <v>0</v>
-      </c>
       <c r="S42" s="1">
         <v>0</v>
       </c>
-      <c r="T42" s="4">
+      <c r="T42" s="1">
         <v>0</v>
       </c>
       <c r="U42" s="4">
         <v>0</v>
       </c>
-      <c r="V42" s="1">
+      <c r="V42" s="4">
+        <v>0</v>
+      </c>
+      <c r="W42" s="1">
         <f t="shared" si="0"/>
         <v>1090</v>
       </c>
-      <c r="W42" s="1">
+      <c r="X42" s="1">
         <f t="shared" si="1"/>
         <v>1090</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A43" s="2"/>
       <c r="C43" s="1">
         <v>110</v>
@@ -13022,64 +13169,68 @@
         <v>38</v>
       </c>
       <c r="H43" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="I43" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="I43" s="13" t="s">
+      <c r="J43" s="6">
+        <f t="shared" si="2"/>
+        <v>1.23611111111111</v>
+      </c>
+      <c r="K43" s="13" t="s">
         <v>223</v>
-      </c>
-      <c r="J43" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="K43" s="2">
-        <f t="shared" si="2"/>
-        <v>1180</v>
       </c>
       <c r="L43" s="2">
         <f t="shared" si="3"/>
-        <v>620</v>
+        <v>1180</v>
       </c>
       <c r="M43" s="2">
         <f t="shared" si="4"/>
-        <v>258</v>
+        <v>620</v>
       </c>
       <c r="N43" s="2">
         <f t="shared" si="5"/>
+        <v>258</v>
+      </c>
+      <c r="O43" s="2">
+        <f t="shared" si="6"/>
         <v>670</v>
       </c>
-      <c r="O43" s="6">
-        <f t="shared" si="8"/>
+      <c r="P43" s="6">
+        <f t="shared" si="9"/>
         <v>19</v>
-      </c>
-      <c r="P43" s="2">
-        <f t="shared" si="6"/>
-        <v>109</v>
       </c>
       <c r="Q43" s="2">
         <f t="shared" si="7"/>
+        <v>109</v>
+      </c>
+      <c r="R43" s="2">
+        <f t="shared" si="8"/>
         <v>110</v>
       </c>
-      <c r="R43" s="1">
-        <v>0</v>
-      </c>
       <c r="S43" s="1">
         <v>0</v>
       </c>
-      <c r="T43" s="4">
+      <c r="T43" s="1">
         <v>0</v>
       </c>
       <c r="U43" s="4">
         <v>0</v>
       </c>
-      <c r="V43" s="1">
+      <c r="V43" s="4">
+        <v>0</v>
+      </c>
+      <c r="W43" s="1">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="W43" s="1">
+      <c r="X43" s="1">
         <f t="shared" si="1"/>
         <v>1100</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A44" s="2"/>
       <c r="C44" s="1">
         <v>111</v>
@@ -13097,64 +13248,68 @@
         <v>39</v>
       </c>
       <c r="H44" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="I44" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="I44" s="13" t="s">
+      <c r="J44" s="6">
+        <f t="shared" si="2"/>
+        <v>1.23756019261637</v>
+      </c>
+      <c r="K44" s="13" t="s">
         <v>226</v>
-      </c>
-      <c r="J44" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="K44" s="2">
-        <f t="shared" si="2"/>
-        <v>1200</v>
       </c>
       <c r="L44" s="2">
         <f t="shared" si="3"/>
-        <v>630</v>
+        <v>1200</v>
       </c>
       <c r="M44" s="2">
         <f t="shared" si="4"/>
-        <v>261</v>
+        <v>630</v>
       </c>
       <c r="N44" s="2">
         <f t="shared" si="5"/>
+        <v>261</v>
+      </c>
+      <c r="O44" s="2">
+        <f t="shared" si="6"/>
         <v>680</v>
       </c>
-      <c r="O44" s="6">
-        <f t="shared" si="8"/>
+      <c r="P44" s="6">
+        <f t="shared" si="9"/>
         <v>19</v>
-      </c>
-      <c r="P44" s="2">
-        <f t="shared" si="6"/>
-        <v>110</v>
       </c>
       <c r="Q44" s="2">
         <f t="shared" si="7"/>
+        <v>110</v>
+      </c>
+      <c r="R44" s="2">
+        <f t="shared" si="8"/>
         <v>111</v>
       </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
       <c r="S44" s="1">
         <v>0</v>
       </c>
-      <c r="T44" s="4">
+      <c r="T44" s="1">
         <v>0</v>
       </c>
       <c r="U44" s="4">
         <v>0</v>
       </c>
-      <c r="V44" s="1">
+      <c r="V44" s="4">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="W44" s="1">
+      <c r="X44" s="1">
         <f t="shared" si="1"/>
         <v>1110</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A45" s="2"/>
       <c r="C45" s="1">
         <v>112</v>
@@ -13172,64 +13327,68 @@
         <v>40</v>
       </c>
       <c r="H45" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="I45" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="I45" s="13" t="s">
+      <c r="J45" s="6">
+        <f t="shared" si="2"/>
+        <v>1.23735408560311</v>
+      </c>
+      <c r="K45" s="13" t="s">
         <v>229</v>
-      </c>
-      <c r="J45" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="K45" s="2">
-        <f t="shared" si="2"/>
-        <v>1220</v>
       </c>
       <c r="L45" s="2">
         <f t="shared" si="3"/>
-        <v>640</v>
+        <v>1220</v>
       </c>
       <c r="M45" s="2">
         <f t="shared" si="4"/>
-        <v>264</v>
+        <v>640</v>
       </c>
       <c r="N45" s="2">
         <f t="shared" si="5"/>
+        <v>264</v>
+      </c>
+      <c r="O45" s="2">
+        <f t="shared" si="6"/>
         <v>690</v>
       </c>
-      <c r="O45" s="6">
-        <f t="shared" si="8"/>
+      <c r="P45" s="6">
+        <f t="shared" si="9"/>
         <v>19</v>
-      </c>
-      <c r="P45" s="2">
-        <f t="shared" si="6"/>
-        <v>111</v>
       </c>
       <c r="Q45" s="2">
         <f t="shared" si="7"/>
+        <v>111</v>
+      </c>
+      <c r="R45" s="2">
+        <f t="shared" si="8"/>
         <v>112</v>
       </c>
-      <c r="R45" s="1">
-        <v>0</v>
-      </c>
       <c r="S45" s="1">
         <v>0</v>
       </c>
-      <c r="T45" s="4">
+      <c r="T45" s="1">
         <v>0</v>
       </c>
       <c r="U45" s="4">
         <v>0</v>
       </c>
-      <c r="V45" s="1">
+      <c r="V45" s="4">
+        <v>0</v>
+      </c>
+      <c r="W45" s="1">
         <f t="shared" si="0"/>
         <v>1120</v>
       </c>
-      <c r="W45" s="1">
+      <c r="X45" s="1">
         <f t="shared" si="1"/>
         <v>1120</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:23">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:24">
       <c r="A46" s="2"/>
       <c r="C46" s="1">
         <v>113</v>
@@ -13247,64 +13406,68 @@
         <v>41</v>
       </c>
       <c r="H46" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="I46" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="I46" s="13" t="s">
+      <c r="J46" s="6">
+        <f t="shared" si="2"/>
+        <v>1.23689727463312</v>
+      </c>
+      <c r="K46" s="13" t="s">
         <v>232</v>
-      </c>
-      <c r="J46" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="K46" s="2">
-        <f t="shared" si="2"/>
-        <v>1240</v>
       </c>
       <c r="L46" s="2">
         <f t="shared" si="3"/>
-        <v>650</v>
+        <v>1240</v>
       </c>
       <c r="M46" s="2">
         <f t="shared" si="4"/>
-        <v>267</v>
+        <v>650</v>
       </c>
       <c r="N46" s="2">
         <f t="shared" si="5"/>
+        <v>267</v>
+      </c>
+      <c r="O46" s="2">
+        <f t="shared" si="6"/>
         <v>700</v>
       </c>
-      <c r="O46" s="6">
-        <f t="shared" si="8"/>
+      <c r="P46" s="6">
+        <f t="shared" si="9"/>
         <v>19</v>
-      </c>
-      <c r="P46" s="2">
-        <f t="shared" si="6"/>
-        <v>112</v>
       </c>
       <c r="Q46" s="2">
         <f t="shared" si="7"/>
+        <v>112</v>
+      </c>
+      <c r="R46" s="2">
+        <f t="shared" si="8"/>
         <v>113</v>
       </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
       <c r="S46" s="1">
         <v>0</v>
       </c>
-      <c r="T46" s="4">
+      <c r="T46" s="1">
         <v>0</v>
       </c>
       <c r="U46" s="4">
         <v>0</v>
       </c>
-      <c r="V46" s="1">
+      <c r="V46" s="4">
+        <v>0</v>
+      </c>
+      <c r="W46" s="1">
         <f t="shared" si="0"/>
         <v>1130</v>
       </c>
-      <c r="W46" s="1">
+      <c r="X46" s="1">
         <f t="shared" si="1"/>
         <v>1130</v>
       </c>
     </row>
-    <row r="47" s="3" customFormat="1" customHeight="1" spans="1:23">
+    <row r="47" s="3" customFormat="1" customHeight="1" spans="1:24">
       <c r="C47" s="1">
         <v>114</v>
       </c>
@@ -13321,1766 +13484,1862 @@
         <v>42</v>
       </c>
       <c r="H47" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="I47" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="I47" s="13" t="s">
+      <c r="J47" s="6">
+        <f t="shared" si="2"/>
+        <v>1.23728813559322</v>
+      </c>
+      <c r="K47" s="13" t="s">
         <v>235</v>
-      </c>
-      <c r="J47" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="K47" s="2">
-        <f t="shared" si="2"/>
-        <v>1260</v>
       </c>
       <c r="L47" s="2">
         <f t="shared" si="3"/>
-        <v>660</v>
+        <v>1260</v>
       </c>
       <c r="M47" s="2">
         <f t="shared" si="4"/>
-        <v>270</v>
+        <v>660</v>
       </c>
       <c r="N47" s="2">
         <f t="shared" si="5"/>
+        <v>270</v>
+      </c>
+      <c r="O47" s="2">
+        <f t="shared" si="6"/>
         <v>710</v>
       </c>
-      <c r="O47" s="6">
+      <c r="P47" s="6">
+        <f t="shared" si="9"/>
+        <v>19</v>
+      </c>
+      <c r="Q47" s="2">
+        <f t="shared" si="7"/>
+        <v>113</v>
+      </c>
+      <c r="R47" s="3">
         <f t="shared" si="8"/>
-        <v>19</v>
-      </c>
-      <c r="P47" s="2">
+        <v>114</v>
+      </c>
+      <c r="S47" s="5">
+        <v>0</v>
+      </c>
+      <c r="T47" s="5">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="1">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="X47" s="1">
+        <f t="shared" si="1"/>
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C48" s="1">
+        <v>115</v>
+      </c>
+      <c r="D48" s="1">
+        <v>115</v>
+      </c>
+      <c r="E48" s="1">
+        <v>2</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G48" s="1">
+        <v>43</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="I48" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="J48" s="6">
+        <f t="shared" si="2"/>
+        <v>1.23287671232877</v>
+      </c>
+      <c r="K48" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="L48" s="2">
+        <f t="shared" si="3"/>
+        <v>1280</v>
+      </c>
+      <c r="M48" s="2">
+        <f t="shared" si="4"/>
+        <v>670</v>
+      </c>
+      <c r="N48" s="2">
+        <f t="shared" si="5"/>
+        <v>273</v>
+      </c>
+      <c r="O48" s="2">
         <f t="shared" si="6"/>
-        <v>113</v>
-      </c>
-      <c r="Q47" s="3">
+        <v>720</v>
+      </c>
+      <c r="P48" s="6">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="Q48" s="2">
         <f t="shared" si="7"/>
         <v>114</v>
       </c>
-      <c r="R47" s="5">
-        <v>0</v>
-      </c>
-      <c r="S47" s="5">
-        <v>0</v>
-      </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
-      <c r="U47" s="3">
-        <v>0</v>
-      </c>
-      <c r="V47" s="1">
+      <c r="R48" s="2">
+        <f t="shared" si="8"/>
+        <v>115</v>
+      </c>
+      <c r="S48" s="1">
+        <v>0</v>
+      </c>
+      <c r="T48" s="1">
+        <v>0</v>
+      </c>
+      <c r="U48" s="4">
+        <v>0</v>
+      </c>
+      <c r="V48" s="4">
+        <v>0</v>
+      </c>
+      <c r="W48" s="1">
         <f t="shared" si="0"/>
-        <v>1140</v>
-      </c>
-      <c r="W47" s="1">
+        <v>1150</v>
+      </c>
+      <c r="X48" s="1">
         <f t="shared" si="1"/>
-        <v>1140</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C48" s="1">
-        <v>115</v>
-      </c>
-      <c r="D48" s="1">
-        <v>115</v>
-      </c>
-      <c r="E48" s="1">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C49" s="1">
+        <v>116</v>
+      </c>
+      <c r="D49" s="1">
+        <v>116</v>
+      </c>
+      <c r="E49" s="1">
         <v>2</v>
       </c>
-      <c r="F48" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="G48" s="1">
-        <v>43</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="I48" s="13" t="s">
+      <c r="F49" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G49" s="1">
+        <v>44</v>
+      </c>
+      <c r="H49" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="J48" s="13" t="s">
+      <c r="I49" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="K48" s="2">
+      <c r="J49" s="6">
         <f t="shared" si="2"/>
-        <v>1280</v>
-      </c>
-      <c r="L48" s="2">
+        <v>1.23333333333333</v>
+      </c>
+      <c r="K49" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="L49" s="2">
         <f t="shared" si="3"/>
-        <v>670</v>
-      </c>
-      <c r="M48" s="2">
+        <v>1300</v>
+      </c>
+      <c r="M49" s="2">
         <f t="shared" si="4"/>
-        <v>273</v>
-      </c>
-      <c r="N48" s="2">
+        <v>680</v>
+      </c>
+      <c r="N49" s="2">
         <f t="shared" si="5"/>
-        <v>720</v>
-      </c>
-      <c r="O48" s="6">
-        <f t="shared" si="8"/>
+        <v>276</v>
+      </c>
+      <c r="O49" s="2">
+        <f t="shared" si="6"/>
+        <v>730</v>
+      </c>
+      <c r="P49" s="6">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="P48" s="2">
-        <f t="shared" si="6"/>
-        <v>114</v>
-      </c>
-      <c r="Q48" s="2">
+      <c r="Q49" s="2">
         <f t="shared" si="7"/>
         <v>115</v>
       </c>
-      <c r="R48" s="1">
-        <v>0</v>
-      </c>
-      <c r="S48" s="1">
-        <v>0</v>
-      </c>
-      <c r="T48" s="4">
-        <v>0</v>
-      </c>
-      <c r="U48" s="4">
-        <v>0</v>
-      </c>
-      <c r="V48" s="1">
+      <c r="R49" s="2">
+        <f t="shared" si="8"/>
+        <v>116</v>
+      </c>
+      <c r="S49" s="1">
+        <v>0</v>
+      </c>
+      <c r="T49" s="1">
+        <v>0</v>
+      </c>
+      <c r="U49" s="4">
+        <v>0</v>
+      </c>
+      <c r="V49" s="4">
+        <v>0</v>
+      </c>
+      <c r="W49" s="1">
         <f t="shared" si="0"/>
-        <v>1150</v>
-      </c>
-      <c r="W48" s="1">
+        <v>1160</v>
+      </c>
+      <c r="X49" s="1">
         <f t="shared" si="1"/>
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C49" s="1">
-        <v>116</v>
-      </c>
-      <c r="D49" s="1">
-        <v>116</v>
-      </c>
-      <c r="E49" s="1">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C50" s="1">
+        <v>117</v>
+      </c>
+      <c r="D50" s="1">
+        <v>117</v>
+      </c>
+      <c r="E50" s="1">
         <v>2</v>
       </c>
-      <c r="F49" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="G49" s="1">
-        <v>44</v>
-      </c>
-      <c r="H49" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="I49" s="13" t="s">
+      <c r="F50" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G50" s="1">
+        <v>45</v>
+      </c>
+      <c r="H50" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="J49" s="13" t="s">
+      <c r="I50" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="K49" s="2">
+      <c r="J50" s="6">
         <f t="shared" si="2"/>
-        <v>1300</v>
-      </c>
-      <c r="L49" s="2">
+        <v>1.22972972972973</v>
+      </c>
+      <c r="K50" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="L50" s="2">
         <f t="shared" si="3"/>
-        <v>680</v>
-      </c>
-      <c r="M49" s="2">
+        <v>1320</v>
+      </c>
+      <c r="M50" s="2">
         <f t="shared" si="4"/>
-        <v>276</v>
-      </c>
-      <c r="N49" s="2">
+        <v>690</v>
+      </c>
+      <c r="N50" s="2">
         <f t="shared" si="5"/>
-        <v>730</v>
-      </c>
-      <c r="O49" s="6">
-        <f t="shared" si="8"/>
+        <v>279</v>
+      </c>
+      <c r="O50" s="2">
+        <f t="shared" si="6"/>
+        <v>740</v>
+      </c>
+      <c r="P50" s="6">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="P49" s="2">
-        <f t="shared" si="6"/>
-        <v>115</v>
-      </c>
-      <c r="Q49" s="2">
+      <c r="Q50" s="2">
         <f t="shared" si="7"/>
         <v>116</v>
       </c>
-      <c r="R49" s="1">
-        <v>0</v>
-      </c>
-      <c r="S49" s="1">
-        <v>0</v>
-      </c>
-      <c r="T49" s="4">
-        <v>0</v>
-      </c>
-      <c r="U49" s="4">
-        <v>0</v>
-      </c>
-      <c r="V49" s="1">
+      <c r="R50" s="2">
+        <f t="shared" si="8"/>
+        <v>117</v>
+      </c>
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="1">
+        <v>0</v>
+      </c>
+      <c r="U50" s="4">
+        <v>0</v>
+      </c>
+      <c r="V50" s="4">
+        <v>0</v>
+      </c>
+      <c r="W50" s="1">
         <f t="shared" si="0"/>
-        <v>1160</v>
-      </c>
-      <c r="W49" s="1">
+        <v>1170</v>
+      </c>
+      <c r="X50" s="1">
         <f t="shared" si="1"/>
-        <v>1160</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C50" s="1">
-        <v>117</v>
-      </c>
-      <c r="D50" s="1">
-        <v>117</v>
-      </c>
-      <c r="E50" s="1">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C51" s="1">
+        <v>118</v>
+      </c>
+      <c r="D51" s="1">
+        <v>118</v>
+      </c>
+      <c r="E51" s="1">
         <v>2</v>
       </c>
-      <c r="F50" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G50" s="1">
-        <v>45</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>243</v>
-      </c>
-      <c r="I50" s="13" t="s">
+      <c r="F51" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="G51" s="1">
+        <v>46</v>
+      </c>
+      <c r="H51" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="J50" s="13" t="s">
+      <c r="I51" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="K50" s="2">
+      <c r="J51" s="6">
         <f t="shared" si="2"/>
-        <v>1320</v>
-      </c>
-      <c r="L50" s="2">
+        <v>1.23076923076923</v>
+      </c>
+      <c r="K51" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="L51" s="2">
         <f t="shared" si="3"/>
-        <v>690</v>
-      </c>
-      <c r="M50" s="2">
+        <v>1340</v>
+      </c>
+      <c r="M51" s="2">
         <f t="shared" si="4"/>
-        <v>279</v>
-      </c>
-      <c r="N50" s="2">
+        <v>700</v>
+      </c>
+      <c r="N51" s="2">
         <f t="shared" si="5"/>
-        <v>740</v>
-      </c>
-      <c r="O50" s="6">
-        <f t="shared" si="8"/>
+        <v>282</v>
+      </c>
+      <c r="O51" s="2">
+        <f t="shared" si="6"/>
+        <v>750</v>
+      </c>
+      <c r="P51" s="6">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="P50" s="2">
-        <f t="shared" si="6"/>
-        <v>116</v>
-      </c>
-      <c r="Q50" s="2">
+      <c r="Q51" s="2">
         <f t="shared" si="7"/>
         <v>117</v>
       </c>
-      <c r="R50" s="1">
-        <v>0</v>
-      </c>
-      <c r="S50" s="1">
-        <v>0</v>
-      </c>
-      <c r="T50" s="4">
-        <v>0</v>
-      </c>
-      <c r="U50" s="4">
-        <v>0</v>
-      </c>
-      <c r="V50" s="1">
+      <c r="R51" s="2">
+        <f t="shared" si="8"/>
+        <v>118</v>
+      </c>
+      <c r="S51" s="1">
+        <v>0</v>
+      </c>
+      <c r="T51" s="1">
+        <v>0</v>
+      </c>
+      <c r="U51" s="4">
+        <v>0</v>
+      </c>
+      <c r="V51" s="4">
+        <v>0</v>
+      </c>
+      <c r="W51" s="1">
         <f t="shared" si="0"/>
-        <v>1170</v>
-      </c>
-      <c r="W50" s="1">
+        <v>1180</v>
+      </c>
+      <c r="X51" s="1">
         <f t="shared" si="1"/>
-        <v>1170</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C51" s="1">
-        <v>118</v>
-      </c>
-      <c r="D51" s="1">
-        <v>118</v>
-      </c>
-      <c r="E51" s="1">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C52" s="1">
+        <v>119</v>
+      </c>
+      <c r="D52" s="1">
+        <v>119</v>
+      </c>
+      <c r="E52" s="1">
         <v>2</v>
       </c>
-      <c r="F51" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="G51" s="1">
-        <v>46</v>
-      </c>
-      <c r="H51" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="I51" s="13" t="s">
+      <c r="F52" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G52" s="1">
+        <v>47</v>
+      </c>
+      <c r="H52" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="J51" s="13" t="s">
+      <c r="I52" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="K51" s="2">
+      <c r="J52" s="6">
         <f t="shared" si="2"/>
-        <v>1340</v>
-      </c>
-      <c r="L51" s="2">
+        <v>1.22619047619048</v>
+      </c>
+      <c r="K52" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="L52" s="2">
         <f t="shared" si="3"/>
-        <v>700</v>
-      </c>
-      <c r="M51" s="2">
+        <v>1360</v>
+      </c>
+      <c r="M52" s="2">
         <f t="shared" si="4"/>
-        <v>282</v>
-      </c>
-      <c r="N51" s="2">
+        <v>710</v>
+      </c>
+      <c r="N52" s="2">
         <f t="shared" si="5"/>
-        <v>750</v>
-      </c>
-      <c r="O51" s="6">
-        <f t="shared" si="8"/>
+        <v>285</v>
+      </c>
+      <c r="O52" s="2">
+        <f t="shared" si="6"/>
+        <v>760</v>
+      </c>
+      <c r="P52" s="6">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="P51" s="2">
-        <f t="shared" si="6"/>
-        <v>117</v>
-      </c>
-      <c r="Q51" s="2">
+      <c r="Q52" s="2">
         <f t="shared" si="7"/>
         <v>118</v>
       </c>
-      <c r="R51" s="1">
-        <v>0</v>
-      </c>
-      <c r="S51" s="1">
-        <v>0</v>
-      </c>
-      <c r="T51" s="4">
-        <v>0</v>
-      </c>
-      <c r="U51" s="4">
-        <v>0</v>
-      </c>
-      <c r="V51" s="1">
+      <c r="R52" s="2">
+        <f t="shared" si="8"/>
+        <v>119</v>
+      </c>
+      <c r="S52" s="1">
+        <v>0</v>
+      </c>
+      <c r="T52" s="1">
+        <v>0</v>
+      </c>
+      <c r="U52" s="4">
+        <v>0</v>
+      </c>
+      <c r="V52" s="4">
+        <v>0</v>
+      </c>
+      <c r="W52" s="1">
         <f t="shared" si="0"/>
-        <v>1180</v>
-      </c>
-      <c r="W51" s="1">
+        <v>1190</v>
+      </c>
+      <c r="X52" s="1">
         <f t="shared" si="1"/>
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C52" s="1">
-        <v>119</v>
-      </c>
-      <c r="D52" s="1">
-        <v>119</v>
-      </c>
-      <c r="E52" s="1">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="53" s="3" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C53" s="1">
+        <v>120</v>
+      </c>
+      <c r="D53" s="1">
+        <v>120</v>
+      </c>
+      <c r="E53" s="1">
         <v>2</v>
       </c>
-      <c r="F52" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="G52" s="1">
-        <v>47</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="I52" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="J52" s="13" t="s">
+      <c r="F53" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="G53" s="5">
+        <v>48</v>
+      </c>
+      <c r="H53" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="K52" s="2">
+      <c r="I53" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="J53" s="6">
         <f t="shared" si="2"/>
-        <v>1360</v>
-      </c>
-      <c r="L52" s="2">
+        <v>1.22330097087379</v>
+      </c>
+      <c r="K53" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="L53" s="2">
         <f t="shared" si="3"/>
-        <v>710</v>
-      </c>
-      <c r="M52" s="2">
+        <v>1380</v>
+      </c>
+      <c r="M53" s="2">
         <f t="shared" si="4"/>
-        <v>285</v>
-      </c>
-      <c r="N52" s="2">
+        <v>720</v>
+      </c>
+      <c r="N53" s="2">
         <f t="shared" si="5"/>
-        <v>760</v>
-      </c>
-      <c r="O52" s="6">
-        <f t="shared" si="8"/>
+        <v>288</v>
+      </c>
+      <c r="O53" s="2">
+        <f t="shared" si="6"/>
+        <v>770</v>
+      </c>
+      <c r="P53" s="6">
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="P52" s="2">
-        <f t="shared" si="6"/>
-        <v>118</v>
-      </c>
-      <c r="Q52" s="2">
+      <c r="Q53" s="2">
         <f t="shared" si="7"/>
         <v>119</v>
       </c>
-      <c r="R52" s="1">
-        <v>0</v>
-      </c>
-      <c r="S52" s="1">
-        <v>0</v>
-      </c>
-      <c r="T52" s="4">
-        <v>0</v>
-      </c>
-      <c r="U52" s="4">
-        <v>0</v>
-      </c>
-      <c r="V52" s="1">
+      <c r="R53" s="3">
+        <f t="shared" si="8"/>
+        <v>120</v>
+      </c>
+      <c r="S53" s="5">
+        <v>0</v>
+      </c>
+      <c r="T53" s="5">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="1">
         <f t="shared" si="0"/>
-        <v>1190</v>
-      </c>
-      <c r="W52" s="1">
+        <v>1200</v>
+      </c>
+      <c r="X53" s="1">
         <f t="shared" si="1"/>
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="53" s="3" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C53" s="1">
-        <v>120</v>
-      </c>
-      <c r="D53" s="1">
-        <v>120</v>
-      </c>
-      <c r="E53" s="1">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C54" s="1">
+        <v>121</v>
+      </c>
+      <c r="D54" s="1">
+        <v>121</v>
+      </c>
+      <c r="E54" s="1">
         <v>2</v>
       </c>
-      <c r="F53" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="G53" s="5">
-        <v>48</v>
-      </c>
-      <c r="H53" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="I53" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="J53" s="13" t="s">
+      <c r="F54" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G54" s="1">
+        <v>49</v>
+      </c>
+      <c r="H54" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="K53" s="2">
+      <c r="I54" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="J54" s="6">
         <f t="shared" si="2"/>
-        <v>1380</v>
-      </c>
-      <c r="L53" s="2">
+        <v>1.22420634920635</v>
+      </c>
+      <c r="K54" s="13" t="s">
+        <v>255</v>
+      </c>
+      <c r="L54" s="2">
         <f t="shared" si="3"/>
-        <v>720</v>
-      </c>
-      <c r="M53" s="2">
+        <v>1400</v>
+      </c>
+      <c r="M54" s="2">
         <f t="shared" si="4"/>
-        <v>288</v>
-      </c>
-      <c r="N53" s="2">
+        <v>730</v>
+      </c>
+      <c r="N54" s="2">
         <f t="shared" si="5"/>
-        <v>770</v>
-      </c>
-      <c r="O53" s="6">
-        <f t="shared" si="8"/>
-        <v>20</v>
-      </c>
-      <c r="P53" s="2">
+        <v>291</v>
+      </c>
+      <c r="O54" s="2">
         <f t="shared" si="6"/>
-        <v>119</v>
-      </c>
-      <c r="Q53" s="3">
+        <v>780</v>
+      </c>
+      <c r="P54" s="6">
+        <f t="shared" si="9"/>
+        <v>21</v>
+      </c>
+      <c r="Q54" s="2">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="R53" s="5">
-        <v>0</v>
-      </c>
-      <c r="S53" s="5">
-        <v>0</v>
-      </c>
-      <c r="T53" s="3">
-        <v>0</v>
-      </c>
-      <c r="U53" s="3">
-        <v>0</v>
-      </c>
-      <c r="V53" s="1">
+      <c r="R54" s="2">
+        <f t="shared" si="8"/>
+        <v>121</v>
+      </c>
+      <c r="S54" s="1">
+        <v>0</v>
+      </c>
+      <c r="T54" s="1">
+        <v>0</v>
+      </c>
+      <c r="U54" s="4">
+        <v>0</v>
+      </c>
+      <c r="V54" s="4">
+        <v>0</v>
+      </c>
+      <c r="W54" s="1">
         <f t="shared" si="0"/>
-        <v>1200</v>
-      </c>
-      <c r="W53" s="1">
+        <v>1210</v>
+      </c>
+      <c r="X54" s="1">
         <f t="shared" si="1"/>
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C54" s="1">
-        <v>121</v>
-      </c>
-      <c r="D54" s="1">
-        <v>121</v>
-      </c>
-      <c r="E54" s="1">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C55" s="1">
+        <v>122</v>
+      </c>
+      <c r="D55" s="1">
+        <v>122</v>
+      </c>
+      <c r="E55" s="1">
         <v>2</v>
       </c>
-      <c r="F54" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="G54" s="1">
-        <v>49</v>
-      </c>
-      <c r="H54" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="I54" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="J54" s="13" t="s">
+      <c r="F55" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G55" s="1">
+        <v>50</v>
+      </c>
+      <c r="H55" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="K54" s="2">
+      <c r="I55" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="J55" s="6">
         <f t="shared" si="2"/>
-        <v>1400</v>
-      </c>
-      <c r="L54" s="2">
+        <v>1.22690437601297</v>
+      </c>
+      <c r="K55" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="L55" s="2">
         <f t="shared" si="3"/>
-        <v>730</v>
-      </c>
-      <c r="M54" s="2">
+        <v>1420</v>
+      </c>
+      <c r="M55" s="2">
         <f t="shared" si="4"/>
-        <v>291</v>
-      </c>
-      <c r="N54" s="2">
+        <v>740</v>
+      </c>
+      <c r="N55" s="2">
         <f t="shared" si="5"/>
-        <v>780</v>
-      </c>
-      <c r="O54" s="6">
-        <f t="shared" si="8"/>
+        <v>294</v>
+      </c>
+      <c r="O55" s="2">
+        <f t="shared" si="6"/>
+        <v>790</v>
+      </c>
+      <c r="P55" s="6">
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="P54" s="2">
-        <f t="shared" si="6"/>
-        <v>120</v>
-      </c>
-      <c r="Q54" s="2">
+      <c r="Q55" s="2">
         <f t="shared" si="7"/>
         <v>121</v>
       </c>
-      <c r="R54" s="1">
-        <v>0</v>
-      </c>
-      <c r="S54" s="1">
-        <v>0</v>
-      </c>
-      <c r="T54" s="4">
-        <v>0</v>
-      </c>
-      <c r="U54" s="4">
-        <v>0</v>
-      </c>
-      <c r="V54" s="1">
+      <c r="R55" s="2">
+        <f t="shared" si="8"/>
+        <v>122</v>
+      </c>
+      <c r="S55" s="1">
+        <v>0</v>
+      </c>
+      <c r="T55" s="1">
+        <v>0</v>
+      </c>
+      <c r="U55" s="4">
+        <v>0</v>
+      </c>
+      <c r="V55" s="4">
+        <v>0</v>
+      </c>
+      <c r="W55" s="1">
         <f t="shared" si="0"/>
-        <v>1210</v>
-      </c>
-      <c r="W54" s="1">
+        <v>1220</v>
+      </c>
+      <c r="X55" s="1">
         <f t="shared" si="1"/>
-        <v>1210</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C55" s="1">
-        <v>122</v>
-      </c>
-      <c r="D55" s="1">
-        <v>122</v>
-      </c>
-      <c r="E55" s="1">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C56" s="1">
+        <v>123</v>
+      </c>
+      <c r="D56" s="1">
+        <v>123</v>
+      </c>
+      <c r="E56" s="1">
         <v>2</v>
       </c>
-      <c r="F55" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="G55" s="1">
-        <v>50</v>
-      </c>
-      <c r="H55" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="I55" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="J55" s="13" t="s">
+      <c r="F56" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G56" s="1">
+        <v>51</v>
+      </c>
+      <c r="H56" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="K55" s="2">
+      <c r="I56" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="J56" s="6">
         <f t="shared" si="2"/>
-        <v>1420</v>
-      </c>
-      <c r="L55" s="2">
+        <v>1.22589167767503</v>
+      </c>
+      <c r="K56" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="L56" s="2">
         <f t="shared" si="3"/>
-        <v>740</v>
-      </c>
-      <c r="M55" s="2">
+        <v>1440</v>
+      </c>
+      <c r="M56" s="2">
         <f t="shared" si="4"/>
-        <v>294</v>
-      </c>
-      <c r="N55" s="2">
+        <v>750</v>
+      </c>
+      <c r="N56" s="2">
         <f t="shared" si="5"/>
-        <v>790</v>
-      </c>
-      <c r="O55" s="6">
-        <f t="shared" si="8"/>
+        <v>297</v>
+      </c>
+      <c r="O56" s="2">
+        <f t="shared" si="6"/>
+        <v>800</v>
+      </c>
+      <c r="P56" s="6">
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="P55" s="2">
-        <f t="shared" si="6"/>
-        <v>121</v>
-      </c>
-      <c r="Q55" s="2">
+      <c r="Q56" s="2">
         <f t="shared" si="7"/>
         <v>122</v>
       </c>
-      <c r="R55" s="1">
-        <v>0</v>
-      </c>
-      <c r="S55" s="1">
-        <v>0</v>
-      </c>
-      <c r="T55" s="4">
-        <v>0</v>
-      </c>
-      <c r="U55" s="4">
-        <v>0</v>
-      </c>
-      <c r="V55" s="1">
+      <c r="R56" s="2">
+        <f t="shared" si="8"/>
+        <v>123</v>
+      </c>
+      <c r="S56" s="1">
+        <v>0</v>
+      </c>
+      <c r="T56" s="1">
+        <v>0</v>
+      </c>
+      <c r="U56" s="4">
+        <v>0</v>
+      </c>
+      <c r="V56" s="4">
+        <v>0</v>
+      </c>
+      <c r="W56" s="1">
         <f t="shared" si="0"/>
-        <v>1220</v>
-      </c>
-      <c r="W55" s="1">
+        <v>1230</v>
+      </c>
+      <c r="X56" s="1">
         <f t="shared" si="1"/>
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C56" s="1">
-        <v>123</v>
-      </c>
-      <c r="D56" s="1">
-        <v>123</v>
-      </c>
-      <c r="E56" s="1">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C57" s="1">
+        <v>124</v>
+      </c>
+      <c r="D57" s="1">
+        <v>124</v>
+      </c>
+      <c r="E57" s="1">
         <v>2</v>
       </c>
-      <c r="F56" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="G56" s="1">
-        <v>51</v>
-      </c>
-      <c r="H56" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="I56" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="J56" s="13" t="s">
+      <c r="F57" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G57" s="1">
+        <v>52</v>
+      </c>
+      <c r="H57" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="K56" s="2">
+      <c r="I57" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="J57" s="6">
         <f t="shared" si="2"/>
-        <v>1440</v>
-      </c>
-      <c r="L56" s="2">
+        <v>1.22844827586207</v>
+      </c>
+      <c r="K57" s="13" t="s">
+        <v>264</v>
+      </c>
+      <c r="L57" s="2">
         <f t="shared" si="3"/>
-        <v>750</v>
-      </c>
-      <c r="M56" s="2">
+        <v>1460</v>
+      </c>
+      <c r="M57" s="2">
         <f t="shared" si="4"/>
-        <v>297</v>
-      </c>
-      <c r="N56" s="2">
+        <v>760</v>
+      </c>
+      <c r="N57" s="2">
         <f t="shared" si="5"/>
-        <v>800</v>
-      </c>
-      <c r="O56" s="6">
-        <f t="shared" si="8"/>
+        <v>300</v>
+      </c>
+      <c r="O57" s="2">
+        <f t="shared" si="6"/>
+        <v>810</v>
+      </c>
+      <c r="P57" s="6">
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="P56" s="2">
-        <f t="shared" si="6"/>
-        <v>122</v>
-      </c>
-      <c r="Q56" s="2">
+      <c r="Q57" s="2">
         <f t="shared" si="7"/>
         <v>123</v>
       </c>
-      <c r="R56" s="1">
-        <v>0</v>
-      </c>
-      <c r="S56" s="1">
-        <v>0</v>
-      </c>
-      <c r="T56" s="4">
-        <v>0</v>
-      </c>
-      <c r="U56" s="4">
-        <v>0</v>
-      </c>
-      <c r="V56" s="1">
+      <c r="R57" s="2">
+        <f t="shared" si="8"/>
+        <v>124</v>
+      </c>
+      <c r="S57" s="1">
+        <v>0</v>
+      </c>
+      <c r="T57" s="1">
+        <v>0</v>
+      </c>
+      <c r="U57" s="4">
+        <v>0</v>
+      </c>
+      <c r="V57" s="4">
+        <v>0</v>
+      </c>
+      <c r="W57" s="1">
         <f t="shared" si="0"/>
-        <v>1230</v>
-      </c>
-      <c r="W56" s="1">
+        <v>1240</v>
+      </c>
+      <c r="X57" s="1">
         <f t="shared" si="1"/>
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C57" s="1">
-        <v>124</v>
-      </c>
-      <c r="D57" s="1">
-        <v>124</v>
-      </c>
-      <c r="E57" s="1">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C58" s="1">
+        <v>125</v>
+      </c>
+      <c r="D58" s="1">
+        <v>125</v>
+      </c>
+      <c r="E58" s="1">
         <v>2</v>
       </c>
-      <c r="F57" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="G57" s="1">
-        <v>52</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="J57" s="13" t="s">
+      <c r="F58" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G58" s="1">
+        <v>53</v>
+      </c>
+      <c r="H58" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="K57" s="2">
+      <c r="I58" s="13" t="s">
+        <v>266</v>
+      </c>
+      <c r="J58" s="6">
         <f t="shared" si="2"/>
-        <v>1460</v>
-      </c>
-      <c r="L57" s="2">
+        <v>1.21929824561404</v>
+      </c>
+      <c r="K58" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="L58" s="2">
         <f t="shared" si="3"/>
-        <v>760</v>
-      </c>
-      <c r="M57" s="2">
+        <v>1480</v>
+      </c>
+      <c r="M58" s="2">
         <f t="shared" si="4"/>
-        <v>300</v>
-      </c>
-      <c r="N57" s="2">
+        <v>770</v>
+      </c>
+      <c r="N58" s="2">
         <f t="shared" si="5"/>
-        <v>810</v>
-      </c>
-      <c r="O57" s="6">
-        <f t="shared" si="8"/>
+        <v>303</v>
+      </c>
+      <c r="O58" s="2">
+        <f t="shared" si="6"/>
+        <v>820</v>
+      </c>
+      <c r="P58" s="6">
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="P57" s="2">
-        <f t="shared" si="6"/>
-        <v>123</v>
-      </c>
-      <c r="Q57" s="2">
+      <c r="Q58" s="2">
         <f t="shared" si="7"/>
         <v>124</v>
       </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
-      <c r="S57" s="1">
-        <v>0</v>
-      </c>
-      <c r="T57" s="4">
-        <v>0</v>
-      </c>
-      <c r="U57" s="4">
-        <v>0</v>
-      </c>
-      <c r="V57" s="1">
+      <c r="R58" s="2">
+        <f t="shared" si="8"/>
+        <v>125</v>
+      </c>
+      <c r="S58" s="1">
+        <v>0</v>
+      </c>
+      <c r="T58" s="1">
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <v>0</v>
+      </c>
+      <c r="W58" s="1">
         <f t="shared" si="0"/>
-        <v>1240</v>
-      </c>
-      <c r="W57" s="1">
+        <v>1250</v>
+      </c>
+      <c r="X58" s="1">
         <f t="shared" si="1"/>
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C58" s="1">
-        <v>125</v>
-      </c>
-      <c r="D58" s="1">
-        <v>125</v>
-      </c>
-      <c r="E58" s="1">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="59" s="3" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C59" s="1">
+        <v>126</v>
+      </c>
+      <c r="D59" s="1">
+        <v>126</v>
+      </c>
+      <c r="E59" s="1">
         <v>2</v>
       </c>
-      <c r="F58" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="G58" s="1">
-        <v>53</v>
-      </c>
-      <c r="H58" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="I58" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="J58" s="13" t="s">
+      <c r="F59" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G59" s="5">
+        <v>54</v>
+      </c>
+      <c r="H59" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="K58" s="2">
+      <c r="I59" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="J59" s="6">
         <f t="shared" si="2"/>
-        <v>1480</v>
-      </c>
-      <c r="L58" s="2">
+        <v>1.22302158273381</v>
+      </c>
+      <c r="K59" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="L59" s="2">
         <f t="shared" si="3"/>
-        <v>770</v>
-      </c>
-      <c r="M58" s="2">
+        <v>1500</v>
+      </c>
+      <c r="M59" s="2">
         <f t="shared" si="4"/>
-        <v>303</v>
-      </c>
-      <c r="N58" s="2">
+        <v>780</v>
+      </c>
+      <c r="N59" s="2">
         <f t="shared" si="5"/>
-        <v>820</v>
-      </c>
-      <c r="O58" s="6">
-        <f t="shared" si="8"/>
+        <v>306</v>
+      </c>
+      <c r="O59" s="2">
+        <f t="shared" si="6"/>
+        <v>830</v>
+      </c>
+      <c r="P59" s="6">
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="P58" s="2">
-        <f t="shared" si="6"/>
-        <v>124</v>
-      </c>
-      <c r="Q58" s="2">
+      <c r="Q59" s="2">
         <f t="shared" si="7"/>
         <v>125</v>
       </c>
-      <c r="R58" s="1">
-        <v>0</v>
-      </c>
-      <c r="S58" s="1">
-        <v>0</v>
-      </c>
-      <c r="T58" s="4">
-        <v>0</v>
-      </c>
-      <c r="U58" s="4">
-        <v>0</v>
-      </c>
-      <c r="V58" s="1">
+      <c r="R59" s="2">
+        <f t="shared" si="8"/>
+        <v>126</v>
+      </c>
+      <c r="S59" s="5">
+        <v>0</v>
+      </c>
+      <c r="T59" s="5">
+        <v>0</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3">
+        <v>0</v>
+      </c>
+      <c r="W59" s="1">
         <f t="shared" si="0"/>
-        <v>1250</v>
-      </c>
-      <c r="W58" s="1">
+        <v>1260</v>
+      </c>
+      <c r="X59" s="1">
         <f t="shared" si="1"/>
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="59" s="3" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C59" s="1">
-        <v>126</v>
-      </c>
-      <c r="D59" s="1">
-        <v>126</v>
-      </c>
-      <c r="E59" s="1">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C60" s="1">
+        <v>127</v>
+      </c>
+      <c r="D60" s="1">
+        <v>127</v>
+      </c>
+      <c r="E60" s="1">
         <v>2</v>
       </c>
-      <c r="F59" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="G59" s="5">
-        <v>54</v>
-      </c>
-      <c r="H59" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="I59" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="J59" s="13" t="s">
+      <c r="F60" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G60" s="1">
+        <v>55</v>
+      </c>
+      <c r="H60" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="K59" s="2">
+      <c r="I60" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="J60" s="6">
         <f t="shared" si="2"/>
-        <v>1500</v>
-      </c>
-      <c r="L59" s="2">
+        <v>1.22352941176471</v>
+      </c>
+      <c r="K60" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="L60" s="2">
         <f t="shared" si="3"/>
-        <v>780</v>
-      </c>
-      <c r="M59" s="2">
+        <v>1520</v>
+      </c>
+      <c r="M60" s="2">
         <f t="shared" si="4"/>
-        <v>306</v>
-      </c>
-      <c r="N59" s="2">
+        <v>790</v>
+      </c>
+      <c r="N60" s="2">
         <f t="shared" si="5"/>
-        <v>830</v>
-      </c>
-      <c r="O59" s="6">
-        <f t="shared" si="8"/>
-        <v>21</v>
-      </c>
-      <c r="P59" s="2">
+        <v>309</v>
+      </c>
+      <c r="O60" s="2">
         <f t="shared" si="6"/>
-        <v>125</v>
-      </c>
-      <c r="Q59" s="2">
+        <v>840</v>
+      </c>
+      <c r="P60" s="6">
+        <f t="shared" si="9"/>
+        <v>22</v>
+      </c>
+      <c r="Q60" s="2">
         <f t="shared" si="7"/>
         <v>126</v>
       </c>
-      <c r="R59" s="5">
-        <v>0</v>
-      </c>
-      <c r="S59" s="5">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
-      <c r="V59" s="1">
+      <c r="R60" s="2">
+        <f t="shared" si="8"/>
+        <v>127</v>
+      </c>
+      <c r="S60" s="1">
+        <v>0</v>
+      </c>
+      <c r="T60" s="1">
+        <v>0</v>
+      </c>
+      <c r="U60" s="4">
+        <v>0</v>
+      </c>
+      <c r="V60" s="4">
+        <v>0</v>
+      </c>
+      <c r="W60" s="1">
         <f t="shared" si="0"/>
-        <v>1260</v>
-      </c>
-      <c r="W59" s="1">
+        <v>1270</v>
+      </c>
+      <c r="X60" s="1">
         <f t="shared" si="1"/>
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C60" s="1">
-        <v>127</v>
-      </c>
-      <c r="D60" s="1">
-        <v>127</v>
-      </c>
-      <c r="E60" s="1">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C61" s="1">
+        <v>128</v>
+      </c>
+      <c r="D61" s="1">
+        <v>128</v>
+      </c>
+      <c r="E61" s="1">
         <v>2</v>
       </c>
-      <c r="F60" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G60" s="1">
-        <v>55</v>
-      </c>
-      <c r="H60" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="J60" s="13" t="s">
+      <c r="F61" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G61" s="1">
+        <v>56</v>
+      </c>
+      <c r="H61" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="K60" s="2">
+      <c r="I61" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="J61" s="6">
         <f t="shared" si="2"/>
-        <v>1520</v>
-      </c>
-      <c r="L60" s="2">
+        <v>1.23076923076923</v>
+      </c>
+      <c r="K61" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="L61" s="2">
         <f t="shared" si="3"/>
-        <v>790</v>
-      </c>
-      <c r="M60" s="2">
+        <v>1540</v>
+      </c>
+      <c r="M61" s="2">
         <f t="shared" si="4"/>
-        <v>309</v>
-      </c>
-      <c r="N60" s="2">
+        <v>800</v>
+      </c>
+      <c r="N61" s="2">
         <f t="shared" si="5"/>
-        <v>840</v>
-      </c>
-      <c r="O60" s="6">
-        <f t="shared" si="8"/>
+        <v>312</v>
+      </c>
+      <c r="O61" s="2">
+        <f t="shared" si="6"/>
+        <v>850</v>
+      </c>
+      <c r="P61" s="6">
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="P60" s="2">
-        <f t="shared" si="6"/>
-        <v>126</v>
-      </c>
-      <c r="Q60" s="2">
+      <c r="Q61" s="2">
         <f t="shared" si="7"/>
         <v>127</v>
       </c>
-      <c r="R60" s="1">
-        <v>0</v>
-      </c>
-      <c r="S60" s="1">
-        <v>0</v>
-      </c>
-      <c r="T60" s="4">
-        <v>0</v>
-      </c>
-      <c r="U60" s="4">
-        <v>0</v>
-      </c>
-      <c r="V60" s="1">
+      <c r="R61" s="2">
+        <f t="shared" si="8"/>
+        <v>128</v>
+      </c>
+      <c r="S61" s="1">
+        <v>0</v>
+      </c>
+      <c r="T61" s="1">
+        <v>0</v>
+      </c>
+      <c r="U61" s="4">
+        <v>0</v>
+      </c>
+      <c r="V61" s="4">
+        <v>0</v>
+      </c>
+      <c r="W61" s="1">
         <f t="shared" si="0"/>
-        <v>1270</v>
-      </c>
-      <c r="W60" s="1">
+        <v>1280</v>
+      </c>
+      <c r="X61" s="1">
         <f t="shared" si="1"/>
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C61" s="1">
-        <v>128</v>
-      </c>
-      <c r="D61" s="1">
-        <v>128</v>
-      </c>
-      <c r="E61" s="1">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C62" s="1">
+        <v>129</v>
+      </c>
+      <c r="D62" s="1">
+        <v>129</v>
+      </c>
+      <c r="E62" s="1">
         <v>2</v>
       </c>
-      <c r="F61" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="G61" s="1">
-        <v>56</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="I61" s="13" t="s">
+      <c r="F62" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G62" s="1">
+        <v>57</v>
+      </c>
+      <c r="H62" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="J61" s="13" t="s">
+      <c r="I62" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="K61" s="2">
+      <c r="J62" s="6">
         <f t="shared" si="2"/>
-        <v>1540</v>
-      </c>
-      <c r="L61" s="2">
+        <v>1.22265625</v>
+      </c>
+      <c r="K62" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="L62" s="2">
         <f t="shared" si="3"/>
-        <v>800</v>
-      </c>
-      <c r="M61" s="2">
+        <v>1560</v>
+      </c>
+      <c r="M62" s="2">
         <f t="shared" si="4"/>
-        <v>312</v>
-      </c>
-      <c r="N61" s="2">
+        <v>810</v>
+      </c>
+      <c r="N62" s="2">
         <f t="shared" si="5"/>
-        <v>850</v>
-      </c>
-      <c r="O61" s="6">
-        <f t="shared" si="8"/>
+        <v>315</v>
+      </c>
+      <c r="O62" s="2">
+        <f t="shared" si="6"/>
+        <v>860</v>
+      </c>
+      <c r="P62" s="6">
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="P61" s="2">
-        <f t="shared" si="6"/>
-        <v>127</v>
-      </c>
-      <c r="Q61" s="2">
+      <c r="Q62" s="2">
         <f t="shared" si="7"/>
         <v>128</v>
       </c>
-      <c r="R61" s="1">
-        <v>0</v>
-      </c>
-      <c r="S61" s="1">
-        <v>0</v>
-      </c>
-      <c r="T61" s="4">
-        <v>0</v>
-      </c>
-      <c r="U61" s="4">
-        <v>0</v>
-      </c>
-      <c r="V61" s="1">
+      <c r="R62" s="2">
+        <f t="shared" si="8"/>
+        <v>129</v>
+      </c>
+      <c r="S62" s="1">
+        <v>0</v>
+      </c>
+      <c r="T62" s="1">
+        <v>0</v>
+      </c>
+      <c r="U62" s="4">
+        <v>0</v>
+      </c>
+      <c r="V62" s="4">
+        <v>0</v>
+      </c>
+      <c r="W62" s="1">
         <f t="shared" si="0"/>
-        <v>1280</v>
-      </c>
-      <c r="W61" s="1">
+        <v>1290</v>
+      </c>
+      <c r="X62" s="1">
         <f t="shared" si="1"/>
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C62" s="1">
-        <v>129</v>
-      </c>
-      <c r="D62" s="1">
-        <v>129</v>
-      </c>
-      <c r="E62" s="1">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C63" s="1">
+        <v>130</v>
+      </c>
+      <c r="D63" s="1">
+        <v>130</v>
+      </c>
+      <c r="E63" s="1">
         <v>2</v>
       </c>
-      <c r="F62" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G62" s="1">
-        <v>57</v>
-      </c>
-      <c r="H62" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="I62" s="13" t="s">
+      <c r="F63" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G63" s="1">
+        <v>58</v>
+      </c>
+      <c r="H63" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="J62" s="13" t="s">
+      <c r="I63" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="K62" s="2">
+      <c r="J63" s="6">
         <f t="shared" si="2"/>
-        <v>1560</v>
-      </c>
-      <c r="L62" s="2">
+        <v>1.22364217252396</v>
+      </c>
+      <c r="K63" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="L63" s="2">
         <f t="shared" si="3"/>
-        <v>810</v>
-      </c>
-      <c r="M62" s="2">
+        <v>1580</v>
+      </c>
+      <c r="M63" s="2">
         <f t="shared" si="4"/>
-        <v>315</v>
-      </c>
-      <c r="N62" s="2">
+        <v>820</v>
+      </c>
+      <c r="N63" s="2">
         <f t="shared" si="5"/>
-        <v>860</v>
-      </c>
-      <c r="O62" s="6">
-        <f t="shared" si="8"/>
+        <v>318</v>
+      </c>
+      <c r="O63" s="2">
+        <f t="shared" si="6"/>
+        <v>870</v>
+      </c>
+      <c r="P63" s="6">
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="P62" s="2">
-        <f t="shared" si="6"/>
-        <v>128</v>
-      </c>
-      <c r="Q62" s="2">
+      <c r="Q63" s="2">
         <f t="shared" si="7"/>
         <v>129</v>
       </c>
-      <c r="R62" s="1">
-        <v>0</v>
-      </c>
-      <c r="S62" s="1">
-        <v>0</v>
-      </c>
-      <c r="T62" s="4">
-        <v>0</v>
-      </c>
-      <c r="U62" s="4">
-        <v>0</v>
-      </c>
-      <c r="V62" s="1">
+      <c r="R63" s="2">
+        <f t="shared" si="8"/>
+        <v>130</v>
+      </c>
+      <c r="S63" s="1">
+        <v>0</v>
+      </c>
+      <c r="T63" s="1">
+        <v>0</v>
+      </c>
+      <c r="U63" s="4">
+        <v>0</v>
+      </c>
+      <c r="V63" s="4">
+        <v>0</v>
+      </c>
+      <c r="W63" s="1">
         <f t="shared" si="0"/>
-        <v>1290</v>
-      </c>
-      <c r="W62" s="1">
+        <v>1300</v>
+      </c>
+      <c r="X63" s="1">
         <f t="shared" si="1"/>
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C63" s="1">
-        <v>130</v>
-      </c>
-      <c r="D63" s="1">
-        <v>130</v>
-      </c>
-      <c r="E63" s="1">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:24">
+      <c r="C64" s="1">
+        <v>131</v>
+      </c>
+      <c r="D64" s="1">
+        <v>131</v>
+      </c>
+      <c r="E64" s="1">
         <v>2</v>
       </c>
-      <c r="F63" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="G63" s="1">
-        <v>58</v>
-      </c>
-      <c r="H63" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="I63" s="13" t="s">
+      <c r="F64" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="G64" s="1">
+        <v>59</v>
+      </c>
+      <c r="H64" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="J63" s="13" t="s">
+      <c r="I64" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="K63" s="2">
+      <c r="J64" s="6">
         <f t="shared" si="2"/>
-        <v>1580</v>
-      </c>
-      <c r="L63" s="2">
+        <v>1.22193211488251</v>
+      </c>
+      <c r="K64" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="L64" s="2">
         <f t="shared" si="3"/>
-        <v>820</v>
-      </c>
-      <c r="M63" s="2">
+        <v>1600</v>
+      </c>
+      <c r="M64" s="2">
         <f t="shared" si="4"/>
-        <v>318</v>
-      </c>
-      <c r="N63" s="2">
+        <v>830</v>
+      </c>
+      <c r="N64" s="2">
         <f t="shared" si="5"/>
-        <v>870</v>
-      </c>
-      <c r="O63" s="6">
-        <f t="shared" si="8"/>
+        <v>321</v>
+      </c>
+      <c r="O64" s="2">
+        <f t="shared" si="6"/>
+        <v>880</v>
+      </c>
+      <c r="P64" s="6">
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="P63" s="2">
-        <f t="shared" si="6"/>
-        <v>129</v>
-      </c>
-      <c r="Q63" s="2">
+      <c r="Q64" s="2">
         <f t="shared" si="7"/>
         <v>130</v>
       </c>
-      <c r="R63" s="1">
-        <v>0</v>
-      </c>
-      <c r="S63" s="1">
-        <v>0</v>
-      </c>
-      <c r="T63" s="4">
-        <v>0</v>
-      </c>
-      <c r="U63" s="4">
-        <v>0</v>
-      </c>
-      <c r="V63" s="1">
+      <c r="R64" s="2">
+        <f t="shared" si="8"/>
+        <v>131</v>
+      </c>
+      <c r="S64" s="1">
+        <v>0</v>
+      </c>
+      <c r="T64" s="1">
+        <v>0</v>
+      </c>
+      <c r="U64" s="4">
+        <v>0</v>
+      </c>
+      <c r="V64" s="4">
+        <v>0</v>
+      </c>
+      <c r="W64" s="1">
         <f t="shared" si="0"/>
-        <v>1300</v>
-      </c>
-      <c r="W63" s="1">
+        <v>1310</v>
+      </c>
+      <c r="X64" s="1">
         <f t="shared" si="1"/>
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:23">
-      <c r="C64" s="1">
-        <v>131</v>
-      </c>
-      <c r="D64" s="1">
-        <v>131</v>
-      </c>
-      <c r="E64" s="1">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="65" s="3" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C65" s="1">
+        <v>132</v>
+      </c>
+      <c r="D65" s="1">
+        <v>132</v>
+      </c>
+      <c r="E65" s="1">
         <v>2</v>
       </c>
-      <c r="F64" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="G64" s="1">
-        <v>59</v>
-      </c>
-      <c r="H64" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="I64" s="13" t="s">
+      <c r="F65" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G65" s="5">
+        <v>60</v>
+      </c>
+      <c r="H65" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="J64" s="13" t="s">
+      <c r="I65" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="K64" s="2">
+      <c r="J65" s="6">
         <f t="shared" si="2"/>
-        <v>1600</v>
-      </c>
-      <c r="L64" s="2">
+        <v>1.22222222222222</v>
+      </c>
+      <c r="K65" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="L65" s="2">
         <f t="shared" si="3"/>
-        <v>830</v>
-      </c>
-      <c r="M64" s="2">
+        <v>1620</v>
+      </c>
+      <c r="M65" s="2">
         <f t="shared" si="4"/>
-        <v>321</v>
-      </c>
-      <c r="N64" s="2">
+        <v>840</v>
+      </c>
+      <c r="N65" s="2">
         <f t="shared" si="5"/>
-        <v>880</v>
-      </c>
-      <c r="O64" s="6">
-        <f t="shared" si="8"/>
+        <v>324</v>
+      </c>
+      <c r="O65" s="2">
+        <f t="shared" si="6"/>
+        <v>890</v>
+      </c>
+      <c r="P65" s="6">
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="P64" s="2">
-        <f t="shared" si="6"/>
-        <v>130</v>
-      </c>
-      <c r="Q64" s="2">
+      <c r="Q65" s="2">
         <f t="shared" si="7"/>
         <v>131</v>
       </c>
-      <c r="R64" s="1">
-        <v>0</v>
-      </c>
-      <c r="S64" s="1">
-        <v>0</v>
-      </c>
-      <c r="T64" s="4">
-        <v>0</v>
-      </c>
-      <c r="U64" s="4">
-        <v>0</v>
-      </c>
-      <c r="V64" s="1">
+      <c r="R65" s="2">
+        <f t="shared" si="8"/>
+        <v>132</v>
+      </c>
+      <c r="S65" s="5">
+        <v>0</v>
+      </c>
+      <c r="T65" s="5">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="1">
         <f t="shared" si="0"/>
-        <v>1310</v>
-      </c>
-      <c r="W64" s="1">
+        <v>1320</v>
+      </c>
+      <c r="X65" s="1">
         <f t="shared" si="1"/>
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="65" s="3" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C65" s="1">
-        <v>132</v>
-      </c>
-      <c r="D65" s="1">
-        <v>132</v>
-      </c>
-      <c r="E65" s="1">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C66" s="1">
+        <v>133</v>
+      </c>
+      <c r="D66" s="1">
+        <v>133</v>
+      </c>
+      <c r="E66" s="1">
         <v>2</v>
       </c>
-      <c r="F65" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="G65" s="5">
-        <v>60</v>
-      </c>
-      <c r="H65" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="I65" s="13" t="s">
+      <c r="F66" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G66" s="1">
+        <v>61</v>
+      </c>
+      <c r="H66" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="J65" s="13" t="s">
+      <c r="I66" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="K65" s="2">
+      <c r="J66" s="6">
         <f t="shared" si="2"/>
-        <v>1620</v>
-      </c>
-      <c r="L65" s="2">
+        <v>1.21853146853147</v>
+      </c>
+      <c r="K66" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="L66" s="2">
         <f t="shared" si="3"/>
-        <v>840</v>
-      </c>
-      <c r="M65" s="2">
+        <v>1640</v>
+      </c>
+      <c r="M66" s="2">
         <f t="shared" si="4"/>
-        <v>324</v>
-      </c>
-      <c r="N65" s="2">
+        <v>850</v>
+      </c>
+      <c r="N66" s="2">
         <f t="shared" si="5"/>
-        <v>890</v>
-      </c>
-      <c r="O65" s="6">
-        <f t="shared" si="8"/>
-        <v>22</v>
-      </c>
-      <c r="P65" s="2">
+        <v>327</v>
+      </c>
+      <c r="O66" s="2">
         <f t="shared" si="6"/>
-        <v>131</v>
-      </c>
-      <c r="Q65" s="2">
+        <v>900</v>
+      </c>
+      <c r="P66" s="6">
+        <f t="shared" si="9"/>
+        <v>23</v>
+      </c>
+      <c r="Q66" s="2">
         <f t="shared" si="7"/>
         <v>132</v>
       </c>
-      <c r="R65" s="5">
-        <v>0</v>
-      </c>
-      <c r="S65" s="5">
-        <v>0</v>
-      </c>
-      <c r="T65" s="3">
-        <v>0</v>
-      </c>
-      <c r="U65" s="3">
-        <v>0</v>
-      </c>
-      <c r="V65" s="1">
+      <c r="R66" s="2">
+        <f t="shared" si="8"/>
+        <v>133</v>
+      </c>
+      <c r="S66" s="1">
+        <v>0</v>
+      </c>
+      <c r="T66" s="1">
+        <v>0</v>
+      </c>
+      <c r="U66" s="4">
+        <v>0</v>
+      </c>
+      <c r="V66" s="4">
+        <v>0</v>
+      </c>
+      <c r="W66" s="1">
         <f t="shared" si="0"/>
-        <v>1320</v>
-      </c>
-      <c r="W65" s="1">
+        <v>1330</v>
+      </c>
+      <c r="X66" s="1">
         <f t="shared" si="1"/>
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="66" s="2" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C66" s="1">
-        <v>133</v>
-      </c>
-      <c r="D66" s="1">
-        <v>133</v>
-      </c>
-      <c r="E66" s="1">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C67" s="1">
+        <v>134</v>
+      </c>
+      <c r="D67" s="1">
+        <v>134</v>
+      </c>
+      <c r="E67" s="1">
         <v>2</v>
       </c>
-      <c r="F66" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G66" s="1">
-        <v>61</v>
-      </c>
-      <c r="H66" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="I66" s="13" t="s">
+      <c r="F67" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G67" s="1">
+        <v>62</v>
+      </c>
+      <c r="H67" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="J66" s="13" t="s">
+      <c r="I67" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="K66" s="2">
+      <c r="J67" s="6">
         <f t="shared" si="2"/>
-        <v>1640</v>
-      </c>
-      <c r="L66" s="2">
+        <v>1.22238163558106</v>
+      </c>
+      <c r="K67" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="L67" s="2">
         <f t="shared" si="3"/>
-        <v>850</v>
-      </c>
-      <c r="M66" s="2">
+        <v>1660</v>
+      </c>
+      <c r="M67" s="2">
         <f t="shared" si="4"/>
-        <v>327</v>
-      </c>
-      <c r="N66" s="2">
+        <v>860</v>
+      </c>
+      <c r="N67" s="2">
         <f t="shared" si="5"/>
-        <v>900</v>
-      </c>
-      <c r="O66" s="6">
-        <f t="shared" si="8"/>
+        <v>330</v>
+      </c>
+      <c r="O67" s="2">
+        <f t="shared" si="6"/>
+        <v>910</v>
+      </c>
+      <c r="P67" s="6">
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="P66" s="2">
-        <f t="shared" si="6"/>
-        <v>132</v>
-      </c>
-      <c r="Q66" s="2">
+      <c r="Q67" s="2">
         <f t="shared" si="7"/>
         <v>133</v>
       </c>
-      <c r="R66" s="1">
-        <v>0</v>
-      </c>
-      <c r="S66" s="1">
-        <v>0</v>
-      </c>
-      <c r="T66" s="4">
-        <v>0</v>
-      </c>
-      <c r="U66" s="4">
-        <v>0</v>
-      </c>
-      <c r="V66" s="1">
+      <c r="R67" s="2">
+        <f t="shared" si="8"/>
+        <v>134</v>
+      </c>
+      <c r="S67" s="1">
+        <v>0</v>
+      </c>
+      <c r="T67" s="1">
+        <v>0</v>
+      </c>
+      <c r="U67" s="4">
+        <v>0</v>
+      </c>
+      <c r="V67" s="4">
+        <v>0</v>
+      </c>
+      <c r="W67" s="1">
         <f t="shared" si="0"/>
-        <v>1330</v>
-      </c>
-      <c r="W66" s="1">
+        <v>1340</v>
+      </c>
+      <c r="X67" s="1">
         <f t="shared" si="1"/>
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="67" s="2" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C67" s="1">
-        <v>134</v>
-      </c>
-      <c r="D67" s="1">
-        <v>134</v>
-      </c>
-      <c r="E67" s="1">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C68" s="1">
+        <v>135</v>
+      </c>
+      <c r="D68" s="1">
+        <v>135</v>
+      </c>
+      <c r="E68" s="1">
         <v>2</v>
       </c>
-      <c r="F67" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="G67" s="1">
-        <v>62</v>
-      </c>
-      <c r="H67" s="14" t="s">
-        <v>293</v>
-      </c>
-      <c r="I67" s="13" t="s">
+      <c r="F68" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G68" s="1">
+        <v>63</v>
+      </c>
+      <c r="H68" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="J67" s="13" t="s">
+      <c r="I68" s="13" t="s">
         <v>295</v>
       </c>
-      <c r="K67" s="2">
+      <c r="J68" s="6">
         <f t="shared" si="2"/>
-        <v>1660</v>
-      </c>
-      <c r="L67" s="2">
+        <v>1.22065727699531</v>
+      </c>
+      <c r="K68" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="L68" s="2">
         <f t="shared" si="3"/>
-        <v>860</v>
-      </c>
-      <c r="M67" s="2">
+        <v>1680</v>
+      </c>
+      <c r="M68" s="2">
         <f t="shared" si="4"/>
-        <v>330</v>
-      </c>
-      <c r="N67" s="2">
+        <v>870</v>
+      </c>
+      <c r="N68" s="2">
         <f t="shared" si="5"/>
-        <v>910</v>
-      </c>
-      <c r="O67" s="6">
-        <f t="shared" si="8"/>
+        <v>333</v>
+      </c>
+      <c r="O68" s="2">
+        <f t="shared" si="6"/>
+        <v>920</v>
+      </c>
+      <c r="P68" s="6">
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="P67" s="2">
-        <f t="shared" si="6"/>
-        <v>133</v>
-      </c>
-      <c r="Q67" s="2">
+      <c r="Q68" s="2">
         <f t="shared" si="7"/>
         <v>134</v>
       </c>
-      <c r="R67" s="1">
-        <v>0</v>
-      </c>
-      <c r="S67" s="1">
-        <v>0</v>
-      </c>
-      <c r="T67" s="4">
-        <v>0</v>
-      </c>
-      <c r="U67" s="4">
-        <v>0</v>
-      </c>
-      <c r="V67" s="1">
+      <c r="R68" s="2">
+        <f t="shared" si="8"/>
+        <v>135</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="T68" s="1">
+        <v>0</v>
+      </c>
+      <c r="U68" s="4">
+        <v>0</v>
+      </c>
+      <c r="V68" s="4">
+        <v>0</v>
+      </c>
+      <c r="W68" s="1">
         <f t="shared" si="0"/>
-        <v>1340</v>
-      </c>
-      <c r="W67" s="1">
+        <v>1350</v>
+      </c>
+      <c r="X68" s="1">
         <f t="shared" si="1"/>
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C68" s="1">
-        <v>135</v>
-      </c>
-      <c r="D68" s="1">
-        <v>135</v>
-      </c>
-      <c r="E68" s="1">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C69" s="1">
+        <v>136</v>
+      </c>
+      <c r="D69" s="1">
+        <v>136</v>
+      </c>
+      <c r="E69" s="1">
         <v>2</v>
       </c>
-      <c r="F68" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G68" s="1">
-        <v>63</v>
-      </c>
-      <c r="H68" s="14" t="s">
-        <v>296</v>
-      </c>
-      <c r="I68" s="13" t="s">
+      <c r="F69" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G69" s="1">
+        <v>64</v>
+      </c>
+      <c r="H69" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="J68" s="13" t="s">
+      <c r="I69" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="K68" s="2">
+      <c r="J69" s="6">
         <f t="shared" si="2"/>
-        <v>1680</v>
-      </c>
-      <c r="L68" s="2">
+        <v>1.22115384615385</v>
+      </c>
+      <c r="K69" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="L69" s="2">
         <f t="shared" si="3"/>
-        <v>870</v>
-      </c>
-      <c r="M68" s="2">
+        <v>1700</v>
+      </c>
+      <c r="M69" s="2">
         <f t="shared" si="4"/>
-        <v>333</v>
-      </c>
-      <c r="N68" s="2">
+        <v>880</v>
+      </c>
+      <c r="N69" s="2">
         <f t="shared" si="5"/>
-        <v>920</v>
-      </c>
-      <c r="O68" s="6">
-        <f t="shared" si="8"/>
+        <v>336</v>
+      </c>
+      <c r="O69" s="2">
+        <f t="shared" si="6"/>
+        <v>930</v>
+      </c>
+      <c r="P69" s="6">
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="P68" s="2">
-        <f t="shared" si="6"/>
-        <v>134</v>
-      </c>
-      <c r="Q68" s="2">
+      <c r="Q69" s="2">
         <f t="shared" si="7"/>
         <v>135</v>
       </c>
-      <c r="R68" s="1">
-        <v>0</v>
-      </c>
-      <c r="S68" s="1">
-        <v>0</v>
-      </c>
-      <c r="T68" s="4">
-        <v>0</v>
-      </c>
-      <c r="U68" s="4">
-        <v>0</v>
-      </c>
-      <c r="V68" s="1">
+      <c r="R69" s="2">
+        <f t="shared" si="8"/>
+        <v>136</v>
+      </c>
+      <c r="S69" s="1">
+        <v>0</v>
+      </c>
+      <c r="T69" s="1">
+        <v>0</v>
+      </c>
+      <c r="U69" s="4">
+        <v>0</v>
+      </c>
+      <c r="V69" s="4">
+        <v>0</v>
+      </c>
+      <c r="W69" s="1">
         <f t="shared" si="0"/>
-        <v>1350</v>
-      </c>
-      <c r="W68" s="1">
+        <v>1360</v>
+      </c>
+      <c r="X69" s="1">
         <f t="shared" si="1"/>
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C69" s="1">
-        <v>136</v>
-      </c>
-      <c r="D69" s="1">
-        <v>136</v>
-      </c>
-      <c r="E69" s="1">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="C70" s="1">
+        <v>137</v>
+      </c>
+      <c r="D70" s="1">
+        <v>137</v>
+      </c>
+      <c r="E70" s="1">
         <v>2</v>
       </c>
-      <c r="F69" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="G69" s="1">
-        <v>64</v>
-      </c>
-      <c r="H69" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="I69" s="13" t="s">
+      <c r="F70" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G70" s="1">
+        <v>65</v>
+      </c>
+      <c r="H70" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="J69" s="13" t="s">
+      <c r="I70" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="K69" s="2">
+      <c r="J70" s="6">
         <f t="shared" si="2"/>
-        <v>1700</v>
-      </c>
-      <c r="L69" s="2">
+        <v>1.22047244094488</v>
+      </c>
+      <c r="K70" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="L70" s="2">
         <f t="shared" si="3"/>
-        <v>880</v>
-      </c>
-      <c r="M69" s="2">
+        <v>1720</v>
+      </c>
+      <c r="M70" s="2">
         <f t="shared" si="4"/>
-        <v>336</v>
-      </c>
-      <c r="N69" s="2">
+        <v>890</v>
+      </c>
+      <c r="N70" s="2">
         <f t="shared" si="5"/>
-        <v>930</v>
-      </c>
-      <c r="O69" s="6">
-        <f t="shared" si="8"/>
+        <v>339</v>
+      </c>
+      <c r="O70" s="2">
+        <f t="shared" si="6"/>
+        <v>940</v>
+      </c>
+      <c r="P70" s="6">
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="P69" s="2">
-        <f t="shared" si="6"/>
-        <v>135</v>
-      </c>
-      <c r="Q69" s="2">
+      <c r="Q70" s="2">
         <f t="shared" si="7"/>
         <v>136</v>
       </c>
-      <c r="R69" s="1">
-        <v>0</v>
-      </c>
-      <c r="S69" s="1">
-        <v>0</v>
-      </c>
-      <c r="T69" s="4">
-        <v>0</v>
-      </c>
-      <c r="U69" s="4">
-        <v>0</v>
-      </c>
-      <c r="V69" s="1">
-        <f t="shared" si="0"/>
-        <v>1360</v>
-      </c>
-      <c r="W69" s="1">
-        <f t="shared" si="1"/>
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" customHeight="1" spans="1:23">
-      <c r="C70" s="1">
+      <c r="R70" s="2">
+        <f t="shared" si="8"/>
         <v>137</v>
       </c>
-      <c r="D70" s="1">
-        <v>137</v>
-      </c>
-      <c r="E70" s="1">
-        <v>2</v>
-      </c>
-      <c r="F70" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G70" s="1">
-        <v>65</v>
-      </c>
-      <c r="H70" s="14" t="s">
-        <v>302</v>
-      </c>
-      <c r="I70" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="J70" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="K70" s="2">
-        <f t="shared" si="2"/>
-        <v>1720</v>
-      </c>
-      <c r="L70" s="2">
-        <f t="shared" si="3"/>
-        <v>890</v>
-      </c>
-      <c r="M70" s="2">
-        <f t="shared" si="4"/>
-        <v>339</v>
-      </c>
-      <c r="N70" s="2">
-        <f t="shared" si="5"/>
-        <v>940</v>
-      </c>
-      <c r="O70" s="6">
-        <f t="shared" si="8"/>
-        <v>23</v>
-      </c>
-      <c r="P70" s="2">
-        <f t="shared" si="6"/>
-        <v>136</v>
-      </c>
-      <c r="Q70" s="2">
-        <f t="shared" si="7"/>
-        <v>137</v>
-      </c>
-      <c r="R70" s="1">
-        <v>0</v>
-      </c>
       <c r="S70" s="1">
         <v>0</v>
       </c>
-      <c r="T70" s="4">
+      <c r="T70" s="1">
         <v>0</v>
       </c>
       <c r="U70" s="4">
         <v>0</v>
       </c>
-      <c r="V70" s="1">
-        <f t="shared" ref="V70:V77" si="9">C70*10</f>
+      <c r="V70" s="4">
+        <v>0</v>
+      </c>
+      <c r="W70" s="1">
+        <f t="shared" ref="W70:W77" si="10">C70*10</f>
         <v>1370</v>
       </c>
-      <c r="W70" s="1">
-        <f t="shared" ref="W70:W77" si="10">D70*10</f>
+      <c r="X70" s="1">
+        <f t="shared" ref="X70:X77" si="11">D70*10</f>
         <v>1370</v>
       </c>
     </row>
-    <row r="71" s="3" customFormat="1" customHeight="1" spans="1:23">
+    <row r="71" s="3" customFormat="1" customHeight="1" spans="1:24">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="1">
@@ -15099,64 +15358,68 @@
         <v>66</v>
       </c>
       <c r="H71" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="I71" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="J71" s="6">
+        <f t="shared" ref="J71:J77" si="12">I71/I70</f>
+        <v>1.21935483870968</v>
+      </c>
+      <c r="K71" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="I71" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="J71" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="K71" s="2">
-        <f t="shared" ref="K71:K77" si="11">K70+20</f>
+      <c r="L71" s="2">
+        <f t="shared" ref="L71:L77" si="13">L70+20</f>
         <v>1740</v>
       </c>
-      <c r="L71" s="2">
-        <f t="shared" ref="L71:L77" si="12">L70+10</f>
+      <c r="M71" s="2">
+        <f t="shared" ref="M71:M77" si="14">M70+10</f>
         <v>900</v>
       </c>
-      <c r="M71" s="2">
-        <f t="shared" ref="M71:M77" si="13">M70+3</f>
+      <c r="N71" s="2">
+        <f t="shared" ref="N71:N77" si="15">N70+3</f>
         <v>342</v>
       </c>
-      <c r="N71" s="2">
-        <f t="shared" ref="N71:N77" si="14">N70+10</f>
+      <c r="O71" s="2">
+        <f t="shared" ref="O71:O77" si="16">O70+10</f>
         <v>950</v>
       </c>
-      <c r="O71" s="6">
-        <f t="shared" si="8"/>
+      <c r="P71" s="6">
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="P71" s="2">
-        <f t="shared" ref="P71:P77" si="15">P70+1</f>
+      <c r="Q71" s="2">
+        <f t="shared" ref="Q71:Q77" si="17">Q70+1</f>
         <v>137</v>
       </c>
-      <c r="Q71" s="2">
-        <f t="shared" ref="Q71:Q77" si="16">Q70+1</f>
+      <c r="R71" s="2">
+        <f t="shared" ref="R71:R77" si="18">R70+1</f>
         <v>138</v>
       </c>
-      <c r="R71" s="5">
-        <v>0</v>
-      </c>
       <c r="S71" s="5">
         <v>0</v>
       </c>
-      <c r="T71" s="3">
+      <c r="T71" s="5">
         <v>0</v>
       </c>
       <c r="U71" s="3">
         <v>0</v>
       </c>
-      <c r="V71" s="1">
-        <f t="shared" si="9"/>
-        <v>1380</v>
+      <c r="V71" s="3">
+        <v>0</v>
       </c>
       <c r="W71" s="1">
         <f t="shared" si="10"/>
         <v>1380</v>
       </c>
-    </row>
-    <row r="72" s="2" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X71" s="1">
+        <f t="shared" si="11"/>
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C72" s="1">
         <v>139</v>
       </c>
@@ -15173,64 +15436,68 @@
         <v>67</v>
       </c>
       <c r="H72" s="14" t="s">
-        <v>252</v>
+        <v>306</v>
       </c>
       <c r="I72" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="J72" s="6">
+        <f t="shared" si="12"/>
+        <v>1.21693121693122</v>
+      </c>
+      <c r="K72" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="J72" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="K72" s="2">
-        <f t="shared" si="11"/>
+      <c r="L72" s="2">
+        <f t="shared" si="13"/>
         <v>1760</v>
       </c>
-      <c r="L72" s="2">
-        <f t="shared" si="12"/>
+      <c r="M72" s="2">
+        <f t="shared" si="14"/>
         <v>910</v>
       </c>
-      <c r="M72" s="2">
-        <f t="shared" si="13"/>
+      <c r="N72" s="2">
+        <f t="shared" si="15"/>
         <v>345</v>
       </c>
-      <c r="N72" s="2">
-        <f t="shared" si="14"/>
+      <c r="O72" s="2">
+        <f t="shared" si="16"/>
         <v>960</v>
       </c>
-      <c r="O72" s="6">
-        <f t="shared" si="8"/>
+      <c r="P72" s="6">
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="P72" s="2">
-        <f t="shared" si="15"/>
+      <c r="Q72" s="2">
+        <f t="shared" si="17"/>
         <v>138</v>
       </c>
-      <c r="Q72" s="2">
-        <f t="shared" si="16"/>
+      <c r="R72" s="2">
+        <f t="shared" si="18"/>
         <v>139</v>
       </c>
-      <c r="R72" s="1">
-        <v>0</v>
-      </c>
       <c r="S72" s="1">
         <v>0</v>
       </c>
-      <c r="T72" s="4">
+      <c r="T72" s="1">
         <v>0</v>
       </c>
       <c r="U72" s="4">
         <v>0</v>
       </c>
-      <c r="V72" s="1">
-        <f t="shared" si="9"/>
-        <v>1390</v>
+      <c r="V72" s="4">
+        <v>0</v>
       </c>
       <c r="W72" s="1">
         <f t="shared" si="10"/>
         <v>1390</v>
       </c>
-    </row>
-    <row r="73" s="2" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X72" s="1">
+        <f t="shared" si="11"/>
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C73" s="1">
         <v>140</v>
       </c>
@@ -15247,64 +15514,68 @@
         <v>68</v>
       </c>
       <c r="H73" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="I73" s="13" t="s">
         <v>310</v>
       </c>
-      <c r="I73" s="13" t="s">
+      <c r="J73" s="6">
+        <f t="shared" si="12"/>
+        <v>1.22173913043478</v>
+      </c>
+      <c r="K73" s="13" t="s">
         <v>311</v>
       </c>
-      <c r="J73" s="13" t="s">
-        <v>312</v>
-      </c>
-      <c r="K73" s="2">
-        <f t="shared" si="11"/>
+      <c r="L73" s="2">
+        <f t="shared" si="13"/>
         <v>1780</v>
       </c>
-      <c r="L73" s="2">
-        <f t="shared" si="12"/>
+      <c r="M73" s="2">
+        <f t="shared" si="14"/>
         <v>920</v>
       </c>
-      <c r="M73" s="2">
-        <f t="shared" si="13"/>
+      <c r="N73" s="2">
+        <f t="shared" si="15"/>
         <v>348</v>
       </c>
-      <c r="N73" s="2">
-        <f t="shared" si="14"/>
+      <c r="O73" s="2">
+        <f t="shared" si="16"/>
         <v>970</v>
       </c>
-      <c r="O73" s="6">
-        <f t="shared" si="8"/>
+      <c r="P73" s="6">
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="P73" s="2">
-        <f t="shared" si="15"/>
+      <c r="Q73" s="2">
+        <f t="shared" si="17"/>
         <v>139</v>
       </c>
-      <c r="Q73" s="2">
-        <f t="shared" si="16"/>
+      <c r="R73" s="2">
+        <f t="shared" si="18"/>
         <v>140</v>
       </c>
-      <c r="R73" s="1">
-        <v>0</v>
-      </c>
       <c r="S73" s="1">
         <v>0</v>
       </c>
-      <c r="T73" s="4">
+      <c r="T73" s="1">
         <v>0</v>
       </c>
       <c r="U73" s="4">
         <v>0</v>
       </c>
-      <c r="V73" s="1">
-        <f t="shared" si="9"/>
-        <v>1400</v>
+      <c r="V73" s="4">
+        <v>0</v>
       </c>
       <c r="W73" s="1">
         <f t="shared" si="10"/>
         <v>1400</v>
       </c>
-    </row>
-    <row r="74" s="2" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X73" s="1">
+        <f t="shared" si="11"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C74" s="1">
         <v>141</v>
       </c>
@@ -15321,64 +15592,68 @@
         <v>69</v>
       </c>
       <c r="H74" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I74" s="13" t="s">
         <v>313</v>
       </c>
-      <c r="I74" s="13" t="s">
+      <c r="J74" s="6">
+        <f t="shared" si="12"/>
+        <v>1.22064056939502</v>
+      </c>
+      <c r="K74" s="13" t="s">
         <v>314</v>
       </c>
-      <c r="J74" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="K74" s="2">
-        <f t="shared" si="11"/>
+      <c r="L74" s="2">
+        <f t="shared" si="13"/>
         <v>1800</v>
       </c>
-      <c r="L74" s="2">
-        <f t="shared" si="12"/>
+      <c r="M74" s="2">
+        <f t="shared" si="14"/>
         <v>930</v>
       </c>
-      <c r="M74" s="2">
-        <f t="shared" si="13"/>
+      <c r="N74" s="2">
+        <f t="shared" si="15"/>
         <v>351</v>
       </c>
-      <c r="N74" s="2">
-        <f t="shared" si="14"/>
+      <c r="O74" s="2">
+        <f t="shared" si="16"/>
         <v>980</v>
       </c>
-      <c r="O74" s="6">
-        <f t="shared" si="8"/>
+      <c r="P74" s="6">
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="P74" s="2">
-        <f t="shared" si="15"/>
+      <c r="Q74" s="2">
+        <f t="shared" si="17"/>
         <v>140</v>
       </c>
-      <c r="Q74" s="2">
-        <f t="shared" si="16"/>
+      <c r="R74" s="2">
+        <f t="shared" si="18"/>
         <v>141</v>
       </c>
-      <c r="R74" s="1">
-        <v>0</v>
-      </c>
       <c r="S74" s="1">
         <v>0</v>
       </c>
-      <c r="T74" s="4">
+      <c r="T74" s="1">
         <v>0</v>
       </c>
       <c r="U74" s="4">
         <v>0</v>
       </c>
-      <c r="V74" s="1">
-        <f t="shared" si="9"/>
-        <v>1410</v>
+      <c r="V74" s="4">
+        <v>0</v>
       </c>
       <c r="W74" s="1">
         <f t="shared" si="10"/>
         <v>1410</v>
       </c>
-    </row>
-    <row r="75" s="2" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X74" s="1">
+        <f t="shared" si="11"/>
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C75" s="1">
         <v>142</v>
       </c>
@@ -15395,64 +15670,68 @@
         <v>70</v>
       </c>
       <c r="H75" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="I75" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="I75" s="13" t="s">
+      <c r="J75" s="6">
+        <f t="shared" si="12"/>
+        <v>1.21865889212828</v>
+      </c>
+      <c r="K75" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="J75" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="K75" s="2">
-        <f t="shared" si="11"/>
+      <c r="L75" s="2">
+        <f t="shared" si="13"/>
         <v>1820</v>
       </c>
-      <c r="L75" s="2">
-        <f t="shared" si="12"/>
+      <c r="M75" s="2">
+        <f t="shared" si="14"/>
         <v>940</v>
       </c>
-      <c r="M75" s="2">
-        <f t="shared" si="13"/>
+      <c r="N75" s="2">
+        <f t="shared" si="15"/>
         <v>354</v>
       </c>
-      <c r="N75" s="2">
-        <f t="shared" si="14"/>
+      <c r="O75" s="2">
+        <f t="shared" si="16"/>
         <v>990</v>
       </c>
-      <c r="O75" s="6">
-        <f t="shared" si="8"/>
+      <c r="P75" s="6">
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="P75" s="2">
-        <f t="shared" si="15"/>
+      <c r="Q75" s="2">
+        <f t="shared" si="17"/>
         <v>141</v>
       </c>
-      <c r="Q75" s="2">
-        <f t="shared" si="16"/>
+      <c r="R75" s="2">
+        <f t="shared" si="18"/>
         <v>142</v>
       </c>
-      <c r="R75" s="1">
-        <v>0</v>
-      </c>
       <c r="S75" s="1">
         <v>0</v>
       </c>
-      <c r="T75" s="4">
+      <c r="T75" s="1">
         <v>0</v>
       </c>
       <c r="U75" s="4">
         <v>0</v>
       </c>
-      <c r="V75" s="1">
-        <f t="shared" si="9"/>
-        <v>1420</v>
+      <c r="V75" s="4">
+        <v>0</v>
       </c>
       <c r="W75" s="1">
         <f t="shared" si="10"/>
         <v>1420</v>
       </c>
-    </row>
-    <row r="76" s="2" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X75" s="1">
+        <f t="shared" si="11"/>
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C76" s="1">
         <v>143</v>
       </c>
@@ -15469,64 +15748,68 @@
         <v>71</v>
       </c>
       <c r="H76" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="I76" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="I76" s="13" t="s">
+      <c r="J76" s="6">
+        <f t="shared" si="12"/>
+        <v>1.2177033492823</v>
+      </c>
+      <c r="K76" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="J76" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="K76" s="2">
-        <f t="shared" si="11"/>
+      <c r="L76" s="2">
+        <f t="shared" si="13"/>
         <v>1840</v>
       </c>
-      <c r="L76" s="2">
-        <f t="shared" si="12"/>
+      <c r="M76" s="2">
+        <f t="shared" si="14"/>
         <v>950</v>
       </c>
-      <c r="M76" s="2">
-        <f t="shared" si="13"/>
+      <c r="N76" s="2">
+        <f t="shared" si="15"/>
         <v>357</v>
       </c>
-      <c r="N76" s="2">
-        <f t="shared" si="14"/>
+      <c r="O76" s="2">
+        <f t="shared" si="16"/>
         <v>1000</v>
       </c>
-      <c r="O76" s="6">
-        <f>O70+1</f>
+      <c r="P76" s="6">
+        <f>P70+1</f>
         <v>24</v>
       </c>
-      <c r="P76" s="2">
-        <f t="shared" si="15"/>
+      <c r="Q76" s="2">
+        <f t="shared" si="17"/>
         <v>142</v>
       </c>
-      <c r="Q76" s="2">
-        <f t="shared" si="16"/>
+      <c r="R76" s="2">
+        <f t="shared" si="18"/>
         <v>143</v>
       </c>
-      <c r="R76" s="1">
-        <v>0</v>
-      </c>
       <c r="S76" s="1">
         <v>0</v>
       </c>
-      <c r="T76" s="4">
+      <c r="T76" s="1">
         <v>0</v>
       </c>
       <c r="U76" s="4">
         <v>0</v>
       </c>
-      <c r="V76" s="1">
-        <f t="shared" si="9"/>
-        <v>1430</v>
+      <c r="V76" s="4">
+        <v>0</v>
       </c>
       <c r="W76" s="1">
         <f t="shared" si="10"/>
         <v>1430</v>
       </c>
-    </row>
-    <row r="77" s="2" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X76" s="1">
+        <f t="shared" si="11"/>
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="77" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C77" s="1">
         <v>144</v>
       </c>
@@ -15543,78 +15826,82 @@
         <v>72</v>
       </c>
       <c r="H77" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="I77" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="I77" s="13" t="s">
+      <c r="J77" s="6">
+        <f t="shared" si="12"/>
+        <v>1.21807465618861</v>
+      </c>
+      <c r="K77" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="J77" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="K77" s="2">
-        <f t="shared" si="11"/>
+      <c r="L77" s="2">
+        <f t="shared" si="13"/>
         <v>1860</v>
       </c>
-      <c r="L77" s="2">
-        <f t="shared" si="12"/>
+      <c r="M77" s="2">
+        <f t="shared" si="14"/>
         <v>960</v>
       </c>
-      <c r="M77" s="2">
-        <f t="shared" si="13"/>
+      <c r="N77" s="2">
+        <f t="shared" si="15"/>
         <v>360</v>
       </c>
-      <c r="N77" s="2">
-        <f t="shared" si="14"/>
+      <c r="O77" s="2">
+        <f t="shared" si="16"/>
         <v>1010</v>
       </c>
-      <c r="O77" s="6">
-        <f>O71+1</f>
+      <c r="P77" s="6">
+        <f>P71+1</f>
         <v>24</v>
       </c>
-      <c r="P77" s="2">
-        <f t="shared" si="15"/>
+      <c r="Q77" s="2">
+        <f t="shared" si="17"/>
         <v>143</v>
       </c>
-      <c r="Q77" s="2">
-        <f t="shared" si="16"/>
+      <c r="R77" s="2">
+        <f t="shared" si="18"/>
         <v>144</v>
       </c>
-      <c r="R77" s="1">
-        <v>0</v>
-      </c>
       <c r="S77" s="1">
         <v>0</v>
       </c>
-      <c r="T77" s="4">
+      <c r="T77" s="1">
         <v>0</v>
       </c>
       <c r="U77" s="4">
         <v>0</v>
       </c>
-      <c r="V77" s="1">
-        <f t="shared" si="9"/>
-        <v>1440</v>
+      <c r="V77" s="4">
+        <v>0</v>
       </c>
       <c r="W77" s="1">
         <f t="shared" si="10"/>
         <v>1440</v>
       </c>
-    </row>
-    <row r="78" s="2" customFormat="1" customHeight="1" spans="1:23">
+      <c r="X77" s="1">
+        <f t="shared" si="11"/>
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="78" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="6"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" s="2" customFormat="1" customHeight="1" spans="1:23">
+    <row r="79" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="6"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" s="2" customFormat="1" customHeight="1" spans="1:23">
+    <row r="80" s="2" customFormat="1" customHeight="1" spans="1:24">
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -15784,7 +16071,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="O3:O5 C3:N5 P3:U5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3:J5 C3:I5 K3:V5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/MonsterConfig.xlsx
+++ b/Excel/MonsterConfig.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="325">
   <si>
     <t>#</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>540E+9</t>
+  </si>
+  <si>
+    <t>MulDamageResit</t>
   </si>
   <si>
     <t>249E+6</t>
@@ -10002,7 +10005,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X103"/>
+  <dimension ref="A1:Y103"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -10019,18 +10022,18 @@
     <col min="13" max="13" width="10.3333333333333" style="2" customWidth="1"/>
     <col min="14" max="14" width="9.91666666666667" style="2" customWidth="1"/>
     <col min="15" max="15" width="8.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="12.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="10.75" style="2" customWidth="1"/>
-    <col min="18" max="18" width="11.3333333333333" style="2" customWidth="1"/>
-    <col min="19" max="20" width="8.75" style="2" customWidth="1"/>
-    <col min="21" max="21" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="22" max="22" width="8.33333333333333" style="2" customWidth="1"/>
-    <col min="23" max="23" width="9.91666666666667" style="2" customWidth="1"/>
-    <col min="24" max="24" width="10.3333333333333" style="2" customWidth="1"/>
-    <col min="25" max="16384" width="9" style="2"/>
+    <col min="16" max="17" width="12.75" style="2" customWidth="1"/>
+    <col min="18" max="18" width="10.75" style="2" customWidth="1"/>
+    <col min="19" max="19" width="11.3333333333333" style="2" customWidth="1"/>
+    <col min="20" max="21" width="8.75" style="2" customWidth="1"/>
+    <col min="22" max="22" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="23" max="23" width="8.33333333333333" style="2" customWidth="1"/>
+    <col min="24" max="24" width="9.91666666666667" style="2" customWidth="1"/>
+    <col min="25" max="25" width="10.3333333333333" style="2" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:24">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="F1" s="6"/>
@@ -10051,8 +10054,9 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
-    </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="Y1" s="2"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="F2" s="6"/>
@@ -10073,8 +10077,9 @@
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
       <c r="X2" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:24">
+      <c r="Y2" s="2"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="7" t="s">
@@ -10118,31 +10123,34 @@
         <v>13</v>
       </c>
       <c r="Q3" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="R3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S3" s="7" t="s">
+      <c r="T3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T3" s="7" t="s">
+      <c r="U3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="7" t="s">
+      <c r="V3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="7" t="s">
+      <c r="W3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="W3" s="7" t="s">
+      <c r="X3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="7" t="s">
+      <c r="Y3" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:24">
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="7" t="s">
@@ -10186,31 +10194,34 @@
         <v>13</v>
       </c>
       <c r="Q4" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="R4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="S4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="T4" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="U4" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="U4" s="7" t="s">
+      <c r="V4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="V4" s="7" t="s">
+      <c r="W4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="W4" s="7" t="s">
+      <c r="X4" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="X4" s="7" t="s">
+      <c r="Y4" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:24">
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="7" t="s">
@@ -10272,13 +10283,16 @@
         <v>32</v>
       </c>
       <c r="W5" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="X5" s="7" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="11.5" spans="1:24">
+      <c r="Y5" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="11.5" spans="1:25">
       <c r="C6" s="1">
         <v>73</v>
       </c>
@@ -10295,10 +10309,10 @@
         <v>1</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="13" t="s">
@@ -10319,34 +10333,35 @@
       <c r="P6" s="1">
         <v>13</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="Q6" s="6"/>
+      <c r="R6" s="2">
         <v>72</v>
       </c>
-      <c r="R6" s="2">
+      <c r="S6" s="2">
         <v>73</v>
       </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
-      <c r="U6" s="4">
+      <c r="U6" s="1">
         <v>0</v>
       </c>
       <c r="V6" s="4">
         <v>0</v>
       </c>
-      <c r="W6" s="1">
-        <f t="shared" ref="W6:W69" si="0">C6*10</f>
+      <c r="W6" s="4">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" ref="X6:X69" si="0">C6*10</f>
         <v>730</v>
       </c>
-      <c r="X6" s="1">
-        <f t="shared" ref="X6:X69" si="1">D6*10</f>
+      <c r="Y6" s="1">
+        <f t="shared" ref="Y6:Y69" si="1">D6*10</f>
         <v>730</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C7" s="1">
         <v>74</v>
       </c>
@@ -10363,17 +10378,17 @@
         <v>2</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J7" s="6">
         <f t="shared" ref="J7:J70" si="2">I7/I6</f>
         <v>1.19838056680162</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L7" s="2">
         <f t="shared" ref="L7:L70" si="3">L6+20</f>
@@ -10394,36 +10409,37 @@
       <c r="P7" s="1">
         <v>13</v>
       </c>
-      <c r="Q7" s="2">
-        <f t="shared" ref="Q7:Q70" si="7">Q6+1</f>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="2">
+        <f t="shared" ref="R7:R70" si="7">R6+1</f>
         <v>73</v>
       </c>
-      <c r="R7" s="2">
-        <f t="shared" ref="R7:R70" si="8">R6+1</f>
+      <c r="S7" s="2">
+        <f t="shared" ref="S7:S70" si="8">S6+1</f>
         <v>74</v>
       </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
       <c r="T7" s="1">
         <v>0</v>
       </c>
-      <c r="U7" s="4">
+      <c r="U7" s="1">
         <v>0</v>
       </c>
       <c r="V7" s="4">
         <v>0</v>
       </c>
-      <c r="W7" s="1">
+      <c r="W7" s="4">
+        <v>0</v>
+      </c>
+      <c r="X7" s="1">
         <f t="shared" si="0"/>
         <v>740</v>
       </c>
-      <c r="X7" s="1">
+      <c r="Y7" s="1">
         <f t="shared" si="1"/>
         <v>740</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C8" s="1">
         <v>75</v>
       </c>
@@ -10440,17 +10456,17 @@
         <v>3</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J8" s="6">
         <f t="shared" si="2"/>
         <v>1.19932432432432</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L8" s="2">
         <f t="shared" si="3"/>
@@ -10471,36 +10487,37 @@
       <c r="P8" s="1">
         <v>13</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="Q8" s="1"/>
+      <c r="R8" s="2">
         <f t="shared" si="7"/>
         <v>74</v>
       </c>
-      <c r="R8" s="2">
+      <c r="S8" s="2">
         <f t="shared" si="8"/>
         <v>75</v>
       </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
       <c r="T8" s="1">
         <v>0</v>
       </c>
-      <c r="U8" s="4">
+      <c r="U8" s="1">
         <v>0</v>
       </c>
       <c r="V8" s="4">
         <v>0</v>
       </c>
-      <c r="W8" s="1">
+      <c r="W8" s="4">
+        <v>0</v>
+      </c>
+      <c r="X8" s="1">
         <f t="shared" si="0"/>
         <v>750</v>
       </c>
-      <c r="X8" s="1">
+      <c r="Y8" s="1">
         <f t="shared" si="1"/>
         <v>750</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C9" s="1">
         <v>76</v>
       </c>
@@ -10517,17 +10534,17 @@
         <v>4</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J9" s="6">
         <f t="shared" si="2"/>
         <v>1.2</v>
       </c>
       <c r="K9" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L9" s="2">
         <f t="shared" si="3"/>
@@ -10548,36 +10565,37 @@
       <c r="P9" s="1">
         <v>13</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1"/>
+      <c r="R9" s="2">
         <f t="shared" si="7"/>
         <v>75</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="2">
         <f t="shared" si="8"/>
         <v>76</v>
       </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
       <c r="T9" s="1">
         <v>0</v>
       </c>
-      <c r="U9" s="4">
+      <c r="U9" s="1">
         <v>0</v>
       </c>
       <c r="V9" s="4">
         <v>0</v>
       </c>
-      <c r="W9" s="1">
+      <c r="W9" s="4">
+        <v>0</v>
+      </c>
+      <c r="X9" s="1">
         <f t="shared" si="0"/>
         <v>760</v>
       </c>
-      <c r="X9" s="1">
+      <c r="Y9" s="1">
         <f t="shared" si="1"/>
         <v>760</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C10" s="1">
         <v>77</v>
       </c>
@@ -10594,17 +10612,17 @@
         <v>5</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J10" s="6">
         <f t="shared" si="2"/>
         <v>1.19953051643192</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L10" s="2">
         <f t="shared" si="3"/>
@@ -10625,36 +10643,37 @@
       <c r="P10" s="1">
         <v>13</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q10" s="1"/>
+      <c r="R10" s="2">
         <f t="shared" si="7"/>
         <v>76</v>
       </c>
-      <c r="R10" s="2">
+      <c r="S10" s="2">
         <f t="shared" si="8"/>
         <v>77</v>
       </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
       <c r="T10" s="1">
         <v>0</v>
       </c>
-      <c r="U10" s="4">
+      <c r="U10" s="1">
         <v>0</v>
       </c>
       <c r="V10" s="4">
         <v>0</v>
       </c>
-      <c r="W10" s="1">
+      <c r="W10" s="4">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1">
         <f t="shared" si="0"/>
         <v>770</v>
       </c>
-      <c r="X10" s="1">
+      <c r="Y10" s="1">
         <f t="shared" si="1"/>
         <v>770</v>
       </c>
     </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="1:24">
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="C11" s="1">
         <v>78</v>
       </c>
@@ -10671,17 +10690,17 @@
         <v>6</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J11" s="6">
         <f t="shared" si="2"/>
         <v>1.19960861056751</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L11" s="2">
         <f t="shared" si="3"/>
@@ -10702,36 +10721,37 @@
       <c r="P11" s="1">
         <v>13</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q11" s="1"/>
+      <c r="R11" s="2">
         <f t="shared" si="7"/>
         <v>77</v>
       </c>
-      <c r="R11" s="3">
+      <c r="S11" s="3">
         <f t="shared" si="8"/>
         <v>78</v>
       </c>
-      <c r="S11" s="5">
-        <v>0</v>
-      </c>
       <c r="T11" s="5">
         <v>0</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U11" s="5">
         <v>0</v>
       </c>
       <c r="V11" s="3">
         <v>0</v>
       </c>
-      <c r="W11" s="1">
+      <c r="W11" s="3">
+        <v>0</v>
+      </c>
+      <c r="X11" s="1">
         <f t="shared" si="0"/>
         <v>780</v>
       </c>
-      <c r="X11" s="1">
+      <c r="Y11" s="1">
         <f t="shared" si="1"/>
         <v>780</v>
       </c>
     </row>
-    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C12" s="1">
         <v>79</v>
       </c>
@@ -10748,17 +10768,17 @@
         <v>7</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J12" s="6">
         <f t="shared" si="2"/>
         <v>1.20065252854812</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L12" s="2">
         <f t="shared" si="3"/>
@@ -10780,36 +10800,37 @@
         <f t="shared" ref="P12:P75" si="9">P6+1</f>
         <v>14</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="6"/>
+      <c r="R12" s="2">
         <f t="shared" si="7"/>
         <v>78</v>
       </c>
-      <c r="R12" s="4">
+      <c r="S12" s="4">
         <f t="shared" si="8"/>
         <v>79</v>
       </c>
-      <c r="S12" s="6">
-        <v>0</v>
-      </c>
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="4">
+      <c r="U12" s="6">
         <v>0</v>
       </c>
       <c r="V12" s="4">
         <v>0</v>
       </c>
-      <c r="W12" s="1">
+      <c r="W12" s="4">
+        <v>0</v>
+      </c>
+      <c r="X12" s="1">
         <f t="shared" si="0"/>
         <v>790</v>
       </c>
-      <c r="X12" s="1">
+      <c r="Y12" s="1">
         <f t="shared" si="1"/>
         <v>790</v>
       </c>
     </row>
-    <row r="13" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="13" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C13" s="1">
         <v>80</v>
       </c>
@@ -10826,17 +10847,17 @@
         <v>8</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J13" s="6">
         <f t="shared" si="2"/>
         <v>1.19972826086957</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L13" s="2">
         <f t="shared" si="3"/>
@@ -10858,36 +10879,37 @@
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="Q13" s="6"/>
+      <c r="R13" s="2">
         <f t="shared" si="7"/>
         <v>79</v>
       </c>
-      <c r="R13" s="4">
+      <c r="S13" s="4">
         <f t="shared" si="8"/>
         <v>80</v>
       </c>
-      <c r="S13" s="6">
-        <v>0</v>
-      </c>
       <c r="T13" s="6">
         <v>0</v>
       </c>
-      <c r="U13" s="4">
+      <c r="U13" s="6">
         <v>0</v>
       </c>
       <c r="V13" s="4">
         <v>0</v>
       </c>
-      <c r="W13" s="1">
+      <c r="W13" s="4">
+        <v>0</v>
+      </c>
+      <c r="X13" s="1">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="X13" s="1">
+      <c r="Y13" s="1">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
     </row>
-    <row r="14" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="14" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C14" s="1">
         <v>81</v>
       </c>
@@ -10904,17 +10926,17 @@
         <v>9</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J14" s="6">
         <f t="shared" si="2"/>
         <v>1.2004530011325</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L14" s="2">
         <f t="shared" si="3"/>
@@ -10936,36 +10958,37 @@
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q14" s="6"/>
+      <c r="R14" s="2">
         <f t="shared" si="7"/>
         <v>80</v>
       </c>
-      <c r="R14" s="4">
+      <c r="S14" s="4">
         <f t="shared" si="8"/>
         <v>81</v>
       </c>
-      <c r="S14" s="6">
-        <v>0</v>
-      </c>
       <c r="T14" s="6">
         <v>0</v>
       </c>
-      <c r="U14" s="4">
+      <c r="U14" s="6">
         <v>0</v>
       </c>
       <c r="V14" s="4">
         <v>0</v>
       </c>
-      <c r="W14" s="1">
+      <c r="W14" s="4">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1">
         <f t="shared" si="0"/>
         <v>810</v>
       </c>
-      <c r="X14" s="1">
+      <c r="Y14" s="1">
         <f t="shared" si="1"/>
         <v>810</v>
       </c>
     </row>
-    <row r="15" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="15" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C15" s="1">
         <v>82</v>
       </c>
@@ -10982,17 +11005,17 @@
         <v>10</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J15" s="6">
         <f t="shared" si="2"/>
         <v>1.19811320754717</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L15" s="2">
         <f t="shared" si="3"/>
@@ -11014,36 +11037,37 @@
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="Q15" s="6"/>
+      <c r="R15" s="2">
         <f t="shared" si="7"/>
         <v>81</v>
       </c>
-      <c r="R15" s="4">
+      <c r="S15" s="4">
         <f t="shared" si="8"/>
         <v>82</v>
       </c>
-      <c r="S15" s="6">
-        <v>0</v>
-      </c>
       <c r="T15" s="6">
         <v>0</v>
       </c>
-      <c r="U15" s="4">
+      <c r="U15" s="6">
         <v>0</v>
       </c>
       <c r="V15" s="4">
         <v>0</v>
       </c>
-      <c r="W15" s="1">
+      <c r="W15" s="4">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1">
         <f t="shared" si="0"/>
         <v>820</v>
       </c>
-      <c r="X15" s="1">
+      <c r="Y15" s="1">
         <f t="shared" si="1"/>
         <v>820</v>
       </c>
     </row>
-    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C16" s="1">
         <v>83</v>
       </c>
@@ -11060,17 +11084,17 @@
         <v>11</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J16" s="6">
         <f t="shared" si="2"/>
         <v>1.19685039370079</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L16" s="2">
         <f t="shared" si="3"/>
@@ -11092,36 +11116,37 @@
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="6"/>
+      <c r="R16" s="2">
         <f t="shared" si="7"/>
         <v>82</v>
       </c>
-      <c r="R16" s="4">
+      <c r="S16" s="4">
         <f t="shared" si="8"/>
         <v>83</v>
       </c>
-      <c r="S16" s="6">
-        <v>0</v>
-      </c>
       <c r="T16" s="6">
         <v>0</v>
       </c>
-      <c r="U16" s="4">
+      <c r="U16" s="6">
         <v>0</v>
       </c>
       <c r="V16" s="4">
         <v>0</v>
       </c>
-      <c r="W16" s="1">
+      <c r="W16" s="4">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1">
         <f t="shared" si="0"/>
         <v>830</v>
       </c>
-      <c r="X16" s="1">
+      <c r="Y16" s="1">
         <f t="shared" si="1"/>
         <v>830</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:24">
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="3:25">
       <c r="C17" s="1">
         <v>84</v>
       </c>
@@ -11138,17 +11163,17 @@
         <v>12</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J17" s="6">
         <f t="shared" si="2"/>
         <v>1.19736842105263</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L17" s="2">
         <f t="shared" si="3"/>
@@ -11170,36 +11195,37 @@
         <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="Q17" s="6"/>
+      <c r="R17" s="2">
         <f t="shared" si="7"/>
         <v>83</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <f t="shared" si="8"/>
         <v>84</v>
       </c>
-      <c r="S17" s="5">
-        <v>0</v>
-      </c>
       <c r="T17" s="5">
         <v>0</v>
       </c>
-      <c r="U17" s="3">
+      <c r="U17" s="5">
         <v>0</v>
       </c>
       <c r="V17" s="3">
         <v>0</v>
       </c>
-      <c r="W17" s="1">
+      <c r="W17" s="3">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1">
         <f t="shared" si="0"/>
         <v>840</v>
       </c>
-      <c r="X17" s="1">
+      <c r="Y17" s="1">
         <f t="shared" si="1"/>
         <v>840</v>
       </c>
     </row>
-    <row r="18" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="18" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C18" s="1">
         <v>85</v>
       </c>
@@ -11216,17 +11242,17 @@
         <v>13</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J18" s="6">
         <f t="shared" si="2"/>
         <v>1.1978021978022</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L18" s="2">
         <f t="shared" si="3"/>
@@ -11248,36 +11274,37 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="6"/>
+      <c r="R18" s="2">
         <f t="shared" si="7"/>
         <v>84</v>
       </c>
-      <c r="R18" s="4">
+      <c r="S18" s="4">
         <f t="shared" si="8"/>
         <v>85</v>
       </c>
-      <c r="S18" s="6">
-        <v>0</v>
-      </c>
       <c r="T18" s="6">
         <v>0</v>
       </c>
-      <c r="U18" s="4">
+      <c r="U18" s="6">
         <v>0</v>
       </c>
       <c r="V18" s="4">
         <v>0</v>
       </c>
-      <c r="W18" s="1">
+      <c r="W18" s="4">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1">
         <f t="shared" si="0"/>
         <v>850</v>
       </c>
-      <c r="X18" s="1">
+      <c r="Y18" s="1">
         <f t="shared" si="1"/>
         <v>850</v>
       </c>
     </row>
-    <row r="19" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="19" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C19" s="1">
         <v>86</v>
       </c>
@@ -11294,17 +11321,17 @@
         <v>14</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J19" s="6">
         <f t="shared" si="2"/>
         <v>1.19724770642202</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L19" s="2">
         <f t="shared" si="3"/>
@@ -11326,36 +11353,37 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="6"/>
+      <c r="R19" s="2">
         <f t="shared" si="7"/>
         <v>85</v>
       </c>
-      <c r="R19" s="4">
+      <c r="S19" s="4">
         <f t="shared" si="8"/>
         <v>86</v>
       </c>
-      <c r="S19" s="6">
-        <v>0</v>
-      </c>
       <c r="T19" s="6">
         <v>0</v>
       </c>
-      <c r="U19" s="4">
+      <c r="U19" s="6">
         <v>0</v>
       </c>
       <c r="V19" s="4">
         <v>0</v>
       </c>
-      <c r="W19" s="1">
+      <c r="W19" s="4">
+        <v>0</v>
+      </c>
+      <c r="X19" s="1">
         <f t="shared" si="0"/>
         <v>860</v>
       </c>
-      <c r="X19" s="1">
+      <c r="Y19" s="1">
         <f t="shared" si="1"/>
         <v>860</v>
       </c>
     </row>
-    <row r="20" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="20" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C20" s="1">
         <v>87</v>
       </c>
@@ -11372,17 +11400,17 @@
         <v>15</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J20" s="6">
         <f t="shared" si="2"/>
         <v>1.1992337164751</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L20" s="2">
         <f t="shared" si="3"/>
@@ -11404,36 +11432,37 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q20" s="6"/>
+      <c r="R20" s="2">
         <f t="shared" si="7"/>
         <v>86</v>
       </c>
-      <c r="R20" s="4">
+      <c r="S20" s="4">
         <f t="shared" si="8"/>
         <v>87</v>
       </c>
-      <c r="S20" s="6">
-        <v>0</v>
-      </c>
       <c r="T20" s="6">
         <v>0</v>
       </c>
-      <c r="U20" s="4">
+      <c r="U20" s="6">
         <v>0</v>
       </c>
       <c r="V20" s="4">
         <v>0</v>
       </c>
-      <c r="W20" s="1">
+      <c r="W20" s="4">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1">
         <f t="shared" si="0"/>
         <v>870</v>
       </c>
-      <c r="X20" s="1">
+      <c r="Y20" s="1">
         <f t="shared" si="1"/>
         <v>870</v>
       </c>
     </row>
-    <row r="21" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="21" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C21" s="1">
         <v>88</v>
       </c>
@@ -11450,17 +11479,17 @@
         <v>16</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J21" s="6">
         <f t="shared" si="2"/>
         <v>1.19808306709265</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L21" s="2">
         <f t="shared" si="3"/>
@@ -11482,36 +11511,37 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q21" s="6"/>
+      <c r="R21" s="2">
         <f t="shared" si="7"/>
         <v>87</v>
       </c>
-      <c r="R21" s="4">
+      <c r="S21" s="4">
         <f t="shared" si="8"/>
         <v>88</v>
       </c>
-      <c r="S21" s="6">
-        <v>0</v>
-      </c>
       <c r="T21" s="6">
         <v>0</v>
       </c>
-      <c r="U21" s="4">
+      <c r="U21" s="6">
         <v>0</v>
       </c>
       <c r="V21" s="4">
         <v>0</v>
       </c>
-      <c r="W21" s="1">
+      <c r="W21" s="4">
+        <v>0</v>
+      </c>
+      <c r="X21" s="1">
         <f t="shared" si="0"/>
         <v>880</v>
       </c>
-      <c r="X21" s="1">
+      <c r="Y21" s="1">
         <f t="shared" si="1"/>
         <v>880</v>
       </c>
     </row>
-    <row r="22" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="22" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C22" s="1">
         <v>89</v>
       </c>
@@ -11528,17 +11558,17 @@
         <v>17</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J22" s="6">
         <f t="shared" si="2"/>
         <v>1.2</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L22" s="2">
         <f t="shared" si="3"/>
@@ -11560,36 +11590,37 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="Q22" s="6"/>
+      <c r="R22" s="2">
         <f t="shared" si="7"/>
         <v>88</v>
       </c>
-      <c r="R22" s="4">
+      <c r="S22" s="4">
         <f t="shared" si="8"/>
         <v>89</v>
       </c>
-      <c r="S22" s="6">
-        <v>0</v>
-      </c>
       <c r="T22" s="6">
         <v>0</v>
       </c>
-      <c r="U22" s="4">
+      <c r="U22" s="6">
         <v>0</v>
       </c>
       <c r="V22" s="4">
         <v>0</v>
       </c>
-      <c r="W22" s="1">
+      <c r="W22" s="4">
+        <v>0</v>
+      </c>
+      <c r="X22" s="1">
         <f t="shared" si="0"/>
         <v>890</v>
       </c>
-      <c r="X22" s="1">
+      <c r="Y22" s="1">
         <f t="shared" si="1"/>
         <v>890</v>
       </c>
     </row>
-    <row r="23" s="3" customFormat="1" customHeight="1" spans="3:24">
+    <row r="23" s="3" customFormat="1" customHeight="1" spans="3:25">
       <c r="C23" s="1">
         <v>90</v>
       </c>
@@ -11606,17 +11637,17 @@
         <v>18</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J23" s="6">
         <f t="shared" si="2"/>
         <v>1.32</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L23" s="2">
         <f t="shared" si="3"/>
@@ -11638,36 +11669,37 @@
         <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="6"/>
+      <c r="R23" s="2">
         <f t="shared" si="7"/>
         <v>89</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <f t="shared" si="8"/>
         <v>90</v>
       </c>
-      <c r="S23" s="5">
-        <v>0</v>
-      </c>
       <c r="T23" s="5">
         <v>0</v>
       </c>
-      <c r="U23" s="3">
+      <c r="U23" s="5">
         <v>0</v>
       </c>
       <c r="V23" s="3">
         <v>0</v>
       </c>
-      <c r="W23" s="1">
+      <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1">
         <f t="shared" si="0"/>
         <v>900</v>
       </c>
-      <c r="X23" s="1">
+      <c r="Y23" s="1">
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
     </row>
-    <row r="24" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="24" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C24" s="1">
         <v>91</v>
       </c>
@@ -11684,17 +11716,17 @@
         <v>19</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J24" s="6">
         <f t="shared" si="2"/>
         <v>1.30808080808081</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L24" s="2">
         <f t="shared" si="3"/>
@@ -11716,36 +11748,37 @@
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="Q24" s="6"/>
+      <c r="R24" s="2">
         <f t="shared" si="7"/>
         <v>90</v>
       </c>
-      <c r="R24" s="4">
+      <c r="S24" s="4">
         <f t="shared" si="8"/>
         <v>91</v>
       </c>
-      <c r="S24" s="6">
-        <v>0</v>
-      </c>
       <c r="T24" s="6">
         <v>0</v>
       </c>
-      <c r="U24" s="4">
+      <c r="U24" s="6">
         <v>0</v>
       </c>
       <c r="V24" s="4">
         <v>0</v>
       </c>
-      <c r="W24" s="1">
+      <c r="W24" s="4">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1">
         <f t="shared" si="0"/>
         <v>910</v>
       </c>
-      <c r="X24" s="1">
+      <c r="Y24" s="1">
         <f t="shared" si="1"/>
         <v>910</v>
       </c>
     </row>
-    <row r="25" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="25" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C25" s="1">
         <v>92</v>
       </c>
@@ -11762,17 +11795,17 @@
         <v>20</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J25" s="6">
         <f t="shared" si="2"/>
         <v>1.2998712998713</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L25" s="2">
         <f t="shared" si="3"/>
@@ -11794,36 +11827,39 @@
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="Q25" s="6">
+        <v>10</v>
+      </c>
+      <c r="R25" s="2">
         <f t="shared" si="7"/>
         <v>91</v>
       </c>
-      <c r="R25" s="4">
+      <c r="S25" s="4">
         <f t="shared" si="8"/>
         <v>92</v>
       </c>
-      <c r="S25" s="6">
-        <v>0</v>
-      </c>
       <c r="T25" s="6">
         <v>0</v>
       </c>
-      <c r="U25" s="4">
+      <c r="U25" s="6">
         <v>0</v>
       </c>
       <c r="V25" s="4">
         <v>0</v>
       </c>
-      <c r="W25" s="1">
+      <c r="W25" s="4">
+        <v>0</v>
+      </c>
+      <c r="X25" s="1">
         <f t="shared" si="0"/>
         <v>920</v>
       </c>
-      <c r="X25" s="1">
+      <c r="Y25" s="1">
         <f t="shared" si="1"/>
         <v>920</v>
       </c>
     </row>
-    <row r="26" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="26" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C26" s="1">
         <v>93</v>
       </c>
@@ -11840,17 +11876,17 @@
         <v>21</v>
       </c>
       <c r="H26" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="6">
         <f t="shared" si="2"/>
         <v>1.28712871287129</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L26" s="2">
         <f t="shared" si="3"/>
@@ -11872,36 +11908,40 @@
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q26" s="6">
+        <f t="shared" ref="Q26:Q77" si="10">Q25+5</f>
+        <v>15</v>
+      </c>
+      <c r="R26" s="2">
         <f t="shared" si="7"/>
         <v>92</v>
       </c>
-      <c r="R26" s="4">
+      <c r="S26" s="4">
         <f t="shared" si="8"/>
         <v>93</v>
       </c>
-      <c r="S26" s="6">
-        <v>0</v>
-      </c>
       <c r="T26" s="6">
         <v>0</v>
       </c>
-      <c r="U26" s="4">
+      <c r="U26" s="6">
         <v>0</v>
       </c>
       <c r="V26" s="4">
         <v>0</v>
       </c>
-      <c r="W26" s="1">
+      <c r="W26" s="4">
+        <v>0</v>
+      </c>
+      <c r="X26" s="1">
         <f t="shared" si="0"/>
         <v>930</v>
       </c>
-      <c r="X26" s="1">
+      <c r="Y26" s="1">
         <f t="shared" si="1"/>
         <v>930</v>
       </c>
     </row>
-    <row r="27" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="27" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C27" s="1">
         <v>94</v>
       </c>
@@ -11918,17 +11958,17 @@
         <v>22</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J27" s="6">
         <f t="shared" si="2"/>
         <v>1.27692307692308</v>
       </c>
       <c r="K27" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L27" s="2">
         <f t="shared" si="3"/>
@@ -11950,36 +11990,40 @@
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="Q27" s="6">
+        <f t="shared" si="10"/>
+        <v>20</v>
+      </c>
+      <c r="R27" s="2">
         <f t="shared" si="7"/>
         <v>93</v>
       </c>
-      <c r="R27" s="4">
+      <c r="S27" s="4">
         <f t="shared" si="8"/>
         <v>94</v>
       </c>
-      <c r="S27" s="6">
-        <v>0</v>
-      </c>
       <c r="T27" s="6">
         <v>0</v>
       </c>
-      <c r="U27" s="4">
+      <c r="U27" s="6">
         <v>0</v>
       </c>
       <c r="V27" s="4">
         <v>0</v>
       </c>
-      <c r="W27" s="1">
+      <c r="W27" s="4">
+        <v>0</v>
+      </c>
+      <c r="X27" s="1">
         <f t="shared" si="0"/>
         <v>940</v>
       </c>
-      <c r="X27" s="1">
+      <c r="Y27" s="1">
         <f t="shared" si="1"/>
         <v>940</v>
       </c>
     </row>
-    <row r="28" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="28" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C28" s="1">
         <v>95</v>
       </c>
@@ -11996,17 +12040,17 @@
         <v>23</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J28" s="6">
         <f t="shared" si="2"/>
         <v>1.28313253012048</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L28" s="2">
         <f t="shared" si="3"/>
@@ -12028,36 +12072,40 @@
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="Q28" s="6">
+        <f t="shared" si="10"/>
+        <v>25</v>
+      </c>
+      <c r="R28" s="2">
         <f t="shared" si="7"/>
         <v>94</v>
       </c>
-      <c r="R28" s="4">
+      <c r="S28" s="4">
         <f t="shared" si="8"/>
         <v>95</v>
       </c>
-      <c r="S28" s="6">
-        <v>0</v>
-      </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="4">
+      <c r="U28" s="6">
         <v>0</v>
       </c>
       <c r="V28" s="4">
         <v>0</v>
       </c>
-      <c r="W28" s="1">
+      <c r="W28" s="4">
+        <v>0</v>
+      </c>
+      <c r="X28" s="1">
         <f t="shared" si="0"/>
         <v>950</v>
       </c>
-      <c r="X28" s="1">
+      <c r="Y28" s="1">
         <f t="shared" si="1"/>
         <v>950</v>
       </c>
     </row>
-    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:24">
+    <row r="29" s="3" customFormat="1" customHeight="1" spans="3:25">
       <c r="C29" s="1">
         <v>96</v>
       </c>
@@ -12074,17 +12122,17 @@
         <v>24</v>
       </c>
       <c r="H29" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J29" s="6">
         <f t="shared" si="2"/>
         <v>1.26760563380282</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L29" s="2">
         <f t="shared" si="3"/>
@@ -12106,36 +12154,40 @@
         <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="6">
+        <f t="shared" si="10"/>
+        <v>30</v>
+      </c>
+      <c r="R29" s="2">
         <f t="shared" si="7"/>
         <v>95</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <f t="shared" si="8"/>
         <v>96</v>
       </c>
-      <c r="S29" s="5">
-        <v>0</v>
-      </c>
       <c r="T29" s="5">
         <v>0</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="5">
         <v>0</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="1">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="1">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="X29" s="1">
+      <c r="Y29" s="1">
         <f t="shared" si="1"/>
         <v>960</v>
       </c>
     </row>
-    <row r="30" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="30" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C30" s="1">
         <v>97</v>
       </c>
@@ -12152,17 +12204,17 @@
         <v>25</v>
       </c>
       <c r="H30" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J30" s="6">
         <f t="shared" si="2"/>
         <v>1.27037037037037</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L30" s="2">
         <f t="shared" si="3"/>
@@ -12184,36 +12236,40 @@
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="6">
+        <f t="shared" si="10"/>
+        <v>35</v>
+      </c>
+      <c r="R30" s="2">
         <f t="shared" si="7"/>
         <v>96</v>
       </c>
-      <c r="R30" s="4">
+      <c r="S30" s="4">
         <f t="shared" si="8"/>
         <v>97</v>
       </c>
-      <c r="S30" s="6">
-        <v>0</v>
-      </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="4">
+      <c r="U30" s="6">
         <v>0</v>
       </c>
       <c r="V30" s="4">
         <v>0</v>
       </c>
-      <c r="W30" s="1">
+      <c r="W30" s="4">
+        <v>0</v>
+      </c>
+      <c r="X30" s="1">
         <f t="shared" si="0"/>
         <v>970</v>
       </c>
-      <c r="X30" s="1">
+      <c r="Y30" s="1">
         <f t="shared" si="1"/>
         <v>970</v>
       </c>
     </row>
-    <row r="31" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="31" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C31" s="1">
         <v>98</v>
       </c>
@@ -12230,17 +12286,17 @@
         <v>26</v>
       </c>
       <c r="H31" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J31" s="6">
         <f t="shared" si="2"/>
         <v>1.26822157434402</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L31" s="2">
         <f t="shared" si="3"/>
@@ -12262,36 +12318,40 @@
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="6">
+        <f t="shared" si="10"/>
+        <v>40</v>
+      </c>
+      <c r="R31" s="2">
         <f t="shared" si="7"/>
         <v>97</v>
       </c>
-      <c r="R31" s="4">
+      <c r="S31" s="4">
         <f t="shared" si="8"/>
         <v>98</v>
       </c>
-      <c r="S31" s="6">
-        <v>0</v>
-      </c>
       <c r="T31" s="6">
         <v>0</v>
       </c>
-      <c r="U31" s="4">
+      <c r="U31" s="6">
         <v>0</v>
       </c>
       <c r="V31" s="4">
         <v>0</v>
       </c>
-      <c r="W31" s="1">
+      <c r="W31" s="4">
+        <v>0</v>
+      </c>
+      <c r="X31" s="1">
         <f t="shared" si="0"/>
         <v>980</v>
       </c>
-      <c r="X31" s="1">
+      <c r="Y31" s="1">
         <f t="shared" si="1"/>
         <v>980</v>
       </c>
     </row>
-    <row r="32" s="4" customFormat="1" customHeight="1" spans="3:24">
+    <row r="32" s="4" customFormat="1" customHeight="1" spans="3:25">
       <c r="C32" s="1">
         <v>99</v>
       </c>
@@ -12308,17 +12368,17 @@
         <v>27</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J32" s="6">
         <f t="shared" si="2"/>
         <v>1.25977011494253</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L32" s="2">
         <f t="shared" si="3"/>
@@ -12340,36 +12400,40 @@
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="Q32" s="6">
+        <f t="shared" si="10"/>
+        <v>45</v>
+      </c>
+      <c r="R32" s="2">
         <f t="shared" si="7"/>
         <v>98</v>
       </c>
-      <c r="R32" s="4">
+      <c r="S32" s="4">
         <f t="shared" si="8"/>
         <v>99</v>
       </c>
-      <c r="S32" s="6">
-        <v>0</v>
-      </c>
       <c r="T32" s="6">
         <v>0</v>
       </c>
-      <c r="U32" s="4">
+      <c r="U32" s="6">
         <v>0</v>
       </c>
       <c r="V32" s="4">
         <v>0</v>
       </c>
-      <c r="W32" s="1">
+      <c r="W32" s="4">
+        <v>0</v>
+      </c>
+      <c r="X32" s="1">
         <f t="shared" si="0"/>
         <v>990</v>
       </c>
-      <c r="X32" s="1">
+      <c r="Y32" s="1">
         <f t="shared" si="1"/>
         <v>990</v>
       </c>
     </row>
-    <row r="33" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="33" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C33" s="1">
         <v>100</v>
       </c>
@@ -12386,17 +12450,17 @@
         <v>28</v>
       </c>
       <c r="H33" s="14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J33" s="6">
         <f t="shared" si="2"/>
         <v>1.26094890510949</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L33" s="2">
         <f t="shared" si="3"/>
@@ -12418,36 +12482,40 @@
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="6">
+        <f t="shared" si="10"/>
+        <v>50</v>
+      </c>
+      <c r="R33" s="2">
         <f t="shared" si="7"/>
         <v>99</v>
       </c>
-      <c r="R33" s="4">
+      <c r="S33" s="4">
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="S33" s="6">
-        <v>0</v>
-      </c>
       <c r="T33" s="6">
         <v>0</v>
       </c>
-      <c r="U33" s="4">
+      <c r="U33" s="6">
         <v>0</v>
       </c>
       <c r="V33" s="4">
         <v>0</v>
       </c>
-      <c r="W33" s="1">
+      <c r="W33" s="4">
+        <v>0</v>
+      </c>
+      <c r="X33" s="1">
         <f t="shared" si="0"/>
         <v>1000</v>
       </c>
-      <c r="X33" s="1">
+      <c r="Y33" s="1">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
     </row>
-    <row r="34" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="34" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C34" s="1">
         <v>101</v>
       </c>
@@ -12464,17 +12532,17 @@
         <v>29</v>
       </c>
       <c r="H34" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J34" s="6">
         <f t="shared" si="2"/>
         <v>1.25904486251809</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L34" s="2">
         <f t="shared" si="3"/>
@@ -12496,36 +12564,40 @@
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="Q34" s="6">
+        <f t="shared" si="10"/>
+        <v>55</v>
+      </c>
+      <c r="R34" s="2">
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="R34" s="4">
+      <c r="S34" s="4">
         <f t="shared" si="8"/>
         <v>101</v>
       </c>
-      <c r="S34" s="6">
-        <v>0</v>
-      </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
-      <c r="U34" s="4">
+      <c r="U34" s="6">
         <v>0</v>
       </c>
       <c r="V34" s="4">
         <v>0</v>
       </c>
-      <c r="W34" s="1">
+      <c r="W34" s="4">
+        <v>0</v>
+      </c>
+      <c r="X34" s="1">
         <f t="shared" si="0"/>
         <v>1010</v>
       </c>
-      <c r="X34" s="1">
+      <c r="Y34" s="1">
         <f t="shared" si="1"/>
         <v>1010</v>
       </c>
     </row>
-    <row r="35" s="3" customFormat="1" customHeight="1" spans="1:24">
+    <row r="35" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="C35" s="1">
         <v>102</v>
       </c>
@@ -12542,17 +12614,17 @@
         <v>30</v>
       </c>
       <c r="H35" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J35" s="6">
         <f t="shared" si="2"/>
         <v>1.25287356321839</v>
       </c>
       <c r="K35" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L35" s="2">
         <f t="shared" si="3"/>
@@ -12574,36 +12646,40 @@
         <f t="shared" si="9"/>
         <v>17</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="Q35" s="6">
+        <f t="shared" si="10"/>
+        <v>60</v>
+      </c>
+      <c r="R35" s="2">
         <f t="shared" si="7"/>
         <v>101</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <f t="shared" si="8"/>
         <v>102</v>
       </c>
-      <c r="S35" s="5">
-        <v>0</v>
-      </c>
       <c r="T35" s="5">
         <v>0</v>
       </c>
-      <c r="U35" s="3">
+      <c r="U35" s="5">
         <v>0</v>
       </c>
       <c r="V35" s="3">
         <v>0</v>
       </c>
-      <c r="W35" s="1">
+      <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="1">
         <f t="shared" si="0"/>
         <v>1020</v>
       </c>
-      <c r="X35" s="1">
+      <c r="Y35" s="1">
         <f t="shared" si="1"/>
         <v>1020</v>
       </c>
     </row>
-    <row r="36" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="36" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C36" s="1">
         <v>103</v>
       </c>
@@ -12620,17 +12696,17 @@
         <v>31</v>
       </c>
       <c r="H36" s="14" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J36" s="6">
         <f t="shared" si="2"/>
         <v>1.24770642201835</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L36" s="2">
         <f t="shared" si="3"/>
@@ -12652,36 +12728,40 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="Q36" s="6">
+        <f t="shared" si="10"/>
+        <v>65</v>
+      </c>
+      <c r="R36" s="2">
         <f t="shared" si="7"/>
         <v>102</v>
       </c>
-      <c r="R36" s="4">
+      <c r="S36" s="4">
         <f t="shared" si="8"/>
         <v>103</v>
       </c>
-      <c r="S36" s="6">
-        <v>0</v>
-      </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="4">
+      <c r="U36" s="6">
         <v>0</v>
       </c>
       <c r="V36" s="4">
         <v>0</v>
       </c>
-      <c r="W36" s="1">
+      <c r="W36" s="4">
+        <v>0</v>
+      </c>
+      <c r="X36" s="1">
         <f t="shared" si="0"/>
         <v>1030</v>
       </c>
-      <c r="X36" s="1">
+      <c r="Y36" s="1">
         <f t="shared" si="1"/>
         <v>1030</v>
       </c>
     </row>
-    <row r="37" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="37" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C37" s="1">
         <v>104</v>
       </c>
@@ -12698,17 +12778,17 @@
         <v>32</v>
       </c>
       <c r="H37" s="14" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J37" s="6">
         <f t="shared" si="2"/>
         <v>1.25</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L37" s="2">
         <f t="shared" si="3"/>
@@ -12730,36 +12810,40 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="6">
+        <f t="shared" si="10"/>
+        <v>70</v>
+      </c>
+      <c r="R37" s="2">
         <f t="shared" si="7"/>
         <v>103</v>
       </c>
-      <c r="R37" s="4">
+      <c r="S37" s="4">
         <f t="shared" si="8"/>
         <v>104</v>
       </c>
-      <c r="S37" s="6">
-        <v>0</v>
-      </c>
       <c r="T37" s="6">
         <v>0</v>
       </c>
-      <c r="U37" s="4">
+      <c r="U37" s="6">
         <v>0</v>
       </c>
       <c r="V37" s="4">
         <v>0</v>
       </c>
-      <c r="W37" s="1">
+      <c r="W37" s="4">
+        <v>0</v>
+      </c>
+      <c r="X37" s="1">
         <f t="shared" si="0"/>
         <v>1040</v>
       </c>
-      <c r="X37" s="1">
+      <c r="Y37" s="1">
         <f t="shared" si="1"/>
         <v>1040</v>
       </c>
     </row>
-    <row r="38" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="38" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C38" s="1">
         <v>105</v>
       </c>
@@ -12776,17 +12860,17 @@
         <v>33</v>
       </c>
       <c r="H38" s="14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J38" s="6">
         <f t="shared" si="2"/>
         <v>1.25294117647059</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L38" s="2">
         <f t="shared" si="3"/>
@@ -12808,36 +12892,40 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="Q38" s="6">
+        <f t="shared" si="10"/>
+        <v>75</v>
+      </c>
+      <c r="R38" s="2">
         <f t="shared" si="7"/>
         <v>104</v>
       </c>
-      <c r="R38" s="4">
+      <c r="S38" s="4">
         <f t="shared" si="8"/>
         <v>105</v>
       </c>
-      <c r="S38" s="6">
-        <v>0</v>
-      </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
-      <c r="U38" s="4">
+      <c r="U38" s="6">
         <v>0</v>
       </c>
       <c r="V38" s="4">
         <v>0</v>
       </c>
-      <c r="W38" s="1">
+      <c r="W38" s="4">
+        <v>0</v>
+      </c>
+      <c r="X38" s="1">
         <f t="shared" si="0"/>
         <v>1050</v>
       </c>
-      <c r="X38" s="1">
+      <c r="Y38" s="1">
         <f t="shared" si="1"/>
         <v>1050</v>
       </c>
     </row>
-    <row r="39" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="39" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C39" s="1">
         <v>106</v>
       </c>
@@ -12854,17 +12942,17 @@
         <v>34</v>
       </c>
       <c r="H39" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J39" s="6">
         <f t="shared" si="2"/>
         <v>1.24413145539906</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L39" s="2">
         <f t="shared" si="3"/>
@@ -12886,36 +12974,40 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="Q39" s="6">
+        <f t="shared" si="10"/>
+        <v>80</v>
+      </c>
+      <c r="R39" s="2">
         <f t="shared" si="7"/>
         <v>105</v>
       </c>
-      <c r="R39" s="4">
+      <c r="S39" s="4">
         <f t="shared" si="8"/>
         <v>106</v>
       </c>
-      <c r="S39" s="6">
-        <v>0</v>
-      </c>
       <c r="T39" s="6">
         <v>0</v>
       </c>
-      <c r="U39" s="4">
+      <c r="U39" s="6">
         <v>0</v>
       </c>
       <c r="V39" s="4">
         <v>0</v>
       </c>
-      <c r="W39" s="1">
+      <c r="W39" s="4">
+        <v>0</v>
+      </c>
+      <c r="X39" s="1">
         <f t="shared" si="0"/>
         <v>1060</v>
       </c>
-      <c r="X39" s="1">
+      <c r="Y39" s="1">
         <f t="shared" si="1"/>
         <v>1060</v>
       </c>
     </row>
-    <row r="40" s="4" customFormat="1" customHeight="1" spans="1:24">
+    <row r="40" s="4" customFormat="1" customHeight="1" spans="1:25">
       <c r="C40" s="1">
         <v>107</v>
       </c>
@@ -12932,17 +13024,17 @@
         <v>35</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J40" s="6">
         <f t="shared" si="2"/>
         <v>1.23396226415094</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L40" s="2">
         <f t="shared" si="3"/>
@@ -12964,36 +13056,40 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="Q40" s="6">
+        <f t="shared" si="10"/>
+        <v>85</v>
+      </c>
+      <c r="R40" s="2">
         <f t="shared" si="7"/>
         <v>106</v>
       </c>
-      <c r="R40" s="4">
+      <c r="S40" s="4">
         <f t="shared" si="8"/>
         <v>107</v>
       </c>
-      <c r="S40" s="6">
-        <v>0</v>
-      </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="4">
+      <c r="U40" s="6">
         <v>0</v>
       </c>
       <c r="V40" s="4">
         <v>0</v>
       </c>
-      <c r="W40" s="1">
+      <c r="W40" s="4">
+        <v>0</v>
+      </c>
+      <c r="X40" s="1">
         <f t="shared" si="0"/>
         <v>1070</v>
       </c>
-      <c r="X40" s="1">
+      <c r="Y40" s="1">
         <f t="shared" si="1"/>
         <v>1070</v>
       </c>
     </row>
-    <row r="41" s="5" customFormat="1" customHeight="1" spans="1:24">
+    <row r="41" s="5" customFormat="1" customHeight="1" spans="1:25">
       <c r="A41" s="3"/>
       <c r="C41" s="1">
         <v>108</v>
@@ -13011,17 +13107,17 @@
         <v>36</v>
       </c>
       <c r="H41" s="14" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J41" s="6">
         <f t="shared" si="2"/>
         <v>1.24159021406728</v>
       </c>
       <c r="K41" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L41" s="2">
         <f t="shared" si="3"/>
@@ -13043,36 +13139,40 @@
         <f t="shared" si="9"/>
         <v>18</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="6">
+        <f t="shared" si="10"/>
+        <v>90</v>
+      </c>
+      <c r="R41" s="2">
         <f t="shared" si="7"/>
         <v>107</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <f t="shared" si="8"/>
         <v>108</v>
       </c>
-      <c r="S41" s="5">
-        <v>0</v>
-      </c>
       <c r="T41" s="5">
         <v>0</v>
       </c>
-      <c r="U41" s="3">
+      <c r="U41" s="5">
         <v>0</v>
       </c>
       <c r="V41" s="3">
         <v>0</v>
       </c>
-      <c r="W41" s="1">
+      <c r="W41" s="3">
+        <v>0</v>
+      </c>
+      <c r="X41" s="1">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="X41" s="1">
+      <c r="Y41" s="1">
         <f t="shared" si="1"/>
         <v>1080</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:24">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A42" s="2"/>
       <c r="C42" s="1">
         <v>109</v>
@@ -13090,17 +13190,17 @@
         <v>37</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J42" s="6">
         <f t="shared" si="2"/>
         <v>1.24137931034483</v>
       </c>
       <c r="K42" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L42" s="2">
         <f t="shared" si="3"/>
@@ -13122,36 +13222,40 @@
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="Q42" s="6">
+        <f t="shared" si="10"/>
+        <v>95</v>
+      </c>
+      <c r="R42" s="2">
         <f t="shared" si="7"/>
         <v>108</v>
       </c>
-      <c r="R42" s="2">
+      <c r="S42" s="2">
         <f t="shared" si="8"/>
         <v>109</v>
       </c>
-      <c r="S42" s="1">
-        <v>0</v>
-      </c>
       <c r="T42" s="1">
         <v>0</v>
       </c>
-      <c r="U42" s="4">
+      <c r="U42" s="1">
         <v>0</v>
       </c>
       <c r="V42" s="4">
         <v>0</v>
       </c>
-      <c r="W42" s="1">
+      <c r="W42" s="4">
+        <v>0</v>
+      </c>
+      <c r="X42" s="1">
         <f t="shared" si="0"/>
         <v>1090</v>
       </c>
-      <c r="X42" s="1">
+      <c r="Y42" s="1">
         <f t="shared" si="1"/>
         <v>1090</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:24">
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A43" s="2"/>
       <c r="C43" s="1">
         <v>110</v>
@@ -13169,17 +13273,17 @@
         <v>38</v>
       </c>
       <c r="H43" s="14" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="2"/>
         <v>1.23611111111111</v>
       </c>
       <c r="K43" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="L43" s="2">
         <f t="shared" si="3"/>
@@ -13201,36 +13305,40 @@
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="Q43" s="6">
+        <f t="shared" si="10"/>
+        <v>100</v>
+      </c>
+      <c r="R43" s="2">
         <f t="shared" si="7"/>
         <v>109</v>
       </c>
-      <c r="R43" s="2">
+      <c r="S43" s="2">
         <f t="shared" si="8"/>
         <v>110</v>
       </c>
-      <c r="S43" s="1">
-        <v>0</v>
-      </c>
       <c r="T43" s="1">
         <v>0</v>
       </c>
-      <c r="U43" s="4">
+      <c r="U43" s="1">
         <v>0</v>
       </c>
       <c r="V43" s="4">
         <v>0</v>
       </c>
-      <c r="W43" s="1">
+      <c r="W43" s="4">
+        <v>0</v>
+      </c>
+      <c r="X43" s="1">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="X43" s="1">
+      <c r="Y43" s="1">
         <f t="shared" si="1"/>
         <v>1100</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:24">
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A44" s="2"/>
       <c r="C44" s="1">
         <v>111</v>
@@ -13248,17 +13356,17 @@
         <v>39</v>
       </c>
       <c r="H44" s="14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J44" s="6">
         <f t="shared" si="2"/>
         <v>1.23756019261637</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L44" s="2">
         <f t="shared" si="3"/>
@@ -13280,36 +13388,40 @@
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="6">
+        <f t="shared" si="10"/>
+        <v>105</v>
+      </c>
+      <c r="R44" s="2">
         <f t="shared" si="7"/>
         <v>110</v>
       </c>
-      <c r="R44" s="2">
+      <c r="S44" s="2">
         <f t="shared" si="8"/>
         <v>111</v>
       </c>
-      <c r="S44" s="1">
-        <v>0</v>
-      </c>
       <c r="T44" s="1">
         <v>0</v>
       </c>
-      <c r="U44" s="4">
+      <c r="U44" s="1">
         <v>0</v>
       </c>
       <c r="V44" s="4">
         <v>0</v>
       </c>
-      <c r="W44" s="1">
+      <c r="W44" s="4">
+        <v>0</v>
+      </c>
+      <c r="X44" s="1">
         <f t="shared" si="0"/>
         <v>1110</v>
       </c>
-      <c r="X44" s="1">
+      <c r="Y44" s="1">
         <f t="shared" si="1"/>
         <v>1110</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:24">
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A45" s="2"/>
       <c r="C45" s="1">
         <v>112</v>
@@ -13327,17 +13439,17 @@
         <v>40</v>
       </c>
       <c r="H45" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J45" s="6">
         <f t="shared" si="2"/>
         <v>1.23735408560311</v>
       </c>
       <c r="K45" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L45" s="2">
         <f t="shared" si="3"/>
@@ -13359,36 +13471,40 @@
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45" s="6">
+        <f t="shared" si="10"/>
+        <v>110</v>
+      </c>
+      <c r="R45" s="2">
         <f t="shared" si="7"/>
         <v>111</v>
       </c>
-      <c r="R45" s="2">
+      <c r="S45" s="2">
         <f t="shared" si="8"/>
         <v>112</v>
       </c>
-      <c r="S45" s="1">
-        <v>0</v>
-      </c>
       <c r="T45" s="1">
         <v>0</v>
       </c>
-      <c r="U45" s="4">
+      <c r="U45" s="1">
         <v>0</v>
       </c>
       <c r="V45" s="4">
         <v>0</v>
       </c>
-      <c r="W45" s="1">
+      <c r="W45" s="4">
+        <v>0</v>
+      </c>
+      <c r="X45" s="1">
         <f t="shared" si="0"/>
         <v>1120</v>
       </c>
-      <c r="X45" s="1">
+      <c r="Y45" s="1">
         <f t="shared" si="1"/>
         <v>1120</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:24">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A46" s="2"/>
       <c r="C46" s="1">
         <v>113</v>
@@ -13406,17 +13522,17 @@
         <v>41</v>
       </c>
       <c r="H46" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J46" s="6">
         <f t="shared" si="2"/>
         <v>1.23689727463312</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L46" s="2">
         <f t="shared" si="3"/>
@@ -13438,36 +13554,40 @@
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="6">
+        <f t="shared" si="10"/>
+        <v>115</v>
+      </c>
+      <c r="R46" s="2">
         <f t="shared" si="7"/>
         <v>112</v>
       </c>
-      <c r="R46" s="2">
+      <c r="S46" s="2">
         <f t="shared" si="8"/>
         <v>113</v>
       </c>
-      <c r="S46" s="1">
-        <v>0</v>
-      </c>
       <c r="T46" s="1">
         <v>0</v>
       </c>
-      <c r="U46" s="4">
+      <c r="U46" s="1">
         <v>0</v>
       </c>
       <c r="V46" s="4">
         <v>0</v>
       </c>
-      <c r="W46" s="1">
+      <c r="W46" s="4">
+        <v>0</v>
+      </c>
+      <c r="X46" s="1">
         <f t="shared" si="0"/>
         <v>1130</v>
       </c>
-      <c r="X46" s="1">
+      <c r="Y46" s="1">
         <f t="shared" si="1"/>
         <v>1130</v>
       </c>
     </row>
-    <row r="47" s="3" customFormat="1" customHeight="1" spans="1:24">
+    <row r="47" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="C47" s="1">
         <v>114</v>
       </c>
@@ -13484,17 +13604,17 @@
         <v>42</v>
       </c>
       <c r="H47" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J47" s="6">
         <f t="shared" si="2"/>
         <v>1.23728813559322</v>
       </c>
       <c r="K47" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L47" s="2">
         <f t="shared" si="3"/>
@@ -13516,36 +13636,40 @@
         <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="Q47" s="6">
+        <f t="shared" si="10"/>
+        <v>120</v>
+      </c>
+      <c r="R47" s="2">
         <f t="shared" si="7"/>
         <v>113</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <f t="shared" si="8"/>
         <v>114</v>
       </c>
-      <c r="S47" s="5">
-        <v>0</v>
-      </c>
       <c r="T47" s="5">
         <v>0</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="5">
         <v>0</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
       </c>
-      <c r="W47" s="1">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="1">
         <f t="shared" si="0"/>
         <v>1140</v>
       </c>
-      <c r="X47" s="1">
+      <c r="Y47" s="1">
         <f t="shared" si="1"/>
         <v>1140</v>
       </c>
     </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C48" s="1">
         <v>115</v>
       </c>
@@ -13562,17 +13686,17 @@
         <v>43</v>
       </c>
       <c r="H48" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J48" s="6">
         <f t="shared" si="2"/>
         <v>1.23287671232877</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="L48" s="2">
         <f t="shared" si="3"/>
@@ -13594,36 +13718,40 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="Q48" s="6">
+        <f t="shared" si="10"/>
+        <v>125</v>
+      </c>
+      <c r="R48" s="2">
         <f t="shared" si="7"/>
         <v>114</v>
       </c>
-      <c r="R48" s="2">
+      <c r="S48" s="2">
         <f t="shared" si="8"/>
         <v>115</v>
       </c>
-      <c r="S48" s="1">
-        <v>0</v>
-      </c>
       <c r="T48" s="1">
         <v>0</v>
       </c>
-      <c r="U48" s="4">
+      <c r="U48" s="1">
         <v>0</v>
       </c>
       <c r="V48" s="4">
         <v>0</v>
       </c>
-      <c r="W48" s="1">
+      <c r="W48" s="4">
+        <v>0</v>
+      </c>
+      <c r="X48" s="1">
         <f t="shared" si="0"/>
         <v>1150</v>
       </c>
-      <c r="X48" s="1">
+      <c r="Y48" s="1">
         <f t="shared" si="1"/>
         <v>1150</v>
       </c>
     </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C49" s="1">
         <v>116</v>
       </c>
@@ -13640,17 +13768,17 @@
         <v>44</v>
       </c>
       <c r="H49" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J49" s="6">
         <f t="shared" si="2"/>
         <v>1.23333333333333</v>
       </c>
       <c r="K49" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L49" s="2">
         <f t="shared" si="3"/>
@@ -13672,36 +13800,40 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="Q49" s="6">
+        <f t="shared" si="10"/>
+        <v>130</v>
+      </c>
+      <c r="R49" s="2">
         <f t="shared" si="7"/>
         <v>115</v>
       </c>
-      <c r="R49" s="2">
+      <c r="S49" s="2">
         <f t="shared" si="8"/>
         <v>116</v>
       </c>
-      <c r="S49" s="1">
-        <v>0</v>
-      </c>
       <c r="T49" s="1">
         <v>0</v>
       </c>
-      <c r="U49" s="4">
+      <c r="U49" s="1">
         <v>0</v>
       </c>
       <c r="V49" s="4">
         <v>0</v>
       </c>
-      <c r="W49" s="1">
+      <c r="W49" s="4">
+        <v>0</v>
+      </c>
+      <c r="X49" s="1">
         <f t="shared" si="0"/>
         <v>1160</v>
       </c>
-      <c r="X49" s="1">
+      <c r="Y49" s="1">
         <f t="shared" si="1"/>
         <v>1160</v>
       </c>
     </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C50" s="1">
         <v>117</v>
       </c>
@@ -13718,17 +13850,17 @@
         <v>45</v>
       </c>
       <c r="H50" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J50" s="6">
         <f t="shared" si="2"/>
         <v>1.22972972972973</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L50" s="2">
         <f t="shared" si="3"/>
@@ -13750,36 +13882,40 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="Q50" s="6">
+        <f t="shared" si="10"/>
+        <v>135</v>
+      </c>
+      <c r="R50" s="2">
         <f t="shared" si="7"/>
         <v>116</v>
       </c>
-      <c r="R50" s="2">
+      <c r="S50" s="2">
         <f t="shared" si="8"/>
         <v>117</v>
       </c>
-      <c r="S50" s="1">
-        <v>0</v>
-      </c>
       <c r="T50" s="1">
         <v>0</v>
       </c>
-      <c r="U50" s="4">
+      <c r="U50" s="1">
         <v>0</v>
       </c>
       <c r="V50" s="4">
         <v>0</v>
       </c>
-      <c r="W50" s="1">
+      <c r="W50" s="4">
+        <v>0</v>
+      </c>
+      <c r="X50" s="1">
         <f t="shared" si="0"/>
         <v>1170</v>
       </c>
-      <c r="X50" s="1">
+      <c r="Y50" s="1">
         <f t="shared" si="1"/>
         <v>1170</v>
       </c>
     </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C51" s="1">
         <v>118</v>
       </c>
@@ -13796,17 +13932,17 @@
         <v>46</v>
       </c>
       <c r="H51" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J51" s="6">
         <f t="shared" si="2"/>
         <v>1.23076923076923</v>
       </c>
       <c r="K51" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="L51" s="2">
         <f t="shared" si="3"/>
@@ -13828,36 +13964,40 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="Q51" s="6">
+        <f t="shared" si="10"/>
+        <v>140</v>
+      </c>
+      <c r="R51" s="2">
         <f t="shared" si="7"/>
         <v>117</v>
       </c>
-      <c r="R51" s="2">
+      <c r="S51" s="2">
         <f t="shared" si="8"/>
         <v>118</v>
       </c>
-      <c r="S51" s="1">
-        <v>0</v>
-      </c>
       <c r="T51" s="1">
         <v>0</v>
       </c>
-      <c r="U51" s="4">
+      <c r="U51" s="1">
         <v>0</v>
       </c>
       <c r="V51" s="4">
         <v>0</v>
       </c>
-      <c r="W51" s="1">
+      <c r="W51" s="4">
+        <v>0</v>
+      </c>
+      <c r="X51" s="1">
         <f t="shared" si="0"/>
         <v>1180</v>
       </c>
-      <c r="X51" s="1">
+      <c r="Y51" s="1">
         <f t="shared" si="1"/>
         <v>1180</v>
       </c>
     </row>
-    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C52" s="1">
         <v>119</v>
       </c>
@@ -13874,17 +14014,17 @@
         <v>47</v>
       </c>
       <c r="H52" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J52" s="6">
         <f t="shared" si="2"/>
         <v>1.22619047619048</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L52" s="2">
         <f t="shared" si="3"/>
@@ -13906,36 +14046,40 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="Q52" s="2">
+      <c r="Q52" s="6">
+        <f t="shared" si="10"/>
+        <v>145</v>
+      </c>
+      <c r="R52" s="2">
         <f t="shared" si="7"/>
         <v>118</v>
       </c>
-      <c r="R52" s="2">
+      <c r="S52" s="2">
         <f t="shared" si="8"/>
         <v>119</v>
       </c>
-      <c r="S52" s="1">
-        <v>0</v>
-      </c>
       <c r="T52" s="1">
         <v>0</v>
       </c>
-      <c r="U52" s="4">
+      <c r="U52" s="1">
         <v>0</v>
       </c>
       <c r="V52" s="4">
         <v>0</v>
       </c>
-      <c r="W52" s="1">
+      <c r="W52" s="4">
+        <v>0</v>
+      </c>
+      <c r="X52" s="1">
         <f t="shared" si="0"/>
         <v>1190</v>
       </c>
-      <c r="X52" s="1">
+      <c r="Y52" s="1">
         <f t="shared" si="1"/>
         <v>1190</v>
       </c>
     </row>
-    <row r="53" s="3" customFormat="1" customHeight="1" spans="3:24">
+    <row r="53" s="3" customFormat="1" customHeight="1" spans="3:25">
       <c r="C53" s="1">
         <v>120</v>
       </c>
@@ -13952,17 +14096,17 @@
         <v>48</v>
       </c>
       <c r="H53" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J53" s="6">
         <f t="shared" si="2"/>
         <v>1.22330097087379</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L53" s="2">
         <f t="shared" si="3"/>
@@ -13984,36 +14128,40 @@
         <f t="shared" si="9"/>
         <v>20</v>
       </c>
-      <c r="Q53" s="2">
+      <c r="Q53" s="6">
+        <f t="shared" si="10"/>
+        <v>150</v>
+      </c>
+      <c r="R53" s="2">
         <f t="shared" si="7"/>
         <v>119</v>
       </c>
-      <c r="R53" s="3">
+      <c r="S53" s="3">
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="S53" s="5">
-        <v>0</v>
-      </c>
       <c r="T53" s="5">
         <v>0</v>
       </c>
-      <c r="U53" s="3">
+      <c r="U53" s="5">
         <v>0</v>
       </c>
       <c r="V53" s="3">
         <v>0</v>
       </c>
-      <c r="W53" s="1">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="1">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="X53" s="1">
+      <c r="Y53" s="1">
         <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C54" s="1">
         <v>121</v>
       </c>
@@ -14030,17 +14178,17 @@
         <v>49</v>
       </c>
       <c r="H54" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J54" s="6">
         <f t="shared" si="2"/>
         <v>1.22420634920635</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L54" s="2">
         <f t="shared" si="3"/>
@@ -14062,36 +14210,40 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="Q54" s="2">
+      <c r="Q54" s="6">
+        <f t="shared" si="10"/>
+        <v>155</v>
+      </c>
+      <c r="R54" s="2">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
-      <c r="R54" s="2">
+      <c r="S54" s="2">
         <f t="shared" si="8"/>
         <v>121</v>
       </c>
-      <c r="S54" s="1">
-        <v>0</v>
-      </c>
       <c r="T54" s="1">
         <v>0</v>
       </c>
-      <c r="U54" s="4">
+      <c r="U54" s="1">
         <v>0</v>
       </c>
       <c r="V54" s="4">
         <v>0</v>
       </c>
-      <c r="W54" s="1">
+      <c r="W54" s="4">
+        <v>0</v>
+      </c>
+      <c r="X54" s="1">
         <f t="shared" si="0"/>
         <v>1210</v>
       </c>
-      <c r="X54" s="1">
+      <c r="Y54" s="1">
         <f t="shared" si="1"/>
         <v>1210</v>
       </c>
     </row>
-    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="55" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C55" s="1">
         <v>122</v>
       </c>
@@ -14108,17 +14260,17 @@
         <v>50</v>
       </c>
       <c r="H55" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J55" s="6">
         <f t="shared" si="2"/>
         <v>1.22690437601297</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L55" s="2">
         <f t="shared" si="3"/>
@@ -14140,36 +14292,40 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="Q55" s="2">
+      <c r="Q55" s="6">
+        <f t="shared" si="10"/>
+        <v>160</v>
+      </c>
+      <c r="R55" s="2">
         <f t="shared" si="7"/>
         <v>121</v>
       </c>
-      <c r="R55" s="2">
+      <c r="S55" s="2">
         <f t="shared" si="8"/>
         <v>122</v>
       </c>
-      <c r="S55" s="1">
-        <v>0</v>
-      </c>
       <c r="T55" s="1">
         <v>0</v>
       </c>
-      <c r="U55" s="4">
+      <c r="U55" s="1">
         <v>0</v>
       </c>
       <c r="V55" s="4">
         <v>0</v>
       </c>
-      <c r="W55" s="1">
+      <c r="W55" s="4">
+        <v>0</v>
+      </c>
+      <c r="X55" s="1">
         <f t="shared" si="0"/>
         <v>1220</v>
       </c>
-      <c r="X55" s="1">
+      <c r="Y55" s="1">
         <f t="shared" si="1"/>
         <v>1220</v>
       </c>
     </row>
-    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="56" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C56" s="1">
         <v>123</v>
       </c>
@@ -14186,17 +14342,17 @@
         <v>51</v>
       </c>
       <c r="H56" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J56" s="6">
         <f t="shared" si="2"/>
         <v>1.22589167767503</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L56" s="2">
         <f t="shared" si="3"/>
@@ -14218,36 +14374,40 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="Q56" s="2">
+      <c r="Q56" s="6">
+        <f t="shared" si="10"/>
+        <v>165</v>
+      </c>
+      <c r="R56" s="2">
         <f t="shared" si="7"/>
         <v>122</v>
       </c>
-      <c r="R56" s="2">
+      <c r="S56" s="2">
         <f t="shared" si="8"/>
         <v>123</v>
       </c>
-      <c r="S56" s="1">
-        <v>0</v>
-      </c>
       <c r="T56" s="1">
         <v>0</v>
       </c>
-      <c r="U56" s="4">
+      <c r="U56" s="1">
         <v>0</v>
       </c>
       <c r="V56" s="4">
         <v>0</v>
       </c>
-      <c r="W56" s="1">
+      <c r="W56" s="4">
+        <v>0</v>
+      </c>
+      <c r="X56" s="1">
         <f t="shared" si="0"/>
         <v>1230</v>
       </c>
-      <c r="X56" s="1">
+      <c r="Y56" s="1">
         <f t="shared" si="1"/>
         <v>1230</v>
       </c>
     </row>
-    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="57" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C57" s="1">
         <v>124</v>
       </c>
@@ -14264,17 +14424,17 @@
         <v>52</v>
       </c>
       <c r="H57" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J57" s="6">
         <f t="shared" si="2"/>
         <v>1.22844827586207</v>
       </c>
       <c r="K57" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L57" s="2">
         <f t="shared" si="3"/>
@@ -14296,36 +14456,40 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="Q57" s="2">
+      <c r="Q57" s="6">
+        <f t="shared" si="10"/>
+        <v>170</v>
+      </c>
+      <c r="R57" s="2">
         <f t="shared" si="7"/>
         <v>123</v>
       </c>
-      <c r="R57" s="2">
+      <c r="S57" s="2">
         <f t="shared" si="8"/>
         <v>124</v>
       </c>
-      <c r="S57" s="1">
-        <v>0</v>
-      </c>
       <c r="T57" s="1">
         <v>0</v>
       </c>
-      <c r="U57" s="4">
+      <c r="U57" s="1">
         <v>0</v>
       </c>
       <c r="V57" s="4">
         <v>0</v>
       </c>
-      <c r="W57" s="1">
+      <c r="W57" s="4">
+        <v>0</v>
+      </c>
+      <c r="X57" s="1">
         <f t="shared" si="0"/>
         <v>1240</v>
       </c>
-      <c r="X57" s="1">
+      <c r="Y57" s="1">
         <f t="shared" si="1"/>
         <v>1240</v>
       </c>
     </row>
-    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="58" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C58" s="1">
         <v>125</v>
       </c>
@@ -14342,17 +14506,17 @@
         <v>53</v>
       </c>
       <c r="H58" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J58" s="6">
         <f t="shared" si="2"/>
         <v>1.21929824561404</v>
       </c>
       <c r="K58" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="L58" s="2">
         <f t="shared" si="3"/>
@@ -14374,36 +14538,40 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="Q58" s="2">
+      <c r="Q58" s="6">
+        <f t="shared" si="10"/>
+        <v>175</v>
+      </c>
+      <c r="R58" s="2">
         <f t="shared" si="7"/>
         <v>124</v>
       </c>
-      <c r="R58" s="2">
+      <c r="S58" s="2">
         <f t="shared" si="8"/>
         <v>125</v>
       </c>
-      <c r="S58" s="1">
-        <v>0</v>
-      </c>
       <c r="T58" s="1">
         <v>0</v>
       </c>
-      <c r="U58" s="4">
+      <c r="U58" s="1">
         <v>0</v>
       </c>
       <c r="V58" s="4">
         <v>0</v>
       </c>
-      <c r="W58" s="1">
+      <c r="W58" s="4">
+        <v>0</v>
+      </c>
+      <c r="X58" s="1">
         <f t="shared" si="0"/>
         <v>1250</v>
       </c>
-      <c r="X58" s="1">
+      <c r="Y58" s="1">
         <f t="shared" si="1"/>
         <v>1250</v>
       </c>
     </row>
-    <row r="59" s="3" customFormat="1" customHeight="1" spans="3:24">
+    <row r="59" s="3" customFormat="1" customHeight="1" spans="3:25">
       <c r="C59" s="1">
         <v>126</v>
       </c>
@@ -14420,17 +14588,17 @@
         <v>54</v>
       </c>
       <c r="H59" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J59" s="6">
         <f t="shared" si="2"/>
         <v>1.22302158273381</v>
       </c>
       <c r="K59" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="L59" s="2">
         <f t="shared" si="3"/>
@@ -14452,36 +14620,40 @@
         <f t="shared" si="9"/>
         <v>21</v>
       </c>
-      <c r="Q59" s="2">
+      <c r="Q59" s="6">
+        <f t="shared" si="10"/>
+        <v>180</v>
+      </c>
+      <c r="R59" s="2">
         <f t="shared" si="7"/>
         <v>125</v>
       </c>
-      <c r="R59" s="2">
+      <c r="S59" s="2">
         <f t="shared" si="8"/>
         <v>126</v>
       </c>
-      <c r="S59" s="5">
-        <v>0</v>
-      </c>
       <c r="T59" s="5">
         <v>0</v>
       </c>
-      <c r="U59" s="3">
+      <c r="U59" s="5">
         <v>0</v>
       </c>
       <c r="V59" s="3">
         <v>0</v>
       </c>
-      <c r="W59" s="1">
+      <c r="W59" s="3">
+        <v>0</v>
+      </c>
+      <c r="X59" s="1">
         <f t="shared" si="0"/>
         <v>1260</v>
       </c>
-      <c r="X59" s="1">
+      <c r="Y59" s="1">
         <f t="shared" si="1"/>
         <v>1260</v>
       </c>
     </row>
-    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="60" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C60" s="1">
         <v>127</v>
       </c>
@@ -14498,17 +14670,17 @@
         <v>55</v>
       </c>
       <c r="H60" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J60" s="6">
         <f t="shared" si="2"/>
         <v>1.22352941176471</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L60" s="2">
         <f t="shared" si="3"/>
@@ -14530,36 +14702,40 @@
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="Q60" s="2">
+      <c r="Q60" s="6">
+        <f t="shared" si="10"/>
+        <v>185</v>
+      </c>
+      <c r="R60" s="2">
         <f t="shared" si="7"/>
         <v>126</v>
       </c>
-      <c r="R60" s="2">
+      <c r="S60" s="2">
         <f t="shared" si="8"/>
         <v>127</v>
       </c>
-      <c r="S60" s="1">
-        <v>0</v>
-      </c>
       <c r="T60" s="1">
         <v>0</v>
       </c>
-      <c r="U60" s="4">
+      <c r="U60" s="1">
         <v>0</v>
       </c>
       <c r="V60" s="4">
         <v>0</v>
       </c>
-      <c r="W60" s="1">
+      <c r="W60" s="4">
+        <v>0</v>
+      </c>
+      <c r="X60" s="1">
         <f t="shared" si="0"/>
         <v>1270</v>
       </c>
-      <c r="X60" s="1">
+      <c r="Y60" s="1">
         <f t="shared" si="1"/>
         <v>1270</v>
       </c>
     </row>
-    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="61" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C61" s="1">
         <v>128</v>
       </c>
@@ -14576,17 +14752,17 @@
         <v>56</v>
       </c>
       <c r="H61" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J61" s="6">
         <f t="shared" si="2"/>
         <v>1.23076923076923</v>
       </c>
       <c r="K61" s="13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L61" s="2">
         <f t="shared" si="3"/>
@@ -14608,36 +14784,40 @@
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="Q61" s="2">
+      <c r="Q61" s="6">
+        <f t="shared" si="10"/>
+        <v>190</v>
+      </c>
+      <c r="R61" s="2">
         <f t="shared" si="7"/>
         <v>127</v>
       </c>
-      <c r="R61" s="2">
+      <c r="S61" s="2">
         <f t="shared" si="8"/>
         <v>128</v>
       </c>
-      <c r="S61" s="1">
-        <v>0</v>
-      </c>
       <c r="T61" s="1">
         <v>0</v>
       </c>
-      <c r="U61" s="4">
+      <c r="U61" s="1">
         <v>0</v>
       </c>
       <c r="V61" s="4">
         <v>0</v>
       </c>
-      <c r="W61" s="1">
+      <c r="W61" s="4">
+        <v>0</v>
+      </c>
+      <c r="X61" s="1">
         <f t="shared" si="0"/>
         <v>1280</v>
       </c>
-      <c r="X61" s="1">
+      <c r="Y61" s="1">
         <f t="shared" si="1"/>
         <v>1280</v>
       </c>
     </row>
-    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="62" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C62" s="1">
         <v>129</v>
       </c>
@@ -14654,17 +14834,17 @@
         <v>57</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J62" s="6">
         <f t="shared" si="2"/>
         <v>1.22265625</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L62" s="2">
         <f t="shared" si="3"/>
@@ -14686,36 +14866,40 @@
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="Q62" s="2">
+      <c r="Q62" s="6">
+        <f t="shared" si="10"/>
+        <v>195</v>
+      </c>
+      <c r="R62" s="2">
         <f t="shared" si="7"/>
         <v>128</v>
       </c>
-      <c r="R62" s="2">
+      <c r="S62" s="2">
         <f t="shared" si="8"/>
         <v>129</v>
       </c>
-      <c r="S62" s="1">
-        <v>0</v>
-      </c>
       <c r="T62" s="1">
         <v>0</v>
       </c>
-      <c r="U62" s="4">
+      <c r="U62" s="1">
         <v>0</v>
       </c>
       <c r="V62" s="4">
         <v>0</v>
       </c>
-      <c r="W62" s="1">
+      <c r="W62" s="4">
+        <v>0</v>
+      </c>
+      <c r="X62" s="1">
         <f t="shared" si="0"/>
         <v>1290</v>
       </c>
-      <c r="X62" s="1">
+      <c r="Y62" s="1">
         <f t="shared" si="1"/>
         <v>1290</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="63" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C63" s="1">
         <v>130</v>
       </c>
@@ -14732,17 +14916,17 @@
         <v>58</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J63" s="6">
         <f t="shared" si="2"/>
         <v>1.22364217252396</v>
       </c>
       <c r="K63" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L63" s="2">
         <f t="shared" si="3"/>
@@ -14764,36 +14948,40 @@
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="Q63" s="2">
+      <c r="Q63" s="6">
+        <f t="shared" si="10"/>
+        <v>200</v>
+      </c>
+      <c r="R63" s="2">
         <f t="shared" si="7"/>
         <v>129</v>
       </c>
-      <c r="R63" s="2">
+      <c r="S63" s="2">
         <f t="shared" si="8"/>
         <v>130</v>
       </c>
-      <c r="S63" s="1">
-        <v>0</v>
-      </c>
       <c r="T63" s="1">
         <v>0</v>
       </c>
-      <c r="U63" s="4">
+      <c r="U63" s="1">
         <v>0</v>
       </c>
       <c r="V63" s="4">
         <v>0</v>
       </c>
-      <c r="W63" s="1">
+      <c r="W63" s="4">
+        <v>0</v>
+      </c>
+      <c r="X63" s="1">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="X63" s="1">
+      <c r="Y63" s="1">
         <f t="shared" si="1"/>
         <v>1300</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:24">
+    <row r="64" s="2" customFormat="1" customHeight="1" spans="3:25">
       <c r="C64" s="1">
         <v>131</v>
       </c>
@@ -14810,17 +14998,17 @@
         <v>59</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J64" s="6">
         <f t="shared" si="2"/>
         <v>1.22193211488251</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L64" s="2">
         <f t="shared" si="3"/>
@@ -14842,36 +15030,40 @@
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="Q64" s="2">
+      <c r="Q64" s="6">
+        <f t="shared" si="10"/>
+        <v>205</v>
+      </c>
+      <c r="R64" s="2">
         <f t="shared" si="7"/>
         <v>130</v>
       </c>
-      <c r="R64" s="2">
+      <c r="S64" s="2">
         <f t="shared" si="8"/>
         <v>131</v>
       </c>
-      <c r="S64" s="1">
-        <v>0</v>
-      </c>
       <c r="T64" s="1">
         <v>0</v>
       </c>
-      <c r="U64" s="4">
+      <c r="U64" s="1">
         <v>0</v>
       </c>
       <c r="V64" s="4">
         <v>0</v>
       </c>
-      <c r="W64" s="1">
+      <c r="W64" s="4">
+        <v>0</v>
+      </c>
+      <c r="X64" s="1">
         <f t="shared" si="0"/>
         <v>1310</v>
       </c>
-      <c r="X64" s="1">
+      <c r="Y64" s="1">
         <f t="shared" si="1"/>
         <v>1310</v>
       </c>
     </row>
-    <row r="65" s="3" customFormat="1" customHeight="1" spans="1:24">
+    <row r="65" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="C65" s="1">
         <v>132</v>
       </c>
@@ -14888,17 +15080,17 @@
         <v>60</v>
       </c>
       <c r="H65" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J65" s="6">
         <f t="shared" si="2"/>
         <v>1.22222222222222</v>
       </c>
       <c r="K65" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L65" s="2">
         <f t="shared" si="3"/>
@@ -14920,36 +15112,40 @@
         <f t="shared" si="9"/>
         <v>22</v>
       </c>
-      <c r="Q65" s="2">
+      <c r="Q65" s="6">
+        <f t="shared" si="10"/>
+        <v>210</v>
+      </c>
+      <c r="R65" s="2">
         <f t="shared" si="7"/>
         <v>131</v>
       </c>
-      <c r="R65" s="2">
+      <c r="S65" s="2">
         <f t="shared" si="8"/>
         <v>132</v>
       </c>
-      <c r="S65" s="5">
-        <v>0</v>
-      </c>
       <c r="T65" s="5">
         <v>0</v>
       </c>
-      <c r="U65" s="3">
+      <c r="U65" s="5">
         <v>0</v>
       </c>
       <c r="V65" s="3">
         <v>0</v>
       </c>
-      <c r="W65" s="1">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="1">
         <f t="shared" si="0"/>
         <v>1320</v>
       </c>
-      <c r="X65" s="1">
+      <c r="Y65" s="1">
         <f t="shared" si="1"/>
         <v>1320</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="66" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C66" s="1">
         <v>133</v>
       </c>
@@ -14966,17 +15162,17 @@
         <v>61</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J66" s="6">
         <f t="shared" si="2"/>
         <v>1.21853146853147</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L66" s="2">
         <f t="shared" si="3"/>
@@ -14998,36 +15194,40 @@
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="Q66" s="2">
+      <c r="Q66" s="6">
+        <f t="shared" si="10"/>
+        <v>215</v>
+      </c>
+      <c r="R66" s="2">
         <f t="shared" si="7"/>
         <v>132</v>
       </c>
-      <c r="R66" s="2">
+      <c r="S66" s="2">
         <f t="shared" si="8"/>
         <v>133</v>
       </c>
-      <c r="S66" s="1">
-        <v>0</v>
-      </c>
       <c r="T66" s="1">
         <v>0</v>
       </c>
-      <c r="U66" s="4">
+      <c r="U66" s="1">
         <v>0</v>
       </c>
       <c r="V66" s="4">
         <v>0</v>
       </c>
-      <c r="W66" s="1">
+      <c r="W66" s="4">
+        <v>0</v>
+      </c>
+      <c r="X66" s="1">
         <f t="shared" si="0"/>
         <v>1330</v>
       </c>
-      <c r="X66" s="1">
+      <c r="Y66" s="1">
         <f t="shared" si="1"/>
         <v>1330</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="67" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C67" s="1">
         <v>134</v>
       </c>
@@ -15044,17 +15244,17 @@
         <v>62</v>
       </c>
       <c r="H67" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J67" s="6">
         <f t="shared" si="2"/>
         <v>1.22238163558106</v>
       </c>
       <c r="K67" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L67" s="2">
         <f t="shared" si="3"/>
@@ -15076,36 +15276,40 @@
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="Q67" s="2">
+      <c r="Q67" s="6">
+        <f t="shared" si="10"/>
+        <v>220</v>
+      </c>
+      <c r="R67" s="2">
         <f t="shared" si="7"/>
         <v>133</v>
       </c>
-      <c r="R67" s="2">
+      <c r="S67" s="2">
         <f t="shared" si="8"/>
         <v>134</v>
       </c>
-      <c r="S67" s="1">
-        <v>0</v>
-      </c>
       <c r="T67" s="1">
         <v>0</v>
       </c>
-      <c r="U67" s="4">
+      <c r="U67" s="1">
         <v>0</v>
       </c>
       <c r="V67" s="4">
         <v>0</v>
       </c>
-      <c r="W67" s="1">
+      <c r="W67" s="4">
+        <v>0</v>
+      </c>
+      <c r="X67" s="1">
         <f t="shared" si="0"/>
         <v>1340</v>
       </c>
-      <c r="X67" s="1">
+      <c r="Y67" s="1">
         <f t="shared" si="1"/>
         <v>1340</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="68" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C68" s="1">
         <v>135</v>
       </c>
@@ -15122,17 +15326,17 @@
         <v>63</v>
       </c>
       <c r="H68" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J68" s="6">
         <f t="shared" si="2"/>
         <v>1.22065727699531</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L68" s="2">
         <f t="shared" si="3"/>
@@ -15154,36 +15358,40 @@
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="Q68" s="2">
+      <c r="Q68" s="6">
+        <f t="shared" si="10"/>
+        <v>225</v>
+      </c>
+      <c r="R68" s="2">
         <f t="shared" si="7"/>
         <v>134</v>
       </c>
-      <c r="R68" s="2">
+      <c r="S68" s="2">
         <f t="shared" si="8"/>
         <v>135</v>
       </c>
-      <c r="S68" s="1">
-        <v>0</v>
-      </c>
       <c r="T68" s="1">
         <v>0</v>
       </c>
-      <c r="U68" s="4">
+      <c r="U68" s="1">
         <v>0</v>
       </c>
       <c r="V68" s="4">
         <v>0</v>
       </c>
-      <c r="W68" s="1">
+      <c r="W68" s="4">
+        <v>0</v>
+      </c>
+      <c r="X68" s="1">
         <f t="shared" si="0"/>
         <v>1350</v>
       </c>
-      <c r="X68" s="1">
+      <c r="Y68" s="1">
         <f t="shared" si="1"/>
         <v>1350</v>
       </c>
     </row>
-    <row r="69" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C69" s="1">
         <v>136</v>
       </c>
@@ -15200,17 +15408,17 @@
         <v>64</v>
       </c>
       <c r="H69" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J69" s="6">
         <f t="shared" si="2"/>
         <v>1.22115384615385</v>
       </c>
       <c r="K69" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L69" s="2">
         <f t="shared" si="3"/>
@@ -15232,36 +15440,40 @@
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="Q69" s="2">
+      <c r="Q69" s="6">
+        <f t="shared" si="10"/>
+        <v>230</v>
+      </c>
+      <c r="R69" s="2">
         <f t="shared" si="7"/>
         <v>135</v>
       </c>
-      <c r="R69" s="2">
+      <c r="S69" s="2">
         <f t="shared" si="8"/>
         <v>136</v>
       </c>
-      <c r="S69" s="1">
-        <v>0</v>
-      </c>
       <c r="T69" s="1">
         <v>0</v>
       </c>
-      <c r="U69" s="4">
+      <c r="U69" s="1">
         <v>0</v>
       </c>
       <c r="V69" s="4">
         <v>0</v>
       </c>
-      <c r="W69" s="1">
+      <c r="W69" s="4">
+        <v>0</v>
+      </c>
+      <c r="X69" s="1">
         <f t="shared" si="0"/>
         <v>1360</v>
       </c>
-      <c r="X69" s="1">
+      <c r="Y69" s="1">
         <f t="shared" si="1"/>
         <v>1360</v>
       </c>
     </row>
-    <row r="70" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C70" s="1">
         <v>137</v>
       </c>
@@ -15278,17 +15490,17 @@
         <v>65</v>
       </c>
       <c r="H70" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J70" s="6">
         <f t="shared" si="2"/>
         <v>1.22047244094488</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L70" s="2">
         <f t="shared" si="3"/>
@@ -15310,36 +15522,40 @@
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="Q70" s="2">
+      <c r="Q70" s="6">
+        <f t="shared" si="10"/>
+        <v>235</v>
+      </c>
+      <c r="R70" s="2">
         <f t="shared" si="7"/>
         <v>136</v>
       </c>
-      <c r="R70" s="2">
+      <c r="S70" s="2">
         <f t="shared" si="8"/>
         <v>137</v>
       </c>
-      <c r="S70" s="1">
-        <v>0</v>
-      </c>
       <c r="T70" s="1">
         <v>0</v>
       </c>
-      <c r="U70" s="4">
+      <c r="U70" s="1">
         <v>0</v>
       </c>
       <c r="V70" s="4">
         <v>0</v>
       </c>
-      <c r="W70" s="1">
-        <f t="shared" ref="W70:W77" si="10">C70*10</f>
+      <c r="W70" s="4">
+        <v>0</v>
+      </c>
+      <c r="X70" s="1">
+        <f t="shared" ref="X70:X77" si="11">C70*10</f>
         <v>1370</v>
       </c>
-      <c r="X70" s="1">
-        <f t="shared" ref="X70:X77" si="11">D70*10</f>
+      <c r="Y70" s="1">
+        <f t="shared" ref="Y70:Y77" si="12">D70*10</f>
         <v>1370</v>
       </c>
     </row>
-    <row r="71" s="3" customFormat="1" customHeight="1" spans="1:24">
+    <row r="71" s="3" customFormat="1" customHeight="1" spans="1:25">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="1">
@@ -15358,68 +15574,72 @@
         <v>66</v>
       </c>
       <c r="H71" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J71" s="6">
-        <f t="shared" ref="J71:J77" si="12">I71/I70</f>
+        <f t="shared" ref="J71:J77" si="13">I71/I70</f>
         <v>1.21935483870968</v>
       </c>
       <c r="K71" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L71" s="2">
-        <f t="shared" ref="L71:L77" si="13">L70+20</f>
+        <f t="shared" ref="L71:L77" si="14">L70+20</f>
         <v>1740</v>
       </c>
       <c r="M71" s="2">
-        <f t="shared" ref="M71:M77" si="14">M70+10</f>
+        <f t="shared" ref="M71:M77" si="15">M70+10</f>
         <v>900</v>
       </c>
       <c r="N71" s="2">
-        <f t="shared" ref="N71:N77" si="15">N70+3</f>
+        <f t="shared" ref="N71:N77" si="16">N70+3</f>
         <v>342</v>
       </c>
       <c r="O71" s="2">
-        <f t="shared" ref="O71:O77" si="16">O70+10</f>
+        <f t="shared" ref="O71:O77" si="17">O70+10</f>
         <v>950</v>
       </c>
       <c r="P71" s="6">
         <f t="shared" si="9"/>
         <v>23</v>
       </c>
-      <c r="Q71" s="2">
-        <f t="shared" ref="Q71:Q77" si="17">Q70+1</f>
-        <v>137</v>
+      <c r="Q71" s="6">
+        <f t="shared" si="10"/>
+        <v>240</v>
       </c>
       <c r="R71" s="2">
         <f t="shared" ref="R71:R77" si="18">R70+1</f>
+        <v>137</v>
+      </c>
+      <c r="S71" s="2">
+        <f t="shared" ref="S71:S77" si="19">S70+1</f>
         <v>138</v>
       </c>
-      <c r="S71" s="5">
-        <v>0</v>
-      </c>
       <c r="T71" s="5">
         <v>0</v>
       </c>
-      <c r="U71" s="3">
+      <c r="U71" s="5">
         <v>0</v>
       </c>
       <c r="V71" s="3">
         <v>0</v>
       </c>
-      <c r="W71" s="1">
-        <f t="shared" si="10"/>
-        <v>1380</v>
+      <c r="W71" s="3">
+        <v>0</v>
       </c>
       <c r="X71" s="1">
         <f t="shared" si="11"/>
         <v>1380</v>
       </c>
-    </row>
-    <row r="72" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="Y71" s="1">
+        <f t="shared" si="12"/>
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C72" s="1">
         <v>139</v>
       </c>
@@ -15436,68 +15656,72 @@
         <v>67</v>
       </c>
       <c r="H72" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J72" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.21693121693122</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L72" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1760</v>
       </c>
       <c r="M72" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>910</v>
       </c>
       <c r="N72" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>345</v>
       </c>
       <c r="O72" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>960</v>
       </c>
       <c r="P72" s="6">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="Q72" s="2">
-        <f t="shared" si="17"/>
-        <v>138</v>
+      <c r="Q72" s="6">
+        <f t="shared" si="10"/>
+        <v>245</v>
       </c>
       <c r="R72" s="2">
         <f t="shared" si="18"/>
+        <v>138</v>
+      </c>
+      <c r="S72" s="2">
+        <f t="shared" si="19"/>
         <v>139</v>
       </c>
-      <c r="S72" s="1">
-        <v>0</v>
-      </c>
       <c r="T72" s="1">
         <v>0</v>
       </c>
-      <c r="U72" s="4">
+      <c r="U72" s="1">
         <v>0</v>
       </c>
       <c r="V72" s="4">
         <v>0</v>
       </c>
-      <c r="W72" s="1">
-        <f t="shared" si="10"/>
-        <v>1390</v>
+      <c r="W72" s="4">
+        <v>0</v>
       </c>
       <c r="X72" s="1">
         <f t="shared" si="11"/>
         <v>1390</v>
       </c>
-    </row>
-    <row r="73" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="Y72" s="1">
+        <f t="shared" si="12"/>
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C73" s="1">
         <v>140</v>
       </c>
@@ -15514,68 +15738,72 @@
         <v>68</v>
       </c>
       <c r="H73" s="14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J73" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.22173913043478</v>
       </c>
       <c r="K73" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L73" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1780</v>
       </c>
       <c r="M73" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>920</v>
       </c>
       <c r="N73" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>348</v>
       </c>
       <c r="O73" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>970</v>
       </c>
       <c r="P73" s="6">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="Q73" s="2">
-        <f t="shared" si="17"/>
-        <v>139</v>
+      <c r="Q73" s="6">
+        <f t="shared" si="10"/>
+        <v>250</v>
       </c>
       <c r="R73" s="2">
         <f t="shared" si="18"/>
+        <v>139</v>
+      </c>
+      <c r="S73" s="2">
+        <f t="shared" si="19"/>
         <v>140</v>
       </c>
-      <c r="S73" s="1">
-        <v>0</v>
-      </c>
       <c r="T73" s="1">
         <v>0</v>
       </c>
-      <c r="U73" s="4">
+      <c r="U73" s="1">
         <v>0</v>
       </c>
       <c r="V73" s="4">
         <v>0</v>
       </c>
-      <c r="W73" s="1">
-        <f t="shared" si="10"/>
-        <v>1400</v>
+      <c r="W73" s="4">
+        <v>0</v>
       </c>
       <c r="X73" s="1">
         <f t="shared" si="11"/>
         <v>1400</v>
       </c>
-    </row>
-    <row r="74" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="Y73" s="1">
+        <f t="shared" si="12"/>
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C74" s="1">
         <v>141</v>
       </c>
@@ -15592,68 +15820,72 @@
         <v>69</v>
       </c>
       <c r="H74" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J74" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.22064056939502</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L74" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1800</v>
       </c>
       <c r="M74" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>930</v>
       </c>
       <c r="N74" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>351</v>
       </c>
       <c r="O74" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>980</v>
       </c>
       <c r="P74" s="6">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="Q74" s="2">
-        <f t="shared" si="17"/>
-        <v>140</v>
+      <c r="Q74" s="6">
+        <f t="shared" si="10"/>
+        <v>255</v>
       </c>
       <c r="R74" s="2">
         <f t="shared" si="18"/>
+        <v>140</v>
+      </c>
+      <c r="S74" s="2">
+        <f t="shared" si="19"/>
         <v>141</v>
       </c>
-      <c r="S74" s="1">
-        <v>0</v>
-      </c>
       <c r="T74" s="1">
         <v>0</v>
       </c>
-      <c r="U74" s="4">
+      <c r="U74" s="1">
         <v>0</v>
       </c>
       <c r="V74" s="4">
         <v>0</v>
       </c>
-      <c r="W74" s="1">
-        <f t="shared" si="10"/>
-        <v>1410</v>
+      <c r="W74" s="4">
+        <v>0</v>
       </c>
       <c r="X74" s="1">
         <f t="shared" si="11"/>
         <v>1410</v>
       </c>
-    </row>
-    <row r="75" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="Y74" s="1">
+        <f t="shared" si="12"/>
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C75" s="1">
         <v>142</v>
       </c>
@@ -15670,68 +15902,72 @@
         <v>70</v>
       </c>
       <c r="H75" s="14" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J75" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.21865889212828</v>
       </c>
       <c r="K75" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L75" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1820</v>
       </c>
       <c r="M75" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>940</v>
       </c>
       <c r="N75" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>354</v>
       </c>
       <c r="O75" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>990</v>
       </c>
       <c r="P75" s="6">
         <f t="shared" si="9"/>
         <v>24</v>
       </c>
-      <c r="Q75" s="2">
-        <f t="shared" si="17"/>
-        <v>141</v>
+      <c r="Q75" s="6">
+        <f t="shared" si="10"/>
+        <v>260</v>
       </c>
       <c r="R75" s="2">
         <f t="shared" si="18"/>
+        <v>141</v>
+      </c>
+      <c r="S75" s="2">
+        <f t="shared" si="19"/>
         <v>142</v>
       </c>
-      <c r="S75" s="1">
-        <v>0</v>
-      </c>
       <c r="T75" s="1">
         <v>0</v>
       </c>
-      <c r="U75" s="4">
+      <c r="U75" s="1">
         <v>0</v>
       </c>
       <c r="V75" s="4">
         <v>0</v>
       </c>
-      <c r="W75" s="1">
-        <f t="shared" si="10"/>
-        <v>1420</v>
+      <c r="W75" s="4">
+        <v>0</v>
       </c>
       <c r="X75" s="1">
         <f t="shared" si="11"/>
         <v>1420</v>
       </c>
-    </row>
-    <row r="76" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="Y75" s="1">
+        <f t="shared" si="12"/>
+        <v>1420</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C76" s="1">
         <v>143</v>
       </c>
@@ -15748,68 +15984,72 @@
         <v>71</v>
       </c>
       <c r="H76" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J76" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.2177033492823</v>
       </c>
       <c r="K76" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L76" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1840</v>
       </c>
       <c r="M76" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>950</v>
       </c>
       <c r="N76" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>357</v>
       </c>
       <c r="O76" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1000</v>
       </c>
       <c r="P76" s="6">
         <f>P70+1</f>
         <v>24</v>
       </c>
-      <c r="Q76" s="2">
-        <f t="shared" si="17"/>
-        <v>142</v>
+      <c r="Q76" s="6">
+        <f t="shared" si="10"/>
+        <v>265</v>
       </c>
       <c r="R76" s="2">
         <f t="shared" si="18"/>
+        <v>142</v>
+      </c>
+      <c r="S76" s="2">
+        <f t="shared" si="19"/>
         <v>143</v>
       </c>
-      <c r="S76" s="1">
-        <v>0</v>
-      </c>
       <c r="T76" s="1">
         <v>0</v>
       </c>
-      <c r="U76" s="4">
+      <c r="U76" s="1">
         <v>0</v>
       </c>
       <c r="V76" s="4">
         <v>0</v>
       </c>
-      <c r="W76" s="1">
-        <f t="shared" si="10"/>
-        <v>1430</v>
+      <c r="W76" s="4">
+        <v>0</v>
       </c>
       <c r="X76" s="1">
         <f t="shared" si="11"/>
         <v>1430</v>
       </c>
-    </row>
-    <row r="77" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="Y76" s="1">
+        <f t="shared" si="12"/>
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="77" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C77" s="1">
         <v>144</v>
       </c>
@@ -15826,82 +16066,86 @@
         <v>72</v>
       </c>
       <c r="H77" s="14" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J77" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.21807465618861</v>
       </c>
       <c r="K77" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="L77" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1860</v>
       </c>
       <c r="M77" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>960</v>
       </c>
       <c r="N77" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>360</v>
       </c>
       <c r="O77" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1010</v>
       </c>
       <c r="P77" s="6">
         <f>P71+1</f>
         <v>24</v>
       </c>
-      <c r="Q77" s="2">
-        <f t="shared" si="17"/>
-        <v>143</v>
+      <c r="Q77" s="6">
+        <f t="shared" si="10"/>
+        <v>270</v>
       </c>
       <c r="R77" s="2">
         <f t="shared" si="18"/>
+        <v>143</v>
+      </c>
+      <c r="S77" s="2">
+        <f t="shared" si="19"/>
         <v>144</v>
       </c>
-      <c r="S77" s="1">
-        <v>0</v>
-      </c>
       <c r="T77" s="1">
         <v>0</v>
       </c>
-      <c r="U77" s="4">
+      <c r="U77" s="1">
         <v>0</v>
       </c>
       <c r="V77" s="4">
         <v>0</v>
       </c>
-      <c r="W77" s="1">
-        <f t="shared" si="10"/>
-        <v>1440</v>
+      <c r="W77" s="4">
+        <v>0</v>
       </c>
       <c r="X77" s="1">
         <f t="shared" si="11"/>
         <v>1440</v>
       </c>
-    </row>
-    <row r="78" s="2" customFormat="1" customHeight="1" spans="1:24">
+      <c r="Y77" s="1">
+        <f t="shared" si="12"/>
+        <v>1440</v>
+      </c>
+    </row>
+    <row r="78" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="6"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="79" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="6"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80" s="2" customFormat="1" customHeight="1" spans="1:24">
+    <row r="80" s="2" customFormat="1" customHeight="1" spans="1:25">
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -16071,7 +16315,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3:J5 C3:I5 K3:V5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="Q3 Q4 Q5 C3:P5 R3:W5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
